--- a/Casa_do_Mosteiro_v6.xlsx
+++ b/Casa_do_Mosteiro_v6.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Patrick SALVADOR\Documents\Immobilier\Locations - Airbnb - Booking\Casa do mosteiro - Aluguer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1513693D-BDA5-4012-8B5E-ADAAC2E77D67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4552421-75B8-49B2-A98B-DA443C33C269}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="53">
   <si>
     <t>🏠  CASA DO MOSTEIRO — Réservations</t>
   </si>
@@ -151,9 +151,6 @@
     <t>⏳ À faire</t>
   </si>
   <si>
-    <t>Direto</t>
-  </si>
-  <si>
     <t>Tarde</t>
   </si>
   <si>
@@ -188,12 +185,6 @@
   </si>
   <si>
     <t>00351925359867</t>
-  </si>
-  <si>
-    <t>Bob</t>
-  </si>
-  <si>
-    <t>0033616081819</t>
   </si>
 </sst>
 </file>
@@ -1026,10 +1017,10 @@
         <v>🔵 À venir</v>
       </c>
       <c r="O3" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P3" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1083,10 +1074,10 @@
         <v>🔵 À venir</v>
       </c>
       <c r="O4" s="19" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="P4" s="20" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1140,10 +1131,10 @@
         <v>🔵 À venir</v>
       </c>
       <c r="O5" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="P5" s="12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1197,10 +1188,10 @@
         <v>✅ Terminée</v>
       </c>
       <c r="O6" s="19" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="P6" s="20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1254,10 +1245,10 @@
         <v>✅ Terminée</v>
       </c>
       <c r="O7" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="P7" s="12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1311,10 +1302,10 @@
         <v>🔵 À venir</v>
       </c>
       <c r="O8" s="19" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="P8" s="20" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1368,10 +1359,10 @@
         <v>🔵 À venir</v>
       </c>
       <c r="O9" s="11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="P9" s="12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
@@ -1425,10 +1416,10 @@
         <v>🔵 À venir</v>
       </c>
       <c r="O10" s="19" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="P10" s="20" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
@@ -2430,7 +2421,7 @@
       <c r="G35" s="5"/>
       <c r="H35" s="8"/>
       <c r="I35" s="9" t="str">
-        <f t="shared" ref="I35:I51" si="8">IF(B35="Direto","",IF(B35="Airbnb",IF(H35&lt;&gt;"",H35*0.03+H35*0.03*0.2,""),IF(B35="Booking.com",IF(H35&lt;&gt;"",H35*0.15+H35*0.014,""),"")))</f>
+        <f t="shared" ref="I35:I50" si="8">IF(B35="Direto","",IF(B35="Airbnb",IF(H35&lt;&gt;"",H35*0.03+H35*0.03*0.2,""),IF(B35="Booking.com",IF(H35&lt;&gt;"",H35*0.15+H35*0.014,""),"")))</f>
         <v/>
       </c>
       <c r="J35" s="10" t="str">
@@ -3071,62 +3062,23 @@
       <c r="O50" s="19"/>
       <c r="P50" s="20"/>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A51" s="13">
-        <v>49</v>
-      </c>
-      <c r="B51" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="C51" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="D51" s="16">
-        <v>46259</v>
-      </c>
-      <c r="E51" s="16">
-        <v>46262</v>
-      </c>
-      <c r="F51" s="14">
-        <f t="shared" si="7"/>
-        <v>3</v>
-      </c>
-      <c r="G51" s="14">
-        <v>5</v>
-      </c>
-      <c r="H51" s="17">
-        <v>600</v>
-      </c>
-      <c r="I51" s="9" t="str">
-        <f>IF(B51="Direto","",IF(B51="Airbnb",IF(H51&lt;&gt;"",H51*0.03+H51*0.03*0.2,""),IF(B51="Booking.com",IF(H51&lt;&gt;"",H51*0.15+H51*0.014,""),"")))</f>
-        <v/>
-      </c>
-      <c r="J51" s="18">
-        <f t="shared" si="9"/>
-        <v>600</v>
-      </c>
-      <c r="K51" s="18">
-        <f t="shared" si="10"/>
-        <v>150</v>
-      </c>
-      <c r="L51" s="9" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="M51" s="9" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="N51" s="14" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v>🔵 À venir</v>
-      </c>
-      <c r="O51" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="P51" s="20" t="s">
-        <v>55</v>
-      </c>
+    <row r="51" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="13"/>
+      <c r="B51" s="14"/>
+      <c r="C51" s="22"/>
+      <c r="D51" s="16"/>
+      <c r="E51" s="16"/>
+      <c r="F51" s="14"/>
+      <c r="G51" s="14"/>
+      <c r="H51" s="17"/>
+      <c r="I51" s="9"/>
+      <c r="J51" s="18"/>
+      <c r="K51" s="18"/>
+      <c r="L51" s="9"/>
+      <c r="M51" s="9"/>
+      <c r="N51" s="14"/>
+      <c r="O51" s="19"/>
+      <c r="P51" s="20"/>
     </row>
     <row r="52" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="38" t="s">
@@ -3140,7 +3092,7 @@
       <c r="G52" s="38"/>
       <c r="H52" s="23">
         <f t="shared" ref="H52:M52" si="14">SUMIF(H3:H51,"&gt;0")</f>
-        <v>4034.04</v>
+        <v>3434.04</v>
       </c>
       <c r="I52" s="24">
         <f t="shared" si="14"/>
@@ -3148,11 +3100,11 @@
       </c>
       <c r="J52" s="23">
         <f t="shared" si="14"/>
-        <v>3578.3774399999998</v>
+        <v>2978.3774399999998</v>
       </c>
       <c r="K52" s="23">
         <f t="shared" si="14"/>
-        <v>894.59435999999994</v>
+        <v>744.59435999999994</v>
       </c>
       <c r="L52" s="24">
         <f t="shared" si="14"/>
@@ -3172,7 +3124,7 @@
     <row r="53" spans="1:16" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J53" s="27">
         <f>J52-K52</f>
-        <v>2683.7830799999997</v>
+        <v>2233.7830799999997</v>
       </c>
     </row>
     <row r="54" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">

--- a/Casa_do_Mosteiro_v6.xlsx
+++ b/Casa_do_Mosteiro_v6.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Patrick SALVADOR\Documents\Immobilier\Locations - Airbnb - Booking\Casa do mosteiro - Aluguer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4552421-75B8-49B2-A98B-DA443C33C269}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1513693D-BDA5-4012-8B5E-ADAAC2E77D67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="56">
   <si>
     <t>🏠  CASA DO MOSTEIRO — Réservations</t>
   </si>
@@ -151,6 +151,9 @@
     <t>⏳ À faire</t>
   </si>
   <si>
+    <t>Direto</t>
+  </si>
+  <si>
     <t>Tarde</t>
   </si>
   <si>
@@ -185,6 +188,12 @@
   </si>
   <si>
     <t>00351925359867</t>
+  </si>
+  <si>
+    <t>Bob</t>
+  </si>
+  <si>
+    <t>0033616081819</t>
   </si>
 </sst>
 </file>
@@ -1017,10 +1026,10 @@
         <v>🔵 À venir</v>
       </c>
       <c r="O3" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="P3" s="12" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1074,10 +1083,10 @@
         <v>🔵 À venir</v>
       </c>
       <c r="O4" s="19" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P4" s="20" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1131,10 +1140,10 @@
         <v>🔵 À venir</v>
       </c>
       <c r="O5" s="11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="P5" s="12" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1188,10 +1197,10 @@
         <v>✅ Terminée</v>
       </c>
       <c r="O6" s="19" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P6" s="20" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1245,10 +1254,10 @@
         <v>✅ Terminée</v>
       </c>
       <c r="O7" s="11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="P7" s="12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1302,10 +1311,10 @@
         <v>🔵 À venir</v>
       </c>
       <c r="O8" s="19" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P8" s="20" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1359,10 +1368,10 @@
         <v>🔵 À venir</v>
       </c>
       <c r="O9" s="11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="P9" s="12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
@@ -1416,10 +1425,10 @@
         <v>🔵 À venir</v>
       </c>
       <c r="O10" s="19" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P10" s="20" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
@@ -2421,7 +2430,7 @@
       <c r="G35" s="5"/>
       <c r="H35" s="8"/>
       <c r="I35" s="9" t="str">
-        <f t="shared" ref="I35:I50" si="8">IF(B35="Direto","",IF(B35="Airbnb",IF(H35&lt;&gt;"",H35*0.03+H35*0.03*0.2,""),IF(B35="Booking.com",IF(H35&lt;&gt;"",H35*0.15+H35*0.014,""),"")))</f>
+        <f t="shared" ref="I35:I51" si="8">IF(B35="Direto","",IF(B35="Airbnb",IF(H35&lt;&gt;"",H35*0.03+H35*0.03*0.2,""),IF(B35="Booking.com",IF(H35&lt;&gt;"",H35*0.15+H35*0.014,""),"")))</f>
         <v/>
       </c>
       <c r="J35" s="10" t="str">
@@ -3062,23 +3071,62 @@
       <c r="O50" s="19"/>
       <c r="P50" s="20"/>
     </row>
-    <row r="51" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="13"/>
-      <c r="B51" s="14"/>
-      <c r="C51" s="22"/>
-      <c r="D51" s="16"/>
-      <c r="E51" s="16"/>
-      <c r="F51" s="14"/>
-      <c r="G51" s="14"/>
-      <c r="H51" s="17"/>
-      <c r="I51" s="9"/>
-      <c r="J51" s="18"/>
-      <c r="K51" s="18"/>
-      <c r="L51" s="9"/>
-      <c r="M51" s="9"/>
-      <c r="N51" s="14"/>
-      <c r="O51" s="19"/>
-      <c r="P51" s="20"/>
+    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A51" s="13">
+        <v>49</v>
+      </c>
+      <c r="B51" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="C51" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="D51" s="16">
+        <v>46259</v>
+      </c>
+      <c r="E51" s="16">
+        <v>46262</v>
+      </c>
+      <c r="F51" s="14">
+        <f t="shared" si="7"/>
+        <v>3</v>
+      </c>
+      <c r="G51" s="14">
+        <v>5</v>
+      </c>
+      <c r="H51" s="17">
+        <v>600</v>
+      </c>
+      <c r="I51" s="9" t="str">
+        <f>IF(B51="Direto","",IF(B51="Airbnb",IF(H51&lt;&gt;"",H51*0.03+H51*0.03*0.2,""),IF(B51="Booking.com",IF(H51&lt;&gt;"",H51*0.15+H51*0.014,""),"")))</f>
+        <v/>
+      </c>
+      <c r="J51" s="18">
+        <f t="shared" si="9"/>
+        <v>600</v>
+      </c>
+      <c r="K51" s="18">
+        <f t="shared" si="10"/>
+        <v>150</v>
+      </c>
+      <c r="L51" s="9" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="M51" s="9" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="N51" s="14" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v>🔵 À venir</v>
+      </c>
+      <c r="O51" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="P51" s="20" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="52" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="38" t="s">
@@ -3092,7 +3140,7 @@
       <c r="G52" s="38"/>
       <c r="H52" s="23">
         <f t="shared" ref="H52:M52" si="14">SUMIF(H3:H51,"&gt;0")</f>
-        <v>3434.04</v>
+        <v>4034.04</v>
       </c>
       <c r="I52" s="24">
         <f t="shared" si="14"/>
@@ -3100,11 +3148,11 @@
       </c>
       <c r="J52" s="23">
         <f t="shared" si="14"/>
-        <v>2978.3774399999998</v>
+        <v>3578.3774399999998</v>
       </c>
       <c r="K52" s="23">
         <f t="shared" si="14"/>
-        <v>744.59435999999994</v>
+        <v>894.59435999999994</v>
       </c>
       <c r="L52" s="24">
         <f t="shared" si="14"/>
@@ -3124,7 +3172,7 @@
     <row r="53" spans="1:16" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J53" s="27">
         <f>J52-K52</f>
-        <v>2233.7830799999997</v>
+        <v>2683.7830799999997</v>
       </c>
     </row>
     <row r="54" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">

--- a/Casa_do_Mosteiro_v6.xlsx
+++ b/Casa_do_Mosteiro_v6.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Patrick SALVADOR\Documents\Immobilier\Locations - Airbnb - Booking\Casa do mosteiro - Aluguer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1513693D-BDA5-4012-8B5E-ADAAC2E77D67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{070BA009-84AD-4AE7-B566-B0DF9EF39411}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="53">
   <si>
     <t>🏠  CASA DO MOSTEIRO — Réservations</t>
   </si>
@@ -151,9 +151,6 @@
     <t>⏳ À faire</t>
   </si>
   <si>
-    <t>Direto</t>
-  </si>
-  <si>
     <t>Tarde</t>
   </si>
   <si>
@@ -188,12 +185,6 @@
   </si>
   <si>
     <t>00351925359867</t>
-  </si>
-  <si>
-    <t>Bob</t>
-  </si>
-  <si>
-    <t>0033616081819</t>
   </si>
 </sst>
 </file>
@@ -1026,10 +1017,10 @@
         <v>🔵 À venir</v>
       </c>
       <c r="O3" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P3" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1083,10 +1074,10 @@
         <v>🔵 À venir</v>
       </c>
       <c r="O4" s="19" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="P4" s="20" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1137,13 +1128,13 @@
       </c>
       <c r="N5" s="5" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>🔵 À venir</v>
+        <v>🟡 En cours</v>
       </c>
       <c r="O5" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="P5" s="12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1197,10 +1188,10 @@
         <v>✅ Terminée</v>
       </c>
       <c r="O6" s="19" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="P6" s="20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1254,10 +1245,10 @@
         <v>✅ Terminée</v>
       </c>
       <c r="O7" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="P7" s="12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1311,10 +1302,10 @@
         <v>🔵 À venir</v>
       </c>
       <c r="O8" s="19" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="P8" s="20" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1368,10 +1359,10 @@
         <v>🔵 À venir</v>
       </c>
       <c r="O9" s="11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="P9" s="12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
@@ -1425,10 +1416,10 @@
         <v>🔵 À venir</v>
       </c>
       <c r="O10" s="19" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="P10" s="20" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
@@ -2424,33 +2415,33 @@
       <c r="D35" s="7"/>
       <c r="E35" s="7"/>
       <c r="F35" s="5" t="str">
-        <f t="shared" ref="F35:F51" si="7">IF(AND(D35&lt;&gt;"",E35&lt;&gt;""),E35-D35,"")</f>
+        <f t="shared" ref="F35:F50" si="7">IF(AND(D35&lt;&gt;"",E35&lt;&gt;""),E35-D35,"")</f>
         <v/>
       </c>
       <c r="G35" s="5"/>
       <c r="H35" s="8"/>
       <c r="I35" s="9" t="str">
-        <f t="shared" ref="I35:I51" si="8">IF(B35="Direto","",IF(B35="Airbnb",IF(H35&lt;&gt;"",H35*0.03+H35*0.03*0.2,""),IF(B35="Booking.com",IF(H35&lt;&gt;"",H35*0.15+H35*0.014,""),"")))</f>
+        <f t="shared" ref="I35:I50" si="8">IF(B35="Direto","",IF(B35="Airbnb",IF(H35&lt;&gt;"",H35*0.03+H35*0.03*0.2,""),IF(B35="Booking.com",IF(H35&lt;&gt;"",H35*0.15+H35*0.014,""),"")))</f>
         <v/>
       </c>
       <c r="J35" s="10" t="str">
-        <f t="shared" ref="J35:J51" si="9">IF(B35="Direto",IF(H35&lt;&gt;"",H35,""),IF(H35&lt;&gt;"",H35-IF(I35&lt;&gt;"",I35,0),""))</f>
+        <f t="shared" ref="J35:J50" si="9">IF(B35="Direto",IF(H35&lt;&gt;"",H35,""),IF(H35&lt;&gt;"",H35-IF(I35&lt;&gt;"",I35,0),""))</f>
         <v/>
       </c>
       <c r="K35" s="10" t="str">
-        <f t="shared" ref="K35:K51" si="10">IF(J35&lt;&gt;"",J35*0.25,"")</f>
+        <f t="shared" ref="K35:K50" si="10">IF(J35&lt;&gt;"",J35*0.25,"")</f>
         <v/>
       </c>
       <c r="L35" s="9" t="str">
-        <f t="shared" ref="L35:L51" si="11">IF(B35="Airbnb",IF(H35&lt;&gt;"",H35*0.03,""),IF(B35="Booking.com",IF(H35&lt;&gt;"",H35*0.15,""),""))</f>
+        <f t="shared" ref="L35:L50" si="11">IF(B35="Airbnb",IF(H35&lt;&gt;"",H35*0.03,""),IF(B35="Booking.com",IF(H35&lt;&gt;"",H35*0.15,""),""))</f>
         <v/>
       </c>
       <c r="M35" s="9" t="str">
-        <f t="shared" ref="M35:M51" si="12">IF(B35="Airbnb",IF(L35&lt;&gt;"",L35*0.2,""),IF(B35="Booking.com",IF(H35&lt;&gt;"",H35*0.014,""),""))</f>
+        <f t="shared" ref="M35:M50" si="12">IF(B35="Airbnb",IF(L35&lt;&gt;"",L35*0.2,""),IF(B35="Booking.com",IF(H35&lt;&gt;"",H35*0.014,""),""))</f>
         <v/>
       </c>
       <c r="N35" s="5" t="str">
-        <f t="shared" ref="N35:N51" ca="1" si="13">IF(D35="","",IF(E35&lt;TODAY(),"✅ Terminée",IF(D35&lt;=TODAY(),"🟡 En cours","🔵 À venir")))</f>
+        <f t="shared" ref="N35:N50" ca="1" si="13">IF(D35="","",IF(E35&lt;TODAY(),"✅ Terminée",IF(D35&lt;=TODAY(),"🟡 En cours","🔵 À venir")))</f>
         <v/>
       </c>
       <c r="O35" s="11"/>
@@ -3071,62 +3062,23 @@
       <c r="O50" s="19"/>
       <c r="P50" s="20"/>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A51" s="13">
-        <v>49</v>
-      </c>
-      <c r="B51" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="C51" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="D51" s="16">
-        <v>46259</v>
-      </c>
-      <c r="E51" s="16">
-        <v>46262</v>
-      </c>
-      <c r="F51" s="14">
-        <f t="shared" si="7"/>
-        <v>3</v>
-      </c>
-      <c r="G51" s="14">
-        <v>5</v>
-      </c>
-      <c r="H51" s="17">
-        <v>600</v>
-      </c>
-      <c r="I51" s="9" t="str">
-        <f>IF(B51="Direto","",IF(B51="Airbnb",IF(H51&lt;&gt;"",H51*0.03+H51*0.03*0.2,""),IF(B51="Booking.com",IF(H51&lt;&gt;"",H51*0.15+H51*0.014,""),"")))</f>
-        <v/>
-      </c>
-      <c r="J51" s="18">
-        <f t="shared" si="9"/>
-        <v>600</v>
-      </c>
-      <c r="K51" s="18">
-        <f t="shared" si="10"/>
-        <v>150</v>
-      </c>
-      <c r="L51" s="9" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="M51" s="9" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="N51" s="14" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v>🔵 À venir</v>
-      </c>
-      <c r="O51" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="P51" s="20" t="s">
-        <v>55</v>
-      </c>
+    <row r="51" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="13"/>
+      <c r="B51" s="14"/>
+      <c r="C51" s="22"/>
+      <c r="D51" s="16"/>
+      <c r="E51" s="16"/>
+      <c r="F51" s="14"/>
+      <c r="G51" s="14"/>
+      <c r="H51" s="17"/>
+      <c r="I51" s="9"/>
+      <c r="J51" s="18"/>
+      <c r="K51" s="18"/>
+      <c r="L51" s="9"/>
+      <c r="M51" s="9"/>
+      <c r="N51" s="14"/>
+      <c r="O51" s="19"/>
+      <c r="P51" s="20"/>
     </row>
     <row r="52" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="38" t="s">
@@ -3140,7 +3092,7 @@
       <c r="G52" s="38"/>
       <c r="H52" s="23">
         <f t="shared" ref="H52:M52" si="14">SUMIF(H3:H51,"&gt;0")</f>
-        <v>4034.04</v>
+        <v>3434.04</v>
       </c>
       <c r="I52" s="24">
         <f t="shared" si="14"/>
@@ -3148,11 +3100,11 @@
       </c>
       <c r="J52" s="23">
         <f t="shared" si="14"/>
-        <v>3578.3774399999998</v>
+        <v>2978.3774399999998</v>
       </c>
       <c r="K52" s="23">
         <f t="shared" si="14"/>
-        <v>894.59435999999994</v>
+        <v>744.59435999999994</v>
       </c>
       <c r="L52" s="24">
         <f t="shared" si="14"/>
@@ -3172,7 +3124,7 @@
     <row r="53" spans="1:16" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J53" s="27">
         <f>J52-K52</f>
-        <v>2683.7830799999997</v>
+        <v>2233.7830799999997</v>
       </c>
     </row>
     <row r="54" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">

--- a/Casa_do_Mosteiro_v6.xlsx
+++ b/Casa_do_Mosteiro_v6.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Patrick SALVADOR\Documents\Immobilier\Locations - Airbnb - Booking\Casa do mosteiro - Aluguer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{070BA009-84AD-4AE7-B566-B0DF9EF39411}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB956B8D-91DD-4D9A-9725-7434B5D04749}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2898,7 +2898,7 @@
       <c r="O46" s="19"/>
       <c r="P46" s="20"/>
     </row>
-    <row r="47" spans="1:16" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="4">
         <v>45</v>
       </c>
@@ -2939,7 +2939,7 @@
       <c r="O47" s="11"/>
       <c r="P47" s="12"/>
     </row>
-    <row r="48" spans="1:16" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="13">
         <v>46</v>
       </c>
@@ -2980,7 +2980,7 @@
       <c r="O48" s="19"/>
       <c r="P48" s="20"/>
     </row>
-    <row r="49" spans="1:16" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="4">
         <v>47</v>
       </c>
@@ -3021,7 +3021,7 @@
       <c r="O49" s="11"/>
       <c r="P49" s="12"/>
     </row>
-    <row r="50" spans="1:16" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="13">
         <v>48</v>
       </c>

--- a/Casa_do_Mosteiro_v6.xlsx
+++ b/Casa_do_Mosteiro_v6.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Patrick SALVADOR\Documents\Immobilier\Locations - Airbnb - Booking\Casa do mosteiro - Aluguer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB956B8D-91DD-4D9A-9725-7434B5D04749}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80F13AED-0D59-4134-814B-130816FF495D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="56">
   <si>
     <t>🏠  CASA DO MOSTEIRO — Réservations</t>
   </si>
@@ -185,6 +185,15 @@
   </si>
   <si>
     <t>00351925359867</t>
+  </si>
+  <si>
+    <t>Direto</t>
+  </si>
+  <si>
+    <t>Fernando</t>
+  </si>
+  <si>
+    <t>39325</t>
   </si>
 </sst>
 </file>
@@ -2415,33 +2424,33 @@
       <c r="D35" s="7"/>
       <c r="E35" s="7"/>
       <c r="F35" s="5" t="str">
-        <f t="shared" ref="F35:F50" si="7">IF(AND(D35&lt;&gt;"",E35&lt;&gt;""),E35-D35,"")</f>
+        <f t="shared" ref="F35:F51" si="7">IF(AND(D35&lt;&gt;"",E35&lt;&gt;""),E35-D35,"")</f>
         <v/>
       </c>
       <c r="G35" s="5"/>
       <c r="H35" s="8"/>
       <c r="I35" s="9" t="str">
-        <f t="shared" ref="I35:I50" si="8">IF(B35="Direto","",IF(B35="Airbnb",IF(H35&lt;&gt;"",H35*0.03+H35*0.03*0.2,""),IF(B35="Booking.com",IF(H35&lt;&gt;"",H35*0.15+H35*0.014,""),"")))</f>
+        <f t="shared" ref="I35:I51" si="8">IF(B35="Direto","",IF(B35="Airbnb",IF(H35&lt;&gt;"",H35*0.03+H35*0.03*0.2,""),IF(B35="Booking.com",IF(H35&lt;&gt;"",H35*0.15+H35*0.014,""),"")))</f>
         <v/>
       </c>
       <c r="J35" s="10" t="str">
-        <f t="shared" ref="J35:J50" si="9">IF(B35="Direto",IF(H35&lt;&gt;"",H35,""),IF(H35&lt;&gt;"",H35-IF(I35&lt;&gt;"",I35,0),""))</f>
+        <f t="shared" ref="J35:J51" si="9">IF(B35="Direto",IF(H35&lt;&gt;"",H35,""),IF(H35&lt;&gt;"",H35-IF(I35&lt;&gt;"",I35,0),""))</f>
         <v/>
       </c>
       <c r="K35" s="10" t="str">
-        <f t="shared" ref="K35:K50" si="10">IF(J35&lt;&gt;"",J35*0.25,"")</f>
+        <f t="shared" ref="K35:K51" si="10">IF(J35&lt;&gt;"",J35*0.25,"")</f>
         <v/>
       </c>
       <c r="L35" s="9" t="str">
-        <f t="shared" ref="L35:L50" si="11">IF(B35="Airbnb",IF(H35&lt;&gt;"",H35*0.03,""),IF(B35="Booking.com",IF(H35&lt;&gt;"",H35*0.15,""),""))</f>
+        <f t="shared" ref="L35:L51" si="11">IF(B35="Airbnb",IF(H35&lt;&gt;"",H35*0.03,""),IF(B35="Booking.com",IF(H35&lt;&gt;"",H35*0.15,""),""))</f>
         <v/>
       </c>
       <c r="M35" s="9" t="str">
-        <f t="shared" ref="M35:M50" si="12">IF(B35="Airbnb",IF(L35&lt;&gt;"",L35*0.2,""),IF(B35="Booking.com",IF(H35&lt;&gt;"",H35*0.014,""),""))</f>
+        <f t="shared" ref="M35:M51" si="12">IF(B35="Airbnb",IF(L35&lt;&gt;"",L35*0.2,""),IF(B35="Booking.com",IF(H35&lt;&gt;"",H35*0.014,""),""))</f>
         <v/>
       </c>
       <c r="N35" s="5" t="str">
-        <f t="shared" ref="N35:N50" ca="1" si="13">IF(D35="","",IF(E35&lt;TODAY(),"✅ Terminée",IF(D35&lt;=TODAY(),"🟡 En cours","🔵 À venir")))</f>
+        <f t="shared" ref="N35:N51" ca="1" si="13">IF(D35="","",IF(E35&lt;TODAY(),"✅ Terminée",IF(D35&lt;=TODAY(),"🟡 En cours","🔵 À venir")))</f>
         <v/>
       </c>
       <c r="O35" s="11"/>
@@ -3062,23 +3071,62 @@
       <c r="O50" s="19"/>
       <c r="P50" s="20"/>
     </row>
-    <row r="51" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="13"/>
-      <c r="B51" s="14"/>
-      <c r="C51" s="22"/>
-      <c r="D51" s="16"/>
-      <c r="E51" s="16"/>
-      <c r="F51" s="14"/>
-      <c r="G51" s="14"/>
-      <c r="H51" s="17"/>
-      <c r="I51" s="9"/>
-      <c r="J51" s="18"/>
-      <c r="K51" s="18"/>
-      <c r="L51" s="9"/>
-      <c r="M51" s="9"/>
-      <c r="N51" s="14"/>
-      <c r="O51" s="19"/>
-      <c r="P51" s="20"/>
+    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A51" s="13">
+        <v>9</v>
+      </c>
+      <c r="B51" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="C51" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="D51" s="16">
+        <v>46105</v>
+      </c>
+      <c r="E51" s="16">
+        <v>46109</v>
+      </c>
+      <c r="F51" s="14">
+        <f t="shared" si="7"/>
+        <v>4</v>
+      </c>
+      <c r="G51" s="14">
+        <v>2</v>
+      </c>
+      <c r="H51" s="17">
+        <v>600</v>
+      </c>
+      <c r="I51" s="9" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="J51" s="18">
+        <f t="shared" si="9"/>
+        <v>600</v>
+      </c>
+      <c r="K51" s="18">
+        <f t="shared" si="10"/>
+        <v>150</v>
+      </c>
+      <c r="L51" s="9" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="M51" s="9" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="N51" s="14" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v>🔵 À venir</v>
+      </c>
+      <c r="O51" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="P51" s="20" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="52" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="38" t="s">
@@ -3092,7 +3140,7 @@
       <c r="G52" s="38"/>
       <c r="H52" s="23">
         <f t="shared" ref="H52:M52" si="14">SUMIF(H3:H51,"&gt;0")</f>
-        <v>3434.04</v>
+        <v>4034.04</v>
       </c>
       <c r="I52" s="24">
         <f t="shared" si="14"/>
@@ -3100,11 +3148,11 @@
       </c>
       <c r="J52" s="23">
         <f t="shared" si="14"/>
-        <v>2978.3774399999998</v>
+        <v>3578.3774399999998</v>
       </c>
       <c r="K52" s="23">
         <f t="shared" si="14"/>
-        <v>744.59435999999994</v>
+        <v>894.59435999999994</v>
       </c>
       <c r="L52" s="24">
         <f t="shared" si="14"/>
@@ -3124,7 +3172,7 @@
     <row r="53" spans="1:16" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J53" s="27">
         <f>J52-K52</f>
-        <v>2233.7830799999997</v>
+        <v>2683.7830799999997</v>
       </c>
     </row>
     <row r="54" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">

--- a/Casa_do_Mosteiro_v6.xlsx
+++ b/Casa_do_Mosteiro_v6.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Patrick SALVADOR\Documents\Immobilier\Locations - Airbnb - Booking\Casa do mosteiro - Aluguer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80F13AED-0D59-4134-814B-130816FF495D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CED93ED-6B0F-4D2E-83A3-0514D6698544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="58">
   <si>
     <t>🏠  CASA DO MOSTEIRO — Réservations</t>
   </si>
@@ -194,6 +194,12 @@
   </si>
   <si>
     <t>39325</t>
+  </si>
+  <si>
+    <t>Banana</t>
+  </si>
+  <si>
+    <t>254102</t>
   </si>
 </sst>
 </file>
@@ -3030,46 +3036,62 @@
       <c r="O49" s="11"/>
       <c r="P49" s="12"/>
     </row>
-    <row r="50" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A50" s="13">
         <v>48</v>
       </c>
-      <c r="B50" s="14"/>
-      <c r="C50" s="22"/>
-      <c r="D50" s="16"/>
-      <c r="E50" s="16"/>
-      <c r="F50" s="14" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="G50" s="14"/>
-      <c r="H50" s="17"/>
+      <c r="B50" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="C50" s="22" t="s">
+        <v>56</v>
+      </c>
+      <c r="D50" s="16">
+        <v>46101</v>
+      </c>
+      <c r="E50" s="16">
+        <v>46104</v>
+      </c>
+      <c r="F50" s="14">
+        <f t="shared" ref="F50" si="14">IF(AND(D50&lt;&gt;"",E50&lt;&gt;""),E50-D50,"")</f>
+        <v>3</v>
+      </c>
+      <c r="G50" s="14">
+        <v>2</v>
+      </c>
+      <c r="H50" s="17">
+        <v>600</v>
+      </c>
       <c r="I50" s="9" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="J50" s="18" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="K50" s="18" t="str">
-        <f t="shared" si="10"/>
-        <v/>
+        <f t="shared" ref="I50" si="15">IF(B50="Direto","",IF(B50="Airbnb",IF(H50&lt;&gt;"",H50*0.03+H50*0.03*0.2,""),IF(B50="Booking.com",IF(H50&lt;&gt;"",H50*0.15+H50*0.014,""),"")))</f>
+        <v/>
+      </c>
+      <c r="J50" s="18">
+        <f t="shared" ref="J50" si="16">IF(B50="Direto",IF(H50&lt;&gt;"",H50,""),IF(H50&lt;&gt;"",H50-IF(I50&lt;&gt;"",I50,0),""))</f>
+        <v>600</v>
+      </c>
+      <c r="K50" s="18">
+        <f t="shared" ref="K50" si="17">IF(J50&lt;&gt;"",J50*0.25,"")</f>
+        <v>150</v>
       </c>
       <c r="L50" s="9" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="L50" si="18">IF(B50="Airbnb",IF(H50&lt;&gt;"",H50*0.03,""),IF(B50="Booking.com",IF(H50&lt;&gt;"",H50*0.15,""),""))</f>
         <v/>
       </c>
       <c r="M50" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" ref="M50" si="19">IF(B50="Airbnb",IF(L50&lt;&gt;"",L50*0.2,""),IF(B50="Booking.com",IF(H50&lt;&gt;"",H50*0.014,""),""))</f>
         <v/>
       </c>
       <c r="N50" s="14" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="O50" s="19"/>
-      <c r="P50" s="20"/>
+        <f t="shared" ref="N50" ca="1" si="20">IF(D50="","",IF(E50&lt;TODAY(),"✅ Terminée",IF(D50&lt;=TODAY(),"🟡 En cours","🔵 À venir")))</f>
+        <v>🔵 À venir</v>
+      </c>
+      <c r="O50" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="P50" s="20" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A51" s="13">
@@ -3139,27 +3161,27 @@
       <c r="F52" s="38"/>
       <c r="G52" s="38"/>
       <c r="H52" s="23">
-        <f t="shared" ref="H52:M52" si="14">SUMIF(H3:H51,"&gt;0")</f>
-        <v>4034.04</v>
+        <f t="shared" ref="H52:M52" si="21">SUMIF(H3:H51,"&gt;0")</f>
+        <v>4634.04</v>
       </c>
       <c r="I52" s="24">
-        <f t="shared" si="14"/>
+        <f t="shared" si="21"/>
         <v>455.66255999999998</v>
       </c>
       <c r="J52" s="23">
-        <f t="shared" si="14"/>
-        <v>3578.3774399999998</v>
+        <f t="shared" si="21"/>
+        <v>4178.3774400000002</v>
       </c>
       <c r="K52" s="23">
-        <f t="shared" si="14"/>
-        <v>894.59435999999994</v>
+        <f t="shared" si="21"/>
+        <v>1044.5943600000001</v>
       </c>
       <c r="L52" s="24">
-        <f t="shared" si="14"/>
+        <f t="shared" si="21"/>
         <v>414.30599999999998</v>
       </c>
       <c r="M52" s="24">
-        <f t="shared" si="14"/>
+        <f t="shared" si="21"/>
         <v>41.356560000000002</v>
       </c>
       <c r="N52" s="25" t="str">
@@ -3172,7 +3194,7 @@
     <row r="53" spans="1:16" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J53" s="27">
         <f>J52-K52</f>
-        <v>2683.7830799999997</v>
+        <v>3133.7830800000002</v>
       </c>
     </row>
     <row r="54" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">

--- a/Casa_do_Mosteiro_v6.xlsx
+++ b/Casa_do_Mosteiro_v6.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Patrick SALVADOR\Documents\Immobilier\Locations - Airbnb - Booking\Casa do mosteiro - Aluguer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CED93ED-6B0F-4D2E-83A3-0514D6698544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D413693-505A-4B50-AF2E-6DB96D02EAB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="53">
   <si>
     <t>🏠  CASA DO MOSTEIRO — Réservations</t>
   </si>
@@ -185,21 +185,6 @@
   </si>
   <si>
     <t>00351925359867</t>
-  </si>
-  <si>
-    <t>Direto</t>
-  </si>
-  <si>
-    <t>Fernando</t>
-  </si>
-  <si>
-    <t>39325</t>
-  </si>
-  <si>
-    <t>Banana</t>
-  </si>
-  <si>
-    <t>254102</t>
   </si>
 </sst>
 </file>
@@ -3036,119 +3021,41 @@
       <c r="O49" s="11"/>
       <c r="P49" s="12"/>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A50" s="13">
-        <v>48</v>
-      </c>
-      <c r="B50" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="C50" s="22" t="s">
-        <v>56</v>
-      </c>
-      <c r="D50" s="16">
-        <v>46101</v>
-      </c>
-      <c r="E50" s="16">
-        <v>46104</v>
-      </c>
-      <c r="F50" s="14">
-        <f t="shared" ref="F50" si="14">IF(AND(D50&lt;&gt;"",E50&lt;&gt;""),E50-D50,"")</f>
-        <v>3</v>
-      </c>
-      <c r="G50" s="14">
-        <v>2</v>
-      </c>
-      <c r="H50" s="17">
-        <v>600</v>
-      </c>
-      <c r="I50" s="9" t="str">
-        <f t="shared" ref="I50" si="15">IF(B50="Direto","",IF(B50="Airbnb",IF(H50&lt;&gt;"",H50*0.03+H50*0.03*0.2,""),IF(B50="Booking.com",IF(H50&lt;&gt;"",H50*0.15+H50*0.014,""),"")))</f>
-        <v/>
-      </c>
-      <c r="J50" s="18">
-        <f t="shared" ref="J50" si="16">IF(B50="Direto",IF(H50&lt;&gt;"",H50,""),IF(H50&lt;&gt;"",H50-IF(I50&lt;&gt;"",I50,0),""))</f>
-        <v>600</v>
-      </c>
-      <c r="K50" s="18">
-        <f t="shared" ref="K50" si="17">IF(J50&lt;&gt;"",J50*0.25,"")</f>
-        <v>150</v>
-      </c>
-      <c r="L50" s="9" t="str">
-        <f t="shared" ref="L50" si="18">IF(B50="Airbnb",IF(H50&lt;&gt;"",H50*0.03,""),IF(B50="Booking.com",IF(H50&lt;&gt;"",H50*0.15,""),""))</f>
-        <v/>
-      </c>
-      <c r="M50" s="9" t="str">
-        <f t="shared" ref="M50" si="19">IF(B50="Airbnb",IF(L50&lt;&gt;"",L50*0.2,""),IF(B50="Booking.com",IF(H50&lt;&gt;"",H50*0.014,""),""))</f>
-        <v/>
-      </c>
-      <c r="N50" s="14" t="str">
-        <f t="shared" ref="N50" ca="1" si="20">IF(D50="","",IF(E50&lt;TODAY(),"✅ Terminée",IF(D50&lt;=TODAY(),"🟡 En cours","🔵 À venir")))</f>
-        <v>🔵 À venir</v>
-      </c>
-      <c r="O50" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="P50" s="20" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A51" s="13">
-        <v>9</v>
-      </c>
-      <c r="B51" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="C51" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="D51" s="16">
-        <v>46105</v>
-      </c>
-      <c r="E51" s="16">
-        <v>46109</v>
-      </c>
-      <c r="F51" s="14">
-        <f t="shared" si="7"/>
-        <v>4</v>
-      </c>
-      <c r="G51" s="14">
-        <v>2</v>
-      </c>
-      <c r="H51" s="17">
-        <v>600</v>
-      </c>
-      <c r="I51" s="9" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="J51" s="18">
-        <f t="shared" si="9"/>
-        <v>600</v>
-      </c>
-      <c r="K51" s="18">
-        <f t="shared" si="10"/>
-        <v>150</v>
-      </c>
-      <c r="L51" s="9" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="M51" s="9" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="N51" s="14" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v>🔵 À venir</v>
-      </c>
-      <c r="O51" s="19" t="s">
-        <v>42</v>
-      </c>
-      <c r="P51" s="20" t="s">
-        <v>55</v>
-      </c>
+    <row r="50" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="13"/>
+      <c r="B50" s="14"/>
+      <c r="C50" s="22"/>
+      <c r="D50" s="16"/>
+      <c r="E50" s="16"/>
+      <c r="F50" s="14"/>
+      <c r="G50" s="14"/>
+      <c r="H50" s="17"/>
+      <c r="I50" s="9"/>
+      <c r="J50" s="18"/>
+      <c r="K50" s="18"/>
+      <c r="L50" s="9"/>
+      <c r="M50" s="9"/>
+      <c r="N50" s="14"/>
+      <c r="O50" s="19"/>
+      <c r="P50" s="20"/>
+    </row>
+    <row r="51" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="13"/>
+      <c r="B51" s="14"/>
+      <c r="C51" s="22"/>
+      <c r="D51" s="16"/>
+      <c r="E51" s="16"/>
+      <c r="F51" s="14"/>
+      <c r="G51" s="14"/>
+      <c r="H51" s="17"/>
+      <c r="I51" s="9"/>
+      <c r="J51" s="18"/>
+      <c r="K51" s="18"/>
+      <c r="L51" s="9"/>
+      <c r="M51" s="9"/>
+      <c r="N51" s="14"/>
+      <c r="O51" s="19"/>
+      <c r="P51" s="20"/>
     </row>
     <row r="52" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="38" t="s">
@@ -3161,27 +3068,27 @@
       <c r="F52" s="38"/>
       <c r="G52" s="38"/>
       <c r="H52" s="23">
-        <f t="shared" ref="H52:M52" si="21">SUMIF(H3:H51,"&gt;0")</f>
-        <v>4634.04</v>
+        <f t="shared" ref="H52:M52" si="14">SUMIF(H3:H51,"&gt;0")</f>
+        <v>3434.04</v>
       </c>
       <c r="I52" s="24">
-        <f t="shared" si="21"/>
+        <f t="shared" si="14"/>
         <v>455.66255999999998</v>
       </c>
       <c r="J52" s="23">
-        <f t="shared" si="21"/>
-        <v>4178.3774400000002</v>
+        <f t="shared" si="14"/>
+        <v>2978.3774399999998</v>
       </c>
       <c r="K52" s="23">
-        <f t="shared" si="21"/>
-        <v>1044.5943600000001</v>
+        <f t="shared" si="14"/>
+        <v>744.59435999999994</v>
       </c>
       <c r="L52" s="24">
-        <f t="shared" si="21"/>
+        <f t="shared" si="14"/>
         <v>414.30599999999998</v>
       </c>
       <c r="M52" s="24">
-        <f t="shared" si="21"/>
+        <f t="shared" si="14"/>
         <v>41.356560000000002</v>
       </c>
       <c r="N52" s="25" t="str">
@@ -3194,7 +3101,7 @@
     <row r="53" spans="1:16" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J53" s="27">
         <f>J52-K52</f>
-        <v>3133.7830800000002</v>
+        <v>2233.7830799999997</v>
       </c>
     </row>
     <row r="54" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">

--- a/Casa_do_Mosteiro_v6.xlsx
+++ b/Casa_do_Mosteiro_v6.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Patrick SALVADOR\Documents\Immobilier\Locations - Airbnb - Booking\Casa do mosteiro - Aluguer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D413693-505A-4B50-AF2E-6DB96D02EAB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91BD6D92-36B6-4DDD-B5E8-AA592812C516}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="📋 Réservations" sheetId="1" r:id="rId1"/>
     <sheet name="📓 Bloc-notes" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="55">
   <si>
     <t>🏠  CASA DO MOSTEIRO — Réservations</t>
   </si>
@@ -106,9 +106,6 @@
     <t>Rubén Rivas lópez</t>
   </si>
   <si>
-    <t>Rui Semanas</t>
-  </si>
-  <si>
     <t>TOTAUX</t>
   </si>
   <si>
@@ -184,7 +181,16 @@
     <t>0034662673619</t>
   </si>
   <si>
-    <t>00351925359867</t>
+    <t>Barbara Gama</t>
+  </si>
+  <si>
+    <t>00351962553779</t>
+  </si>
+  <si>
+    <t>Direto</t>
+  </si>
+  <si>
+    <t>X</t>
   </si>
 </sst>
 </file>
@@ -195,7 +201,7 @@
     <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
     <numFmt numFmtId="165" formatCode="#,##0.00&quot; €&quot;"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -284,8 +290,15 @@
       <name val="Arial"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -343,6 +356,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFBF0"/>
+        <bgColor rgb="FFFDFAF6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor rgb="FFFDFAF6"/>
       </patternFill>
     </fill>
@@ -477,7 +496,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -584,6 +603,9 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="11" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -897,24 +919,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="37"/>
-      <c r="M1" s="37"/>
-      <c r="N1" s="37"/>
-      <c r="O1" s="37"/>
-      <c r="P1" s="37"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="38"/>
+      <c r="K1" s="38"/>
+      <c r="L1" s="38"/>
+      <c r="M1" s="38"/>
+      <c r="N1" s="38"/>
+      <c r="O1" s="38"/>
+      <c r="P1" s="38"/>
     </row>
     <row r="2" spans="1:16" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1017,10 +1039,10 @@
         <v>🔵 À venir</v>
       </c>
       <c r="O3" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="P3" s="12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1053,13 +1075,12 @@
         <f t="shared" si="1"/>
         <v>10.8</v>
       </c>
-      <c r="J4" s="18">
-        <f t="shared" si="2"/>
-        <v>289.2</v>
+      <c r="J4" s="37">
+        <v>231.36</v>
       </c>
       <c r="K4" s="18">
         <f t="shared" si="3"/>
-        <v>72.3</v>
+        <v>57.84</v>
       </c>
       <c r="L4" s="9">
         <f t="shared" si="4"/>
@@ -1074,10 +1095,10 @@
         <v>🔵 À venir</v>
       </c>
       <c r="O4" s="19" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P4" s="20" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1128,13 +1149,13 @@
       </c>
       <c r="N5" s="5" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>🟡 En cours</v>
+        <v>✅ Terminée</v>
       </c>
       <c r="O5" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="P5" s="12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1188,10 +1209,10 @@
         <v>✅ Terminée</v>
       </c>
       <c r="O6" s="19" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P6" s="20" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1245,10 +1266,10 @@
         <v>✅ Terminée</v>
       </c>
       <c r="O7" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="P7" s="12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1302,10 +1323,10 @@
         <v>🔵 À venir</v>
       </c>
       <c r="O8" s="19" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P8" s="20" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1359,10 +1380,10 @@
         <v>🔵 À venir</v>
       </c>
       <c r="O9" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="P9" s="12" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
@@ -1373,50 +1394,50 @@
         <v>20</v>
       </c>
       <c r="C10" s="22" t="s">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="D10" s="16">
-        <v>46237</v>
+        <v>46185</v>
       </c>
       <c r="E10" s="16">
-        <v>46241</v>
+        <v>46187</v>
       </c>
       <c r="F10" s="14">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G10" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H10" s="17">
-        <v>600</v>
+        <v>270</v>
       </c>
       <c r="I10" s="9">
         <f t="shared" si="1"/>
-        <v>98.4</v>
+        <v>44.28</v>
       </c>
       <c r="J10" s="18">
         <f t="shared" si="2"/>
-        <v>501.6</v>
+        <v>225.72</v>
       </c>
       <c r="K10" s="18">
         <f t="shared" si="3"/>
-        <v>125.4</v>
+        <v>56.43</v>
       </c>
       <c r="L10" s="9">
         <f t="shared" si="4"/>
-        <v>90</v>
+        <v>40.5</v>
       </c>
       <c r="M10" s="9">
         <f t="shared" si="5"/>
-        <v>8.4</v>
+        <v>3.7800000000000002</v>
       </c>
       <c r="N10" s="14" t="str">
         <f t="shared" ca="1" si="6"/>
         <v>🔵 À venir</v>
       </c>
       <c r="O10" s="19" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P10" s="20" t="s">
         <v>52</v>
@@ -2415,33 +2436,33 @@
       <c r="D35" s="7"/>
       <c r="E35" s="7"/>
       <c r="F35" s="5" t="str">
-        <f t="shared" ref="F35:F51" si="7">IF(AND(D35&lt;&gt;"",E35&lt;&gt;""),E35-D35,"")</f>
+        <f t="shared" ref="F35:F49" si="7">IF(AND(D35&lt;&gt;"",E35&lt;&gt;""),E35-D35,"")</f>
         <v/>
       </c>
       <c r="G35" s="5"/>
       <c r="H35" s="8"/>
       <c r="I35" s="9" t="str">
-        <f t="shared" ref="I35:I51" si="8">IF(B35="Direto","",IF(B35="Airbnb",IF(H35&lt;&gt;"",H35*0.03+H35*0.03*0.2,""),IF(B35="Booking.com",IF(H35&lt;&gt;"",H35*0.15+H35*0.014,""),"")))</f>
+        <f t="shared" ref="I35:I49" si="8">IF(B35="Direto","",IF(B35="Airbnb",IF(H35&lt;&gt;"",H35*0.03+H35*0.03*0.2,""),IF(B35="Booking.com",IF(H35&lt;&gt;"",H35*0.15+H35*0.014,""),"")))</f>
         <v/>
       </c>
       <c r="J35" s="10" t="str">
-        <f t="shared" ref="J35:J51" si="9">IF(B35="Direto",IF(H35&lt;&gt;"",H35,""),IF(H35&lt;&gt;"",H35-IF(I35&lt;&gt;"",I35,0),""))</f>
+        <f t="shared" ref="J35:J49" si="9">IF(B35="Direto",IF(H35&lt;&gt;"",H35,""),IF(H35&lt;&gt;"",H35-IF(I35&lt;&gt;"",I35,0),""))</f>
         <v/>
       </c>
       <c r="K35" s="10" t="str">
-        <f t="shared" ref="K35:K51" si="10">IF(J35&lt;&gt;"",J35*0.25,"")</f>
+        <f t="shared" ref="K35:K49" si="10">IF(J35&lt;&gt;"",J35*0.25,"")</f>
         <v/>
       </c>
       <c r="L35" s="9" t="str">
-        <f t="shared" ref="L35:L51" si="11">IF(B35="Airbnb",IF(H35&lt;&gt;"",H35*0.03,""),IF(B35="Booking.com",IF(H35&lt;&gt;"",H35*0.15,""),""))</f>
+        <f t="shared" ref="L35:L49" si="11">IF(B35="Airbnb",IF(H35&lt;&gt;"",H35*0.03,""),IF(B35="Booking.com",IF(H35&lt;&gt;"",H35*0.15,""),""))</f>
         <v/>
       </c>
       <c r="M35" s="9" t="str">
-        <f t="shared" ref="M35:M51" si="12">IF(B35="Airbnb",IF(L35&lt;&gt;"",L35*0.2,""),IF(B35="Booking.com",IF(H35&lt;&gt;"",H35*0.014,""),""))</f>
+        <f t="shared" ref="M35:M49" si="12">IF(B35="Airbnb",IF(L35&lt;&gt;"",L35*0.2,""),IF(B35="Booking.com",IF(H35&lt;&gt;"",H35*0.014,""),""))</f>
         <v/>
       </c>
       <c r="N35" s="5" t="str">
-        <f t="shared" ref="N35:N51" ca="1" si="13">IF(D35="","",IF(E35&lt;TODAY(),"✅ Terminée",IF(D35&lt;=TODAY(),"🟡 En cours","🔵 À venir")))</f>
+        <f t="shared" ref="N35:N49" ca="1" si="13">IF(D35="","",IF(E35&lt;TODAY(),"✅ Terminée",IF(D35&lt;=TODAY(),"🟡 En cours","🔵 À venir")))</f>
         <v/>
       </c>
       <c r="O35" s="11"/>
@@ -3039,61 +3060,100 @@
       <c r="O50" s="19"/>
       <c r="P50" s="20"/>
     </row>
-    <row r="51" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="13"/>
-      <c r="B51" s="14"/>
-      <c r="C51" s="22"/>
-      <c r="D51" s="16"/>
-      <c r="E51" s="16"/>
-      <c r="F51" s="14"/>
-      <c r="G51" s="14"/>
-      <c r="H51" s="17"/>
-      <c r="I51" s="9"/>
-      <c r="J51" s="18"/>
-      <c r="K51" s="18"/>
-      <c r="L51" s="9"/>
-      <c r="M51" s="9"/>
-      <c r="N51" s="14"/>
-      <c r="O51" s="19"/>
-      <c r="P51" s="20"/>
+    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A51" s="13">
+        <v>9</v>
+      </c>
+      <c r="B51" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="C51" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="D51" s="16">
+        <v>46143</v>
+      </c>
+      <c r="E51" s="16">
+        <v>46144</v>
+      </c>
+      <c r="F51" s="14">
+        <f t="shared" ref="F51" si="14">IF(AND(D51&lt;&gt;"",E51&lt;&gt;""),E51-D51,"")</f>
+        <v>1</v>
+      </c>
+      <c r="G51" s="14">
+        <v>3</v>
+      </c>
+      <c r="H51" s="17">
+        <v>130</v>
+      </c>
+      <c r="I51" s="9" t="str">
+        <f t="shared" ref="I51" si="15">IF(B51="Direto","",IF(B51="Airbnb",IF(H51&lt;&gt;"",H51*0.03+H51*0.03*0.2,""),IF(B51="Booking.com",IF(H51&lt;&gt;"",H51*0.15+H51*0.014,""),"")))</f>
+        <v/>
+      </c>
+      <c r="J51" s="18">
+        <f t="shared" ref="J51" si="16">IF(B51="Direto",IF(H51&lt;&gt;"",H51,""),IF(H51&lt;&gt;"",H51-IF(I51&lt;&gt;"",I51,0),""))</f>
+        <v>130</v>
+      </c>
+      <c r="K51" s="18">
+        <f t="shared" ref="K51" si="17">IF(J51&lt;&gt;"",J51*0.25,"")</f>
+        <v>32.5</v>
+      </c>
+      <c r="L51" s="9" t="str">
+        <f t="shared" ref="L51" si="18">IF(B51="Airbnb",IF(H51&lt;&gt;"",H51*0.03,""),IF(B51="Booking.com",IF(H51&lt;&gt;"",H51*0.15,""),""))</f>
+        <v/>
+      </c>
+      <c r="M51" s="9" t="str">
+        <f t="shared" ref="M51" si="19">IF(B51="Airbnb",IF(L51&lt;&gt;"",L51*0.2,""),IF(B51="Booking.com",IF(H51&lt;&gt;"",H51*0.014,""),""))</f>
+        <v/>
+      </c>
+      <c r="N51" s="14" t="str">
+        <f t="shared" ref="N51" ca="1" si="20">IF(D51="","",IF(E51&lt;TODAY(),"✅ Terminée",IF(D51&lt;=TODAY(),"🟡 En cours","🔵 À venir")))</f>
+        <v>🔵 À venir</v>
+      </c>
+      <c r="O51" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="P51" s="20" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="52" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="38" t="s">
-        <v>27</v>
-      </c>
-      <c r="B52" s="38"/>
-      <c r="C52" s="38"/>
-      <c r="D52" s="38"/>
-      <c r="E52" s="38"/>
-      <c r="F52" s="38"/>
-      <c r="G52" s="38"/>
+      <c r="A52" s="39" t="s">
+        <v>26</v>
+      </c>
+      <c r="B52" s="39"/>
+      <c r="C52" s="39"/>
+      <c r="D52" s="39"/>
+      <c r="E52" s="39"/>
+      <c r="F52" s="39"/>
+      <c r="G52" s="39"/>
       <c r="H52" s="23">
-        <f t="shared" ref="H52:M52" si="14">SUMIF(H3:H51,"&gt;0")</f>
-        <v>3434.04</v>
+        <f t="shared" ref="H52:M52" si="21">SUMIF(H3:H51,"&gt;0")</f>
+        <v>3234.04</v>
       </c>
       <c r="I52" s="24">
-        <f t="shared" si="14"/>
-        <v>455.66255999999998</v>
+        <f t="shared" si="21"/>
+        <v>401.54255999999998</v>
       </c>
       <c r="J52" s="23">
-        <f t="shared" si="14"/>
-        <v>2978.3774399999998</v>
+        <f t="shared" si="21"/>
+        <v>2774.6574399999995</v>
       </c>
       <c r="K52" s="23">
-        <f t="shared" si="14"/>
-        <v>744.59435999999994</v>
+        <f t="shared" si="21"/>
+        <v>693.66435999999987</v>
       </c>
       <c r="L52" s="24">
-        <f t="shared" si="14"/>
-        <v>414.30599999999998</v>
+        <f t="shared" si="21"/>
+        <v>364.80599999999998</v>
       </c>
       <c r="M52" s="24">
-        <f t="shared" si="14"/>
-        <v>41.356560000000002</v>
+        <f t="shared" si="21"/>
+        <v>36.736560000000004</v>
       </c>
       <c r="N52" s="25" t="str">
         <f ca="1">COUNTIF(N3:N10,"✅ Terminée")&amp;" terminée(s)"</f>
-        <v>2 terminée(s)</v>
+        <v>3 terminée(s)</v>
       </c>
       <c r="O52" s="26"/>
       <c r="P52" s="26"/>
@@ -3101,28 +3161,28 @@
     <row r="53" spans="1:16" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J53" s="27">
         <f>J52-K52</f>
-        <v>2233.7830799999997</v>
+        <v>2080.9930799999997</v>
       </c>
     </row>
     <row r="54" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="39" t="s">
-        <v>28</v>
-      </c>
-      <c r="B54" s="39"/>
-      <c r="C54" s="39"/>
-      <c r="D54" s="39"/>
-      <c r="E54" s="39"/>
-      <c r="F54" s="39"/>
-      <c r="G54" s="39"/>
-      <c r="H54" s="39"/>
-      <c r="I54" s="39"/>
-      <c r="J54" s="39"/>
-      <c r="K54" s="39"/>
-      <c r="L54" s="39"/>
-      <c r="M54" s="39"/>
-      <c r="N54" s="39"/>
-      <c r="O54" s="39"/>
-      <c r="P54" s="39"/>
+      <c r="A54" s="40" t="s">
+        <v>27</v>
+      </c>
+      <c r="B54" s="40"/>
+      <c r="C54" s="40"/>
+      <c r="D54" s="40"/>
+      <c r="E54" s="40"/>
+      <c r="F54" s="40"/>
+      <c r="G54" s="40"/>
+      <c r="H54" s="40"/>
+      <c r="I54" s="40"/>
+      <c r="J54" s="40"/>
+      <c r="K54" s="40"/>
+      <c r="L54" s="40"/>
+      <c r="M54" s="40"/>
+      <c r="N54" s="40"/>
+      <c r="O54" s="40"/>
+      <c r="P54" s="40"/>
     </row>
     <row r="55" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
@@ -3169,51 +3229,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="40" t="s">
-        <v>29</v>
-      </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
+      <c r="A1" s="41" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
     </row>
     <row r="2" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="28" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="28" t="s">
+      <c r="C2" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="28" t="s">
+      <c r="D2" s="28" t="s">
         <v>32</v>
-      </c>
-      <c r="D2" s="28" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="B3" s="30" t="s">
+      <c r="C3" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="30" t="s">
+      <c r="D3" s="30" t="s">
         <v>36</v>
-      </c>
-      <c r="D3" s="30" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="31"/>
       <c r="B4" s="32" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="C4" s="32" t="s">
+      <c r="D4" s="32" t="s">
         <v>39</v>
-      </c>
-      <c r="D4" s="32" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">

--- a/Casa_do_Mosteiro_v6.xlsx
+++ b/Casa_do_Mosteiro_v6.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91BD6D92-36B6-4DDD-B5E8-AA592812C516}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3075" yWindow="3075" windowWidth="21600" windowHeight="11295" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="📋 Réservations" sheetId="1" r:id="rId1"/>

--- a/Casa_do_Mosteiro_v6.xlsx
+++ b/Casa_do_Mosteiro_v6.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Patrick SALVADOR\Documents\Immobilier\Locations - Airbnb - Booking\Casa do mosteiro - Aluguer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91BD6D92-36B6-4DDD-B5E8-AA592812C516}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A39AB832-5E40-4D9C-BCBE-D298A4767FF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3075" yWindow="3075" windowWidth="21600" windowHeight="11295" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="📋 Réservations" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="58">
   <si>
     <t>🏠  CASA DO MOSTEIRO — Réservations</t>
   </si>
@@ -191,6 +191,15 @@
   </si>
   <si>
     <t>X</t>
+  </si>
+  <si>
+    <t>Abritel</t>
+  </si>
+  <si>
+    <t>Bruno Sousa</t>
+  </si>
+  <si>
+    <t>0623755787</t>
   </si>
 </sst>
 </file>
@@ -1036,7 +1045,7 @@
       </c>
       <c r="N3" s="5" t="str">
         <f t="shared" ref="N3:N34" ca="1" si="6">IF(D3="","",IF(E3&lt;TODAY(),"✅ Terminée",IF(D3&lt;=TODAY(),"🟡 En cours","🔵 À venir")))</f>
-        <v>🔵 À venir</v>
+        <v>🟡 En cours</v>
       </c>
       <c r="O3" s="11" t="s">
         <v>40</v>
@@ -1323,7 +1332,7 @@
         <v>🔵 À venir</v>
       </c>
       <c r="O8" s="19" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="P8" s="20" t="s">
         <v>49</v>
@@ -2436,7 +2445,7 @@
       <c r="D35" s="7"/>
       <c r="E35" s="7"/>
       <c r="F35" s="5" t="str">
-        <f t="shared" ref="F35:F49" si="7">IF(AND(D35&lt;&gt;"",E35&lt;&gt;""),E35-D35,"")</f>
+        <f t="shared" ref="F35:F50" si="7">IF(AND(D35&lt;&gt;"",E35&lt;&gt;""),E35-D35,"")</f>
         <v/>
       </c>
       <c r="G35" s="5"/>
@@ -2450,7 +2459,7 @@
         <v/>
       </c>
       <c r="K35" s="10" t="str">
-        <f t="shared" ref="K35:K49" si="10">IF(J35&lt;&gt;"",J35*0.25,"")</f>
+        <f t="shared" ref="K35:K50" si="10">IF(J35&lt;&gt;"",J35*0.25,"")</f>
         <v/>
       </c>
       <c r="L35" s="9" t="str">
@@ -2462,7 +2471,7 @@
         <v/>
       </c>
       <c r="N35" s="5" t="str">
-        <f t="shared" ref="N35:N49" ca="1" si="13">IF(D35="","",IF(E35&lt;TODAY(),"✅ Terminée",IF(D35&lt;=TODAY(),"🟡 En cours","🔵 À venir")))</f>
+        <f t="shared" ref="N35:N50" ca="1" si="13">IF(D35="","",IF(E35&lt;TODAY(),"✅ Terminée",IF(D35&lt;=TODAY(),"🟡 En cours","🔵 À venir")))</f>
         <v/>
       </c>
       <c r="O35" s="11"/>
@@ -3042,27 +3051,56 @@
       <c r="O49" s="11"/>
       <c r="P49" s="12"/>
     </row>
-    <row r="50" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="13"/>
-      <c r="B50" s="14"/>
-      <c r="C50" s="22"/>
-      <c r="D50" s="16"/>
-      <c r="E50" s="16"/>
-      <c r="F50" s="14"/>
-      <c r="G50" s="14"/>
-      <c r="H50" s="17"/>
+    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A50" s="13">
+        <v>9</v>
+      </c>
+      <c r="B50" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="C50" s="22" t="s">
+        <v>56</v>
+      </c>
+      <c r="D50" s="16">
+        <v>46175</v>
+      </c>
+      <c r="E50" s="16">
+        <v>46178</v>
+      </c>
+      <c r="F50" s="14">
+        <f t="shared" si="7"/>
+        <v>3</v>
+      </c>
+      <c r="G50" s="14">
+        <v>5</v>
+      </c>
+      <c r="H50" s="17">
+        <v>364.5</v>
+      </c>
       <c r="I50" s="9"/>
-      <c r="J50" s="18"/>
-      <c r="K50" s="18"/>
+      <c r="J50" s="18">
+        <v>328.67</v>
+      </c>
+      <c r="K50" s="18">
+        <f t="shared" si="10"/>
+        <v>82.167500000000004</v>
+      </c>
       <c r="L50" s="9"/>
       <c r="M50" s="9"/>
-      <c r="N50" s="14"/>
-      <c r="O50" s="19"/>
-      <c r="P50" s="20"/>
+      <c r="N50" s="14" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v>🔵 À venir</v>
+      </c>
+      <c r="O50" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="P50" s="20" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A51" s="13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B51" s="14" t="s">
         <v>53</v>
@@ -3129,7 +3167,7 @@
       <c r="G52" s="39"/>
       <c r="H52" s="23">
         <f t="shared" ref="H52:M52" si="21">SUMIF(H3:H51,"&gt;0")</f>
-        <v>3234.04</v>
+        <v>3598.54</v>
       </c>
       <c r="I52" s="24">
         <f t="shared" si="21"/>
@@ -3137,11 +3175,11 @@
       </c>
       <c r="J52" s="23">
         <f t="shared" si="21"/>
-        <v>2774.6574399999995</v>
+        <v>3103.3274399999996</v>
       </c>
       <c r="K52" s="23">
         <f t="shared" si="21"/>
-        <v>693.66435999999987</v>
+        <v>775.83185999999989</v>
       </c>
       <c r="L52" s="24">
         <f t="shared" si="21"/>
@@ -3161,7 +3199,7 @@
     <row r="53" spans="1:16" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J53" s="27">
         <f>J52-K52</f>
-        <v>2080.9930799999997</v>
+        <v>2327.4955799999998</v>
       </c>
     </row>
     <row r="54" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">

--- a/Casa_do_Mosteiro_v6.xlsx
+++ b/Casa_do_Mosteiro_v6.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Patrick SALVADOR\Documents\Immobilier\Locations - Airbnb - Booking\Casa do mosteiro - Aluguer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A39AB832-5E40-4D9C-BCBE-D298A4767FF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AE64396-3160-4EB3-A9E2-682788976357}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="64">
   <si>
     <t>🏠  CASA DO MOSTEIRO — Réservations</t>
   </si>
@@ -200,6 +200,24 @@
   </si>
   <si>
     <t>0623755787</t>
+  </si>
+  <si>
+    <t>Ana Isabel Bechaud</t>
+  </si>
+  <si>
+    <t>0619814951</t>
+  </si>
+  <si>
+    <t>Juan Neira Conde</t>
+  </si>
+  <si>
+    <t>0034675633865</t>
+  </si>
+  <si>
+    <t>Dulce Morais</t>
+  </si>
+  <si>
+    <t>00351936282687</t>
   </si>
 </sst>
 </file>
@@ -616,10 +634,10 @@
     <xf numFmtId="165" fontId="13" fillId="11" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -630,7 +648,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="13">
     <dxf>
       <fill>
         <patternFill>
@@ -644,6 +662,458 @@
           <bgColor theme="3" tint="0.79989013336588644"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFDFAF6"/>
+          <bgColor rgb="FFF8F3EE"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFCCCCCC"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFCCCCCC"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFCCCCCC"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFCCCCCC"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFDFAF6"/>
+          <bgColor rgb="FFF8F3EE"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFCCCCCC"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFCCCCCC"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFCCCCCC"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFCCCCCC"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFDFAF6"/>
+          <bgColor rgb="FFF8F3EE"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFCCCCCC"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFCCCCCC"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFCCCCCC"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFCCCCCC"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF888888"/>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="#,##0.00&quot; €&quot;"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFCCCCCC"/>
+          <bgColor rgb="FFD9D9D9"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFBBBBBB"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFBBBBBB"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFBBBBBB"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFBBBBBB"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF888888"/>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="#,##0.00&quot; €&quot;"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFCCCCCC"/>
+          <bgColor rgb="FFD9D9D9"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFBBBBBB"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFBBBBBB"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFBBBBBB"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFBBBBBB"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="#,##0.00&quot; €&quot;"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFDFAF6"/>
+          <bgColor rgb="FFF8F3EE"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFCCCCCC"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFCCCCCC"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFCCCCCC"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFCCCCCC"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="#,##0.00&quot; €&quot;"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFDFAF6"/>
+          <bgColor rgb="FFF8F3EE"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFCCCCCC"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFCCCCCC"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFCCCCCC"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFCCCCCC"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF888888"/>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="#,##0.00&quot; €&quot;"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFCCCCCC"/>
+          <bgColor rgb="FFD9D9D9"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFBBBBBB"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFBBBBBB"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFBBBBBB"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFBBBBBB"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="#,##0.00&quot; €&quot;"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFDFAF6"/>
+          <bgColor rgb="FFF8F3EE"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFCCCCCC"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFCCCCCC"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFCCCCCC"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFCCCCCC"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFDFAF6"/>
+          <bgColor rgb="FFF8F3EE"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFCCCCCC"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFCCCCCC"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFCCCCCC"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFCCCCCC"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FFFDFAF6"/>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFA85A3A"/>
+          <bgColor rgb="FFC2714F"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FFA85A3A"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFA85A3A"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -724,6 +1194,31 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F2313CAB-7AD2-4EDB-930F-5D65625B6D2B}" name="Tableau1" displayName="Tableau1" ref="A2:P51" totalsRowShown="0" headerRowDxfId="12">
+  <autoFilter ref="A2:P51" xr:uid="{F2313CAB-7AD2-4EDB-930F-5D65625B6D2B}"/>
+  <tableColumns count="16">
+    <tableColumn id="1" xr3:uid="{AC60970B-A2FC-4DDF-A9CC-349A2480743F}" name="N°"/>
+    <tableColumn id="2" xr3:uid="{D1C29AA2-7371-49D7-A3A3-4422D13F1388}" name="Plateforme"/>
+    <tableColumn id="3" xr3:uid="{B122446C-E3FE-40E2-87A7-AB4899728B1C}" name="Voyageur"/>
+    <tableColumn id="4" xr3:uid="{97208B29-BAB5-42E9-B831-9D4590177054}" name="Arrivée"/>
+    <tableColumn id="5" xr3:uid="{D3FE3381-C4B8-498F-A625-9962CB8A6588}" name="Départ"/>
+    <tableColumn id="6" xr3:uid="{597E1DA1-8BEB-4388-9DEE-46070032A16C}" name="Nuits" dataDxfId="11"/>
+    <tableColumn id="7" xr3:uid="{FB4B88CE-AF8F-4750-B8B0-B7F7393E68C9}" name="Personnes"/>
+    <tableColumn id="8" xr3:uid="{5D9F9F94-AD5D-4170-9B0D-1889D7F3F70D}" name="Prix brut (€)" dataDxfId="10"/>
+    <tableColumn id="9" xr3:uid="{E2297A44-4273-4BA7-878E-97F599090065}" name="Frais plate. (€) 🔒" dataDxfId="9"/>
+    <tableColumn id="10" xr3:uid="{CFAAEAA3-2982-40AF-B875-EE881355E43E}" name="Net reçu (€)" dataDxfId="8"/>
+    <tableColumn id="11" xr3:uid="{B8A370C8-5D57-48C1-8BE6-3A2B5ACFB5DD}" name="Gloria 25% (€)" dataDxfId="7"/>
+    <tableColumn id="12" xr3:uid="{596F80C5-7E4A-4CD8-9C07-871967C53D6A}" name="Commission (€) 🔒" dataDxfId="6"/>
+    <tableColumn id="13" xr3:uid="{EB1AD7D4-C5F7-417D-9953-52A1CF811051}" name="TVA / Fr.banc. (€) 🔒" dataDxfId="5"/>
+    <tableColumn id="14" xr3:uid="{DE0D1F8C-57FF-492D-BFE6-FE4E7A8BEABC}" name="Statut" dataDxfId="4"/>
+    <tableColumn id="15" xr3:uid="{8C802233-1B0A-46BB-A281-14B1BE490844}" name="Hora de chegada" dataDxfId="3"/>
+    <tableColumn id="16" xr3:uid="{0737B9E8-1278-4EF0-9A9B-3B9B8DE56851}" name="Telefone" dataDxfId="2"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -908,7 +1403,7 @@
   <sheetPr>
     <tabColor rgb="FFC2714F"/>
   </sheetPr>
-  <dimension ref="A1:P55"/>
+  <dimension ref="A1:P54"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -916,36 +1411,37 @@
     <col min="3" max="3" width="22" customWidth="1"/>
     <col min="4" max="5" width="13" customWidth="1"/>
     <col min="6" max="6" width="8" customWidth="1"/>
-    <col min="7" max="7" width="11.7109375" customWidth="1"/>
+    <col min="7" max="7" width="12.42578125" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="15" customWidth="1"/>
+    <col min="9" max="9" width="17.140625" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
     <col min="11" max="11" width="16" customWidth="1"/>
-    <col min="12" max="12" width="15.85546875" customWidth="1"/>
-    <col min="13" max="14" width="14" customWidth="1"/>
-    <col min="15" max="15" width="17" customWidth="1"/>
+    <col min="12" max="12" width="18.42578125" customWidth="1"/>
+    <col min="13" max="13" width="19.28515625" customWidth="1"/>
+    <col min="14" max="14" width="14" customWidth="1"/>
+    <col min="15" max="15" width="18.5703125" customWidth="1"/>
     <col min="16" max="16" width="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
-      <c r="J1" s="38"/>
-      <c r="K1" s="38"/>
-      <c r="L1" s="38"/>
-      <c r="M1" s="38"/>
-      <c r="N1" s="38"/>
-      <c r="O1" s="38"/>
-      <c r="P1" s="38"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
+      <c r="I1" s="39"/>
+      <c r="J1" s="39"/>
+      <c r="K1" s="39"/>
+      <c r="L1" s="39"/>
+      <c r="M1" s="39"/>
+      <c r="N1" s="39"/>
+      <c r="O1" s="39"/>
+      <c r="P1" s="39"/>
     </row>
     <row r="2" spans="1:16" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1014,7 +1510,7 @@
         <v>46118</v>
       </c>
       <c r="F3" s="5">
-        <f t="shared" ref="F3:F34" si="0">IF(AND(D3&lt;&gt;"",E3&lt;&gt;""),E3-D3,"")</f>
+        <f t="shared" ref="F3:F35" si="0">IF(AND(D3&lt;&gt;"",E3&lt;&gt;""),E3-D3,"")</f>
         <v>4</v>
       </c>
       <c r="G3" s="5">
@@ -1024,28 +1520,28 @@
         <v>540</v>
       </c>
       <c r="I3" s="9">
-        <f t="shared" ref="I3:I34" si="1">IF(B3="Direto","",IF(B3="Airbnb",IF(H3&lt;&gt;"",H3*0.03+H3*0.03*0.2,""),IF(B3="Booking.com",IF(H3&lt;&gt;"",H3*0.15+H3*0.014,""),"")))</f>
+        <f t="shared" ref="I3:I35" si="1">IF(B3="Direto","",IF(B3="Airbnb",IF(H3&lt;&gt;"",H3*0.03+H3*0.03*0.2,""),IF(B3="Booking.com",IF(H3&lt;&gt;"",H3*0.15+H3*0.014,""),"")))</f>
         <v>19.439999999999998</v>
       </c>
       <c r="J3" s="10">
-        <f t="shared" ref="J3:J34" si="2">IF(B3="Direto",IF(H3&lt;&gt;"",H3,""),IF(H3&lt;&gt;"",H3-IF(I3&lt;&gt;"",I3,0),""))</f>
+        <f t="shared" ref="J3:J35" si="2">IF(B3="Direto",IF(H3&lt;&gt;"",H3,""),IF(H3&lt;&gt;"",H3-IF(I3&lt;&gt;"",I3,0),""))</f>
         <v>520.55999999999995</v>
       </c>
       <c r="K3" s="10">
-        <f t="shared" ref="K3:K34" si="3">IF(J3&lt;&gt;"",J3*0.25,"")</f>
+        <f t="shared" ref="K3:K35" si="3">IF(J3&lt;&gt;"",J3*0.25,"")</f>
         <v>130.13999999999999</v>
       </c>
       <c r="L3" s="9">
-        <f t="shared" ref="L3:L34" si="4">IF(B3="Airbnb",IF(H3&lt;&gt;"",H3*0.03,""),IF(B3="Booking.com",IF(H3&lt;&gt;"",H3*0.15,""),""))</f>
+        <f t="shared" ref="L3:L35" si="4">IF(B3="Airbnb",IF(H3&lt;&gt;"",H3*0.03,""),IF(B3="Booking.com",IF(H3&lt;&gt;"",H3*0.15,""),""))</f>
         <v>16.2</v>
       </c>
       <c r="M3" s="9">
-        <f t="shared" ref="M3:M34" si="5">IF(B3="Airbnb",IF(L3&lt;&gt;"",L3*0.2,""),IF(B3="Booking.com",IF(H3&lt;&gt;"",H3*0.014,""),""))</f>
+        <f t="shared" ref="M3:M35" si="5">IF(B3="Airbnb",IF(L3&lt;&gt;"",L3*0.2,""),IF(B3="Booking.com",IF(H3&lt;&gt;"",H3*0.014,""),""))</f>
         <v>3.24</v>
       </c>
       <c r="N3" s="5" t="str">
-        <f t="shared" ref="N3:N34" ca="1" si="6">IF(D3="","",IF(E3&lt;TODAY(),"✅ Terminée",IF(D3&lt;=TODAY(),"🟡 En cours","🔵 À venir")))</f>
-        <v>🟡 En cours</v>
+        <f t="shared" ref="N3:N35" ca="1" si="6">IF(D3="","",IF(E3&lt;TODAY(),"✅ Terminée",IF(D3&lt;=TODAY(),"🟡 En cours","🔵 À venir")))</f>
+        <v>✅ Terminée</v>
       </c>
       <c r="O3" s="11" t="s">
         <v>40</v>
@@ -1329,7 +1825,7 @@
       </c>
       <c r="N8" s="14" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>🔵 À venir</v>
+        <v>✅ Terminée</v>
       </c>
       <c r="O8" s="19" t="s">
         <v>40</v>
@@ -1452,234 +1948,302 @@
         <v>52</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <v>9</v>
       </c>
-      <c r="B11" s="5"/>
-      <c r="C11" s="21"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G11" s="5"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J11" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K11" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="L11" s="9" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="M11" s="9" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="N11" s="5" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="O11" s="11"/>
-      <c r="P11" s="12"/>
-    </row>
-    <row r="12" spans="1:16" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="D11" s="7">
+        <v>46297</v>
+      </c>
+      <c r="E11" s="7">
+        <v>46299</v>
+      </c>
+      <c r="F11" s="14">
+        <f>IF(AND(D11&lt;&gt;"",E11&lt;&gt;""),E11-D11,"")</f>
+        <v>2</v>
+      </c>
+      <c r="G11" s="5">
+        <v>6</v>
+      </c>
+      <c r="H11" s="17">
+        <v>270</v>
+      </c>
+      <c r="I11" s="9">
+        <f>IF(B11="Direto","",IF(B11="Airbnb",IF(H11&lt;&gt;"",H11*0.03+H11*0.03*0.2,""),IF(B11="Booking.com",IF(H11&lt;&gt;"",H11*0.15+H11*0.014,""),"")))</f>
+        <v>44.28</v>
+      </c>
+      <c r="J11" s="18">
+        <f>IF(B11="Direto",IF(H11&lt;&gt;"",H11,""),IF(H11&lt;&gt;"",H11-IF(I11&lt;&gt;"",I11,0),""))</f>
+        <v>225.72</v>
+      </c>
+      <c r="K11" s="18">
+        <f>IF(J11&lt;&gt;"",J11*0.25,"")</f>
+        <v>56.43</v>
+      </c>
+      <c r="L11" s="9">
+        <f>IF(B11="Airbnb",IF(H11&lt;&gt;"",H11*0.03,""),IF(B11="Booking.com",IF(H11&lt;&gt;"",H11*0.15,""),""))</f>
+        <v>40.5</v>
+      </c>
+      <c r="M11" s="9">
+        <f>IF(B11="Airbnb",IF(L11&lt;&gt;"",L11*0.2,""),IF(B11="Booking.com",IF(H11&lt;&gt;"",H11*0.014,""),""))</f>
+        <v>3.7800000000000002</v>
+      </c>
+      <c r="N11" s="14" t="str">
+        <f ca="1">IF(D11="","",IF(E11&lt;TODAY(),"✅ Terminée",IF(D11&lt;=TODAY(),"🟡 En cours","🔵 À venir")))</f>
+        <v>🔵 À venir</v>
+      </c>
+      <c r="O11" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="P11" s="20" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="13">
         <v>10</v>
       </c>
-      <c r="B12" s="14"/>
-      <c r="C12" s="22"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="14" t="str">
+      <c r="B12" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="D12" s="7">
+        <v>46236</v>
+      </c>
+      <c r="E12" s="7">
+        <v>46240</v>
+      </c>
+      <c r="F12" s="14">
+        <f>IF(AND(D12&lt;&gt;"",E12&lt;&gt;""),E12-D12,"")</f>
+        <v>4</v>
+      </c>
+      <c r="G12" s="5">
+        <v>2</v>
+      </c>
+      <c r="H12" s="17">
+        <v>540</v>
+      </c>
+      <c r="I12" s="9">
+        <f>IF(B12="Direto","",IF(B12="Airbnb",IF(H12&lt;&gt;"",H12*0.03+H12*0.03*0.2,""),IF(B12="Booking.com",IF(H12&lt;&gt;"",H12*0.15+H12*0.014,""),"")))</f>
+        <v>88.56</v>
+      </c>
+      <c r="J12" s="18">
+        <f>IF(B12="Direto",IF(H12&lt;&gt;"",H12,""),IF(H12&lt;&gt;"",H12-IF(I12&lt;&gt;"",I12,0),""))</f>
+        <v>451.44</v>
+      </c>
+      <c r="K12" s="18">
+        <f>IF(J12&lt;&gt;"",J12*0.25,"")</f>
+        <v>112.86</v>
+      </c>
+      <c r="L12" s="9">
+        <f>IF(B12="Airbnb",IF(H12&lt;&gt;"",H12*0.03,""),IF(B12="Booking.com",IF(H12&lt;&gt;"",H12*0.15,""),""))</f>
+        <v>81</v>
+      </c>
+      <c r="M12" s="9">
+        <f>IF(B12="Airbnb",IF(L12&lt;&gt;"",L12*0.2,""),IF(B12="Booking.com",IF(H12&lt;&gt;"",H12*0.014,""),""))</f>
+        <v>7.5600000000000005</v>
+      </c>
+      <c r="N12" s="14" t="str">
+        <f ca="1">IF(D12="","",IF(E12&lt;TODAY(),"✅ Terminée",IF(D12&lt;=TODAY(),"🟡 En cours","🔵 À venir")))</f>
+        <v>🔵 À venir</v>
+      </c>
+      <c r="O12" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="P12" s="20" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="13"/>
+      <c r="B13" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="D13" s="7">
+        <v>46291</v>
+      </c>
+      <c r="E13" s="7">
+        <v>46295</v>
+      </c>
+      <c r="F13" s="14">
+        <f>IF(AND(D13&lt;&gt;"",E13&lt;&gt;""),E13-D13,"")</f>
+        <v>4</v>
+      </c>
+      <c r="G13" s="5">
+        <v>7</v>
+      </c>
+      <c r="H13" s="17">
+        <v>680</v>
+      </c>
+      <c r="I13" s="9">
+        <f>IF(B13="Direto","",IF(B13="Airbnb",IF(H13&lt;&gt;"",H13*0.03+H13*0.03*0.2,""),IF(B13="Booking.com",IF(H13&lt;&gt;"",H13*0.15+H13*0.014,""),"")))</f>
+        <v>111.52</v>
+      </c>
+      <c r="J13" s="18">
+        <f>IF(B13="Direto",IF(H13&lt;&gt;"",H13,""),IF(H13&lt;&gt;"",H13-IF(I13&lt;&gt;"",I13,0),""))</f>
+        <v>568.48</v>
+      </c>
+      <c r="K13" s="18">
+        <f>IF(J13&lt;&gt;"",J13*0.25,"")</f>
+        <v>142.12</v>
+      </c>
+      <c r="L13" s="9">
+        <f>IF(B13="Airbnb",IF(H13&lt;&gt;"",H13*0.03,""),IF(B13="Booking.com",IF(H13&lt;&gt;"",H13*0.15,""),""))</f>
+        <v>102</v>
+      </c>
+      <c r="M13" s="9">
+        <f>IF(B13="Airbnb",IF(L13&lt;&gt;"",L13*0.2,""),IF(B13="Booking.com",IF(H13&lt;&gt;"",H13*0.014,""),""))</f>
+        <v>9.52</v>
+      </c>
+      <c r="N13" s="14" t="str">
+        <f ca="1">IF(D13="","",IF(E13&lt;TODAY(),"✅ Terminée",IF(D13&lt;=TODAY(),"🟡 En cours","🔵 À venir")))</f>
+        <v>🔵 À venir</v>
+      </c>
+      <c r="O13" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="P13" s="20" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="4">
+        <v>11</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="C14" s="22" t="s">
+        <v>56</v>
+      </c>
+      <c r="D14" s="16">
+        <v>46175</v>
+      </c>
+      <c r="E14" s="16">
+        <v>46178</v>
+      </c>
+      <c r="F14" s="14">
+        <f>IF(AND(D14&lt;&gt;"",E14&lt;&gt;""),E14-D14,"")</f>
+        <v>3</v>
+      </c>
+      <c r="G14" s="14">
+        <v>5</v>
+      </c>
+      <c r="H14" s="17">
+        <v>364.5</v>
+      </c>
+      <c r="I14" s="9"/>
+      <c r="J14" s="18">
+        <v>328.67</v>
+      </c>
+      <c r="K14" s="18">
+        <f>IF(J14&lt;&gt;"",J14*0.25,"")</f>
+        <v>82.167500000000004</v>
+      </c>
+      <c r="L14" s="9"/>
+      <c r="M14" s="9"/>
+      <c r="N14" s="14" t="str">
+        <f ca="1">IF(D14="","",IF(E14&lt;TODAY(),"✅ Terminée",IF(D14&lt;=TODAY(),"🟡 En cours","🔵 À venir")))</f>
+        <v>🔵 À venir</v>
+      </c>
+      <c r="O14" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="P14" s="20" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="13">
+        <v>12</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="C15" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="D15" s="16">
+        <v>46143</v>
+      </c>
+      <c r="E15" s="16">
+        <v>46144</v>
+      </c>
+      <c r="F15" s="14">
+        <f>IF(AND(D15&lt;&gt;"",E15&lt;&gt;""),E15-D15,"")</f>
+        <v>1</v>
+      </c>
+      <c r="G15" s="14">
+        <v>3</v>
+      </c>
+      <c r="H15" s="17">
+        <v>130</v>
+      </c>
+      <c r="I15" s="9" t="str">
+        <f>IF(B15="Direto","",IF(B15="Airbnb",IF(H15&lt;&gt;"",H15*0.03+H15*0.03*0.2,""),IF(B15="Booking.com",IF(H15&lt;&gt;"",H15*0.15+H15*0.014,""),"")))</f>
+        <v/>
+      </c>
+      <c r="J15" s="18">
+        <f>IF(B15="Direto",IF(H15&lt;&gt;"",H15,""),IF(H15&lt;&gt;"",H15-IF(I15&lt;&gt;"",I15,0),""))</f>
+        <v>130</v>
+      </c>
+      <c r="K15" s="18">
+        <f>IF(J15&lt;&gt;"",J15*0.25,"")</f>
+        <v>32.5</v>
+      </c>
+      <c r="L15" s="9" t="str">
+        <f>IF(B15="Airbnb",IF(H15&lt;&gt;"",H15*0.03,""),IF(B15="Booking.com",IF(H15&lt;&gt;"",H15*0.15,""),""))</f>
+        <v/>
+      </c>
+      <c r="M15" s="9" t="str">
+        <f>IF(B15="Airbnb",IF(L15&lt;&gt;"",L15*0.2,""),IF(B15="Booking.com",IF(H15&lt;&gt;"",H15*0.014,""),""))</f>
+        <v/>
+      </c>
+      <c r="N15" s="14" t="str">
+        <f ca="1">IF(D15="","",IF(E15&lt;TODAY(),"✅ Terminée",IF(D15&lt;=TODAY(),"🟡 En cours","🔵 À venir")))</f>
+        <v>🔵 À venir</v>
+      </c>
+      <c r="O15" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="P15" s="20" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="4">
+        <v>13</v>
+      </c>
+      <c r="B16" s="5"/>
+      <c r="C16" s="21"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="5" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G12" s="14"/>
-      <c r="H12" s="17"/>
-      <c r="I12" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J12" s="18" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K12" s="18" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="L12" s="9" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="M12" s="9" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="N12" s="14" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="O12" s="19"/>
-      <c r="P12" s="20"/>
-    </row>
-    <row r="13" spans="1:16" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="4">
-        <v>11</v>
-      </c>
-      <c r="B13" s="5"/>
-      <c r="C13" s="21"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G13" s="5"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J13" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K13" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="L13" s="9" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="M13" s="9" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="N13" s="5" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="O13" s="11"/>
-      <c r="P13" s="12"/>
-    </row>
-    <row r="14" spans="1:16" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="13">
-        <v>12</v>
-      </c>
-      <c r="B14" s="14"/>
-      <c r="C14" s="22"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="14" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G14" s="14"/>
-      <c r="H14" s="17"/>
-      <c r="I14" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J14" s="18" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K14" s="18" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="L14" s="9" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="M14" s="9" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="N14" s="14" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="O14" s="19"/>
-      <c r="P14" s="20"/>
-    </row>
-    <row r="15" spans="1:16" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="4">
-        <v>13</v>
-      </c>
-      <c r="B15" s="5"/>
-      <c r="C15" s="21"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G15" s="5"/>
-      <c r="H15" s="8"/>
-      <c r="I15" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J15" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K15" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="L15" s="9" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="M15" s="9" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="N15" s="5" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="O15" s="11"/>
-      <c r="P15" s="12"/>
-    </row>
-    <row r="16" spans="1:16" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="13">
-        <v>14</v>
-      </c>
-      <c r="B16" s="14"/>
-      <c r="C16" s="22"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16"/>
-      <c r="F16" s="14" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G16" s="14"/>
-      <c r="H16" s="17"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="8"/>
       <c r="I16" s="9" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J16" s="18" t="str">
+      <c r="J16" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K16" s="18" t="str">
+      <c r="K16" s="10" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -1691,36 +2255,36 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N16" s="14" t="str">
+      <c r="N16" s="5" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="O16" s="19"/>
-      <c r="P16" s="20"/>
-    </row>
-    <row r="17" spans="1:16" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="4">
-        <v>15</v>
-      </c>
-      <c r="B17" s="5"/>
-      <c r="C17" s="21"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="5" t="str">
+      <c r="O16" s="11"/>
+      <c r="P16" s="12"/>
+    </row>
+    <row r="17" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="13">
+        <v>14</v>
+      </c>
+      <c r="B17" s="14"/>
+      <c r="C17" s="22"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="14" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G17" s="5"/>
-      <c r="H17" s="8"/>
+      <c r="G17" s="14"/>
+      <c r="H17" s="17"/>
       <c r="I17" s="9" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J17" s="10" t="str">
+      <c r="J17" s="18" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K17" s="10" t="str">
+      <c r="K17" s="18" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -1732,36 +2296,36 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N17" s="5" t="str">
+      <c r="N17" s="14" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="O17" s="11"/>
-      <c r="P17" s="12"/>
-    </row>
-    <row r="18" spans="1:16" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="13">
-        <v>16</v>
-      </c>
-      <c r="B18" s="14"/>
-      <c r="C18" s="22"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="16"/>
-      <c r="F18" s="14" t="str">
+      <c r="O17" s="19"/>
+      <c r="P17" s="20"/>
+    </row>
+    <row r="18" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="4">
+        <v>15</v>
+      </c>
+      <c r="B18" s="5"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="5" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G18" s="14"/>
-      <c r="H18" s="17"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="8"/>
       <c r="I18" s="9" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J18" s="18" t="str">
+      <c r="J18" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K18" s="18" t="str">
+      <c r="K18" s="10" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -1773,36 +2337,36 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N18" s="14" t="str">
+      <c r="N18" s="5" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="O18" s="19"/>
-      <c r="P18" s="20"/>
-    </row>
-    <row r="19" spans="1:16" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="4">
-        <v>17</v>
-      </c>
-      <c r="B19" s="5"/>
-      <c r="C19" s="21"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="5" t="str">
+      <c r="O18" s="11"/>
+      <c r="P18" s="12"/>
+    </row>
+    <row r="19" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="13">
+        <v>16</v>
+      </c>
+      <c r="B19" s="14"/>
+      <c r="C19" s="22"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="16"/>
+      <c r="F19" s="14" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G19" s="5"/>
-      <c r="H19" s="8"/>
+      <c r="G19" s="14"/>
+      <c r="H19" s="17"/>
       <c r="I19" s="9" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J19" s="10" t="str">
+      <c r="J19" s="18" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K19" s="10" t="str">
+      <c r="K19" s="18" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -1814,36 +2378,36 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N19" s="5" t="str">
+      <c r="N19" s="14" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="O19" s="11"/>
-      <c r="P19" s="12"/>
-    </row>
-    <row r="20" spans="1:16" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="13">
-        <v>18</v>
-      </c>
-      <c r="B20" s="14"/>
-      <c r="C20" s="22"/>
-      <c r="D20" s="16"/>
-      <c r="E20" s="16"/>
-      <c r="F20" s="14" t="str">
+      <c r="O19" s="19"/>
+      <c r="P19" s="20"/>
+    </row>
+    <row r="20" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="4">
+        <v>17</v>
+      </c>
+      <c r="B20" s="5"/>
+      <c r="C20" s="21"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="5" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G20" s="14"/>
-      <c r="H20" s="17"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="8"/>
       <c r="I20" s="9" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J20" s="18" t="str">
+      <c r="J20" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K20" s="18" t="str">
+      <c r="K20" s="10" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -1855,36 +2419,36 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N20" s="14" t="str">
+      <c r="N20" s="5" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="O20" s="19"/>
-      <c r="P20" s="20"/>
-    </row>
-    <row r="21" spans="1:16" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="4">
-        <v>19</v>
-      </c>
-      <c r="B21" s="5"/>
-      <c r="C21" s="21"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="5" t="str">
+      <c r="O20" s="11"/>
+      <c r="P20" s="12"/>
+    </row>
+    <row r="21" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="13">
+        <v>18</v>
+      </c>
+      <c r="B21" s="14"/>
+      <c r="C21" s="22"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="16"/>
+      <c r="F21" s="14" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G21" s="5"/>
-      <c r="H21" s="8"/>
+      <c r="G21" s="14"/>
+      <c r="H21" s="17"/>
       <c r="I21" s="9" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J21" s="10" t="str">
+      <c r="J21" s="18" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K21" s="10" t="str">
+      <c r="K21" s="18" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -1896,36 +2460,36 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N21" s="5" t="str">
+      <c r="N21" s="14" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="O21" s="11"/>
-      <c r="P21" s="12"/>
-    </row>
-    <row r="22" spans="1:16" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="13">
-        <v>20</v>
-      </c>
-      <c r="B22" s="14"/>
-      <c r="C22" s="22"/>
-      <c r="D22" s="16"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="14" t="str">
+      <c r="O21" s="19"/>
+      <c r="P21" s="20"/>
+    </row>
+    <row r="22" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="4">
+        <v>19</v>
+      </c>
+      <c r="B22" s="5"/>
+      <c r="C22" s="21"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="5" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G22" s="14"/>
-      <c r="H22" s="17"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="8"/>
       <c r="I22" s="9" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J22" s="18" t="str">
+      <c r="J22" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K22" s="18" t="str">
+      <c r="K22" s="10" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -1937,36 +2501,36 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N22" s="14" t="str">
+      <c r="N22" s="5" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="O22" s="19"/>
-      <c r="P22" s="20"/>
-    </row>
-    <row r="23" spans="1:16" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="4">
-        <v>21</v>
-      </c>
-      <c r="B23" s="5"/>
-      <c r="C23" s="21"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="5" t="str">
+      <c r="O22" s="11"/>
+      <c r="P22" s="12"/>
+    </row>
+    <row r="23" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="13">
+        <v>20</v>
+      </c>
+      <c r="B23" s="14"/>
+      <c r="C23" s="22"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="16"/>
+      <c r="F23" s="14" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G23" s="5"/>
-      <c r="H23" s="8"/>
+      <c r="G23" s="14"/>
+      <c r="H23" s="17"/>
       <c r="I23" s="9" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J23" s="10" t="str">
+      <c r="J23" s="18" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K23" s="10" t="str">
+      <c r="K23" s="18" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -1978,36 +2542,36 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N23" s="5" t="str">
+      <c r="N23" s="14" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="O23" s="11"/>
-      <c r="P23" s="12"/>
-    </row>
-    <row r="24" spans="1:16" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="13">
-        <v>22</v>
-      </c>
-      <c r="B24" s="14"/>
-      <c r="C24" s="22"/>
-      <c r="D24" s="16"/>
-      <c r="E24" s="16"/>
-      <c r="F24" s="14" t="str">
+      <c r="O23" s="19"/>
+      <c r="P23" s="20"/>
+    </row>
+    <row r="24" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="4">
+        <v>21</v>
+      </c>
+      <c r="B24" s="5"/>
+      <c r="C24" s="21"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="5" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G24" s="14"/>
-      <c r="H24" s="17"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="8"/>
       <c r="I24" s="9" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J24" s="18" t="str">
+      <c r="J24" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K24" s="18" t="str">
+      <c r="K24" s="10" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -2019,36 +2583,36 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N24" s="14" t="str">
+      <c r="N24" s="5" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="O24" s="19"/>
-      <c r="P24" s="20"/>
-    </row>
-    <row r="25" spans="1:16" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="4">
-        <v>23</v>
-      </c>
-      <c r="B25" s="5"/>
-      <c r="C25" s="21"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="5" t="str">
+      <c r="O24" s="11"/>
+      <c r="P24" s="12"/>
+    </row>
+    <row r="25" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="13">
+        <v>22</v>
+      </c>
+      <c r="B25" s="14"/>
+      <c r="C25" s="22"/>
+      <c r="D25" s="16"/>
+      <c r="E25" s="16"/>
+      <c r="F25" s="14" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G25" s="5"/>
-      <c r="H25" s="8"/>
+      <c r="G25" s="14"/>
+      <c r="H25" s="17"/>
       <c r="I25" s="9" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J25" s="10" t="str">
+      <c r="J25" s="18" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K25" s="10" t="str">
+      <c r="K25" s="18" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -2060,36 +2624,36 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N25" s="5" t="str">
+      <c r="N25" s="14" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="O25" s="11"/>
-      <c r="P25" s="12"/>
-    </row>
-    <row r="26" spans="1:16" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="13">
-        <v>24</v>
-      </c>
-      <c r="B26" s="14"/>
-      <c r="C26" s="22"/>
-      <c r="D26" s="16"/>
-      <c r="E26" s="16"/>
-      <c r="F26" s="14" t="str">
+      <c r="O25" s="19"/>
+      <c r="P25" s="20"/>
+    </row>
+    <row r="26" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="4">
+        <v>23</v>
+      </c>
+      <c r="B26" s="5"/>
+      <c r="C26" s="21"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="5" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G26" s="14"/>
-      <c r="H26" s="17"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="8"/>
       <c r="I26" s="9" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J26" s="18" t="str">
+      <c r="J26" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K26" s="18" t="str">
+      <c r="K26" s="10" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -2101,36 +2665,36 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N26" s="14" t="str">
+      <c r="N26" s="5" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="O26" s="19"/>
-      <c r="P26" s="20"/>
-    </row>
-    <row r="27" spans="1:16" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="4">
-        <v>25</v>
-      </c>
-      <c r="B27" s="5"/>
-      <c r="C27" s="21"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="5" t="str">
+      <c r="O26" s="11"/>
+      <c r="P26" s="12"/>
+    </row>
+    <row r="27" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="13">
+        <v>24</v>
+      </c>
+      <c r="B27" s="14"/>
+      <c r="C27" s="22"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="16"/>
+      <c r="F27" s="14" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G27" s="5"/>
-      <c r="H27" s="8"/>
+      <c r="G27" s="14"/>
+      <c r="H27" s="17"/>
       <c r="I27" s="9" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J27" s="10" t="str">
+      <c r="J27" s="18" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K27" s="10" t="str">
+      <c r="K27" s="18" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -2142,36 +2706,36 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N27" s="5" t="str">
+      <c r="N27" s="14" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="O27" s="11"/>
-      <c r="P27" s="12"/>
-    </row>
-    <row r="28" spans="1:16" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="13">
-        <v>26</v>
-      </c>
-      <c r="B28" s="14"/>
-      <c r="C28" s="22"/>
-      <c r="D28" s="16"/>
-      <c r="E28" s="16"/>
-      <c r="F28" s="14" t="str">
+      <c r="O27" s="19"/>
+      <c r="P27" s="20"/>
+    </row>
+    <row r="28" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="4">
+        <v>25</v>
+      </c>
+      <c r="B28" s="5"/>
+      <c r="C28" s="21"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="5" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G28" s="14"/>
-      <c r="H28" s="17"/>
+      <c r="G28" s="5"/>
+      <c r="H28" s="8"/>
       <c r="I28" s="9" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J28" s="18" t="str">
+      <c r="J28" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K28" s="18" t="str">
+      <c r="K28" s="10" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -2183,36 +2747,36 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N28" s="14" t="str">
+      <c r="N28" s="5" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="O28" s="19"/>
-      <c r="P28" s="20"/>
-    </row>
-    <row r="29" spans="1:16" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="4">
-        <v>27</v>
-      </c>
-      <c r="B29" s="5"/>
-      <c r="C29" s="21"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="7"/>
-      <c r="F29" s="5" t="str">
+      <c r="O28" s="11"/>
+      <c r="P28" s="12"/>
+    </row>
+    <row r="29" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="13">
+        <v>26</v>
+      </c>
+      <c r="B29" s="14"/>
+      <c r="C29" s="22"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="14" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G29" s="5"/>
-      <c r="H29" s="8"/>
+      <c r="G29" s="14"/>
+      <c r="H29" s="17"/>
       <c r="I29" s="9" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J29" s="10" t="str">
+      <c r="J29" s="18" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K29" s="10" t="str">
+      <c r="K29" s="18" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -2224,36 +2788,36 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N29" s="5" t="str">
+      <c r="N29" s="14" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="O29" s="11"/>
-      <c r="P29" s="12"/>
-    </row>
-    <row r="30" spans="1:16" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="13">
-        <v>28</v>
-      </c>
-      <c r="B30" s="14"/>
-      <c r="C30" s="22"/>
-      <c r="D30" s="16"/>
-      <c r="E30" s="16"/>
-      <c r="F30" s="14" t="str">
+      <c r="O29" s="19"/>
+      <c r="P29" s="20"/>
+    </row>
+    <row r="30" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="4">
+        <v>27</v>
+      </c>
+      <c r="B30" s="5"/>
+      <c r="C30" s="21"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
+      <c r="F30" s="5" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G30" s="14"/>
-      <c r="H30" s="17"/>
+      <c r="G30" s="5"/>
+      <c r="H30" s="8"/>
       <c r="I30" s="9" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J30" s="18" t="str">
+      <c r="J30" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K30" s="18" t="str">
+      <c r="K30" s="10" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -2265,36 +2829,36 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N30" s="14" t="str">
+      <c r="N30" s="5" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="O30" s="19"/>
-      <c r="P30" s="20"/>
-    </row>
-    <row r="31" spans="1:16" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="4">
-        <v>29</v>
-      </c>
-      <c r="B31" s="5"/>
-      <c r="C31" s="21"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
-      <c r="F31" s="5" t="str">
+      <c r="O30" s="11"/>
+      <c r="P30" s="12"/>
+    </row>
+    <row r="31" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="13">
+        <v>28</v>
+      </c>
+      <c r="B31" s="14"/>
+      <c r="C31" s="22"/>
+      <c r="D31" s="16"/>
+      <c r="E31" s="16"/>
+      <c r="F31" s="14" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G31" s="5"/>
-      <c r="H31" s="8"/>
+      <c r="G31" s="14"/>
+      <c r="H31" s="17"/>
       <c r="I31" s="9" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J31" s="10" t="str">
+      <c r="J31" s="18" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K31" s="10" t="str">
+      <c r="K31" s="18" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -2306,36 +2870,36 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N31" s="5" t="str">
+      <c r="N31" s="14" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="O31" s="11"/>
-      <c r="P31" s="12"/>
-    </row>
-    <row r="32" spans="1:16" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="13">
-        <v>30</v>
-      </c>
-      <c r="B32" s="14"/>
-      <c r="C32" s="22"/>
-      <c r="D32" s="16"/>
-      <c r="E32" s="16"/>
-      <c r="F32" s="14" t="str">
+      <c r="O31" s="19"/>
+      <c r="P31" s="20"/>
+    </row>
+    <row r="32" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="4">
+        <v>29</v>
+      </c>
+      <c r="B32" s="5"/>
+      <c r="C32" s="21"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="7"/>
+      <c r="F32" s="5" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G32" s="14"/>
-      <c r="H32" s="17"/>
+      <c r="G32" s="5"/>
+      <c r="H32" s="8"/>
       <c r="I32" s="9" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J32" s="18" t="str">
+      <c r="J32" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K32" s="18" t="str">
+      <c r="K32" s="10" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -2347,36 +2911,36 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N32" s="14" t="str">
+      <c r="N32" s="5" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="O32" s="19"/>
-      <c r="P32" s="20"/>
-    </row>
-    <row r="33" spans="1:16" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="4">
-        <v>31</v>
-      </c>
-      <c r="B33" s="5"/>
-      <c r="C33" s="21"/>
-      <c r="D33" s="7"/>
-      <c r="E33" s="7"/>
-      <c r="F33" s="5" t="str">
+      <c r="O32" s="11"/>
+      <c r="P32" s="12"/>
+    </row>
+    <row r="33" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="13">
+        <v>30</v>
+      </c>
+      <c r="B33" s="14"/>
+      <c r="C33" s="22"/>
+      <c r="D33" s="16"/>
+      <c r="E33" s="16"/>
+      <c r="F33" s="14" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G33" s="5"/>
-      <c r="H33" s="8"/>
+      <c r="G33" s="14"/>
+      <c r="H33" s="17"/>
       <c r="I33" s="9" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J33" s="10" t="str">
+      <c r="J33" s="18" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K33" s="10" t="str">
+      <c r="K33" s="18" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -2388,36 +2952,36 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N33" s="5" t="str">
+      <c r="N33" s="14" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="O33" s="11"/>
-      <c r="P33" s="12"/>
-    </row>
-    <row r="34" spans="1:16" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="13">
-        <v>32</v>
-      </c>
-      <c r="B34" s="14"/>
-      <c r="C34" s="22"/>
-      <c r="D34" s="16"/>
-      <c r="E34" s="16"/>
-      <c r="F34" s="14" t="str">
+      <c r="O33" s="19"/>
+      <c r="P33" s="20"/>
+    </row>
+    <row r="34" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="4">
+        <v>31</v>
+      </c>
+      <c r="B34" s="5"/>
+      <c r="C34" s="21"/>
+      <c r="D34" s="7"/>
+      <c r="E34" s="7"/>
+      <c r="F34" s="5" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G34" s="14"/>
-      <c r="H34" s="17"/>
+      <c r="G34" s="5"/>
+      <c r="H34" s="8"/>
       <c r="I34" s="9" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J34" s="18" t="str">
+      <c r="J34" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K34" s="18" t="str">
+      <c r="K34" s="10" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -2429,118 +2993,118 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N34" s="14" t="str">
+      <c r="N34" s="5" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="O34" s="19"/>
-      <c r="P34" s="20"/>
-    </row>
-    <row r="35" spans="1:16" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="4">
+      <c r="O34" s="11"/>
+      <c r="P34" s="12"/>
+    </row>
+    <row r="35" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="13">
+        <v>32</v>
+      </c>
+      <c r="B35" s="14"/>
+      <c r="C35" s="22"/>
+      <c r="D35" s="16"/>
+      <c r="E35" s="16"/>
+      <c r="F35" s="14" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G35" s="14"/>
+      <c r="H35" s="17"/>
+      <c r="I35" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J35" s="18" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="K35" s="18" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="L35" s="9" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="M35" s="9" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="N35" s="14" t="str">
+        <f t="shared" ca="1" si="6"/>
+        <v/>
+      </c>
+      <c r="O35" s="19"/>
+      <c r="P35" s="20"/>
+    </row>
+    <row r="36" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="4">
         <v>33</v>
       </c>
-      <c r="B35" s="5"/>
-      <c r="C35" s="21"/>
-      <c r="D35" s="7"/>
-      <c r="E35" s="7"/>
-      <c r="F35" s="5" t="str">
-        <f t="shared" ref="F35:F50" si="7">IF(AND(D35&lt;&gt;"",E35&lt;&gt;""),E35-D35,"")</f>
-        <v/>
-      </c>
-      <c r="G35" s="5"/>
-      <c r="H35" s="8"/>
-      <c r="I35" s="9" t="str">
-        <f t="shared" ref="I35:I49" si="8">IF(B35="Direto","",IF(B35="Airbnb",IF(H35&lt;&gt;"",H35*0.03+H35*0.03*0.2,""),IF(B35="Booking.com",IF(H35&lt;&gt;"",H35*0.15+H35*0.014,""),"")))</f>
-        <v/>
-      </c>
-      <c r="J35" s="10" t="str">
-        <f t="shared" ref="J35:J49" si="9">IF(B35="Direto",IF(H35&lt;&gt;"",H35,""),IF(H35&lt;&gt;"",H35-IF(I35&lt;&gt;"",I35,0),""))</f>
-        <v/>
-      </c>
-      <c r="K35" s="10" t="str">
-        <f t="shared" ref="K35:K50" si="10">IF(J35&lt;&gt;"",J35*0.25,"")</f>
-        <v/>
-      </c>
-      <c r="L35" s="9" t="str">
-        <f t="shared" ref="L35:L49" si="11">IF(B35="Airbnb",IF(H35&lt;&gt;"",H35*0.03,""),IF(B35="Booking.com",IF(H35&lt;&gt;"",H35*0.15,""),""))</f>
-        <v/>
-      </c>
-      <c r="M35" s="9" t="str">
-        <f t="shared" ref="M35:M49" si="12">IF(B35="Airbnb",IF(L35&lt;&gt;"",L35*0.2,""),IF(B35="Booking.com",IF(H35&lt;&gt;"",H35*0.014,""),""))</f>
-        <v/>
-      </c>
-      <c r="N35" s="5" t="str">
-        <f t="shared" ref="N35:N50" ca="1" si="13">IF(D35="","",IF(E35&lt;TODAY(),"✅ Terminée",IF(D35&lt;=TODAY(),"🟡 En cours","🔵 À venir")))</f>
-        <v/>
-      </c>
-      <c r="O35" s="11"/>
-      <c r="P35" s="12"/>
-    </row>
-    <row r="36" spans="1:16" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="13">
+      <c r="B36" s="5"/>
+      <c r="C36" s="21"/>
+      <c r="D36" s="7"/>
+      <c r="E36" s="7"/>
+      <c r="F36" s="5" t="str">
+        <f t="shared" ref="F36:F50" si="7">IF(AND(D36&lt;&gt;"",E36&lt;&gt;""),E36-D36,"")</f>
+        <v/>
+      </c>
+      <c r="G36" s="5"/>
+      <c r="H36" s="8"/>
+      <c r="I36" s="9" t="str">
+        <f t="shared" ref="I36:I50" si="8">IF(B36="Direto","",IF(B36="Airbnb",IF(H36&lt;&gt;"",H36*0.03+H36*0.03*0.2,""),IF(B36="Booking.com",IF(H36&lt;&gt;"",H36*0.15+H36*0.014,""),"")))</f>
+        <v/>
+      </c>
+      <c r="J36" s="10" t="str">
+        <f t="shared" ref="J36:J50" si="9">IF(B36="Direto",IF(H36&lt;&gt;"",H36,""),IF(H36&lt;&gt;"",H36-IF(I36&lt;&gt;"",I36,0),""))</f>
+        <v/>
+      </c>
+      <c r="K36" s="10" t="str">
+        <f t="shared" ref="K36:K50" si="10">IF(J36&lt;&gt;"",J36*0.25,"")</f>
+        <v/>
+      </c>
+      <c r="L36" s="9" t="str">
+        <f t="shared" ref="L36:L50" si="11">IF(B36="Airbnb",IF(H36&lt;&gt;"",H36*0.03,""),IF(B36="Booking.com",IF(H36&lt;&gt;"",H36*0.15,""),""))</f>
+        <v/>
+      </c>
+      <c r="M36" s="9" t="str">
+        <f t="shared" ref="M36:M50" si="12">IF(B36="Airbnb",IF(L36&lt;&gt;"",L36*0.2,""),IF(B36="Booking.com",IF(H36&lt;&gt;"",H36*0.014,""),""))</f>
+        <v/>
+      </c>
+      <c r="N36" s="5" t="str">
+        <f t="shared" ref="N36:N50" ca="1" si="13">IF(D36="","",IF(E36&lt;TODAY(),"✅ Terminée",IF(D36&lt;=TODAY(),"🟡 En cours","🔵 À venir")))</f>
+        <v/>
+      </c>
+      <c r="O36" s="11"/>
+      <c r="P36" s="12"/>
+    </row>
+    <row r="37" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="13">
         <v>34</v>
       </c>
-      <c r="B36" s="14"/>
-      <c r="C36" s="22"/>
-      <c r="D36" s="16"/>
-      <c r="E36" s="16"/>
-      <c r="F36" s="14" t="str">
+      <c r="B37" s="14"/>
+      <c r="C37" s="22"/>
+      <c r="D37" s="16"/>
+      <c r="E37" s="16"/>
+      <c r="F37" s="14" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="G36" s="14"/>
-      <c r="H36" s="17"/>
-      <c r="I36" s="9" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="J36" s="18" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="K36" s="18" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="L36" s="9" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="M36" s="9" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="N36" s="14" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="O36" s="19"/>
-      <c r="P36" s="20"/>
-    </row>
-    <row r="37" spans="1:16" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="4">
-        <v>35</v>
-      </c>
-      <c r="B37" s="5"/>
-      <c r="C37" s="21"/>
-      <c r="D37" s="7"/>
-      <c r="E37" s="7"/>
-      <c r="F37" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="G37" s="5"/>
-      <c r="H37" s="8"/>
+      <c r="G37" s="14"/>
+      <c r="H37" s="17"/>
       <c r="I37" s="9" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="J37" s="10" t="str">
+      <c r="J37" s="18" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="K37" s="10" t="str">
+      <c r="K37" s="18" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
@@ -2552,36 +3116,36 @@
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="N37" s="5" t="str">
+      <c r="N37" s="14" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="O37" s="11"/>
-      <c r="P37" s="12"/>
-    </row>
-    <row r="38" spans="1:16" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="13">
-        <v>36</v>
-      </c>
-      <c r="B38" s="14"/>
-      <c r="C38" s="22"/>
-      <c r="D38" s="16"/>
-      <c r="E38" s="16"/>
-      <c r="F38" s="14" t="str">
+      <c r="O37" s="19"/>
+      <c r="P37" s="20"/>
+    </row>
+    <row r="38" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="4">
+        <v>35</v>
+      </c>
+      <c r="B38" s="5"/>
+      <c r="C38" s="21"/>
+      <c r="D38" s="7"/>
+      <c r="E38" s="7"/>
+      <c r="F38" s="5" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="G38" s="14"/>
-      <c r="H38" s="17"/>
+      <c r="G38" s="5"/>
+      <c r="H38" s="8"/>
       <c r="I38" s="9" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="J38" s="18" t="str">
+      <c r="J38" s="10" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="K38" s="18" t="str">
+      <c r="K38" s="10" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
@@ -2593,36 +3157,36 @@
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="N38" s="14" t="str">
+      <c r="N38" s="5" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="O38" s="19"/>
-      <c r="P38" s="20"/>
-    </row>
-    <row r="39" spans="1:16" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="4">
-        <v>37</v>
-      </c>
-      <c r="B39" s="5"/>
-      <c r="C39" s="21"/>
-      <c r="D39" s="7"/>
-      <c r="E39" s="7"/>
-      <c r="F39" s="5" t="str">
+      <c r="O38" s="11"/>
+      <c r="P38" s="12"/>
+    </row>
+    <row r="39" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="13">
+        <v>36</v>
+      </c>
+      <c r="B39" s="14"/>
+      <c r="C39" s="22"/>
+      <c r="D39" s="16"/>
+      <c r="E39" s="16"/>
+      <c r="F39" s="14" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="G39" s="5"/>
-      <c r="H39" s="8"/>
+      <c r="G39" s="14"/>
+      <c r="H39" s="17"/>
       <c r="I39" s="9" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="J39" s="10" t="str">
+      <c r="J39" s="18" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="K39" s="10" t="str">
+      <c r="K39" s="18" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
@@ -2634,36 +3198,36 @@
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="N39" s="5" t="str">
+      <c r="N39" s="14" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="O39" s="11"/>
-      <c r="P39" s="12"/>
-    </row>
-    <row r="40" spans="1:16" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="13">
-        <v>38</v>
-      </c>
-      <c r="B40" s="14"/>
-      <c r="C40" s="22"/>
-      <c r="D40" s="16"/>
-      <c r="E40" s="16"/>
-      <c r="F40" s="14" t="str">
+      <c r="O39" s="19"/>
+      <c r="P39" s="20"/>
+    </row>
+    <row r="40" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="4">
+        <v>37</v>
+      </c>
+      <c r="B40" s="5"/>
+      <c r="C40" s="21"/>
+      <c r="D40" s="7"/>
+      <c r="E40" s="7"/>
+      <c r="F40" s="5" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="G40" s="14"/>
-      <c r="H40" s="17"/>
+      <c r="G40" s="5"/>
+      <c r="H40" s="8"/>
       <c r="I40" s="9" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="J40" s="18" t="str">
+      <c r="J40" s="10" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="K40" s="18" t="str">
+      <c r="K40" s="10" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
@@ -2675,36 +3239,36 @@
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="N40" s="14" t="str">
+      <c r="N40" s="5" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="O40" s="19"/>
-      <c r="P40" s="20"/>
-    </row>
-    <row r="41" spans="1:16" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="4">
-        <v>39</v>
-      </c>
-      <c r="B41" s="5"/>
-      <c r="C41" s="21"/>
-      <c r="D41" s="7"/>
-      <c r="E41" s="7"/>
-      <c r="F41" s="5" t="str">
+      <c r="O40" s="11"/>
+      <c r="P40" s="12"/>
+    </row>
+    <row r="41" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="13">
+        <v>38</v>
+      </c>
+      <c r="B41" s="14"/>
+      <c r="C41" s="22"/>
+      <c r="D41" s="16"/>
+      <c r="E41" s="16"/>
+      <c r="F41" s="14" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="G41" s="5"/>
-      <c r="H41" s="8"/>
+      <c r="G41" s="14"/>
+      <c r="H41" s="17"/>
       <c r="I41" s="9" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="J41" s="10" t="str">
+      <c r="J41" s="18" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="K41" s="10" t="str">
+      <c r="K41" s="18" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
@@ -2716,36 +3280,36 @@
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="N41" s="5" t="str">
+      <c r="N41" s="14" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="O41" s="11"/>
-      <c r="P41" s="12"/>
-    </row>
-    <row r="42" spans="1:16" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="13">
-        <v>40</v>
-      </c>
-      <c r="B42" s="14"/>
-      <c r="C42" s="22"/>
-      <c r="D42" s="16"/>
-      <c r="E42" s="16"/>
-      <c r="F42" s="14" t="str">
+      <c r="O41" s="19"/>
+      <c r="P41" s="20"/>
+    </row>
+    <row r="42" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="4">
+        <v>39</v>
+      </c>
+      <c r="B42" s="5"/>
+      <c r="C42" s="21"/>
+      <c r="D42" s="7"/>
+      <c r="E42" s="7"/>
+      <c r="F42" s="5" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="G42" s="14"/>
-      <c r="H42" s="17"/>
+      <c r="G42" s="5"/>
+      <c r="H42" s="8"/>
       <c r="I42" s="9" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="J42" s="18" t="str">
+      <c r="J42" s="10" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="K42" s="18" t="str">
+      <c r="K42" s="10" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
@@ -2757,36 +3321,36 @@
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="N42" s="14" t="str">
+      <c r="N42" s="5" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="O42" s="19"/>
-      <c r="P42" s="20"/>
-    </row>
-    <row r="43" spans="1:16" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="4">
-        <v>41</v>
-      </c>
-      <c r="B43" s="5"/>
-      <c r="C43" s="21"/>
-      <c r="D43" s="7"/>
-      <c r="E43" s="7"/>
-      <c r="F43" s="5" t="str">
+      <c r="O42" s="11"/>
+      <c r="P42" s="12"/>
+    </row>
+    <row r="43" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="13">
+        <v>40</v>
+      </c>
+      <c r="B43" s="14"/>
+      <c r="C43" s="22"/>
+      <c r="D43" s="16"/>
+      <c r="E43" s="16"/>
+      <c r="F43" s="14" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="G43" s="5"/>
-      <c r="H43" s="8"/>
+      <c r="G43" s="14"/>
+      <c r="H43" s="17"/>
       <c r="I43" s="9" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="J43" s="10" t="str">
+      <c r="J43" s="18" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="K43" s="10" t="str">
+      <c r="K43" s="18" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
@@ -2798,36 +3362,36 @@
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="N43" s="5" t="str">
+      <c r="N43" s="14" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="O43" s="11"/>
-      <c r="P43" s="12"/>
-    </row>
-    <row r="44" spans="1:16" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="13">
-        <v>42</v>
-      </c>
-      <c r="B44" s="14"/>
-      <c r="C44" s="22"/>
-      <c r="D44" s="16"/>
-      <c r="E44" s="16"/>
-      <c r="F44" s="14" t="str">
+      <c r="O43" s="19"/>
+      <c r="P43" s="20"/>
+    </row>
+    <row r="44" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="4">
+        <v>41</v>
+      </c>
+      <c r="B44" s="5"/>
+      <c r="C44" s="21"/>
+      <c r="D44" s="7"/>
+      <c r="E44" s="7"/>
+      <c r="F44" s="5" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="G44" s="14"/>
-      <c r="H44" s="17"/>
+      <c r="G44" s="5"/>
+      <c r="H44" s="8"/>
       <c r="I44" s="9" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="J44" s="18" t="str">
+      <c r="J44" s="10" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="K44" s="18" t="str">
+      <c r="K44" s="10" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
@@ -2839,36 +3403,36 @@
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="N44" s="14" t="str">
+      <c r="N44" s="5" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="O44" s="19"/>
-      <c r="P44" s="20"/>
-    </row>
-    <row r="45" spans="1:16" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="4">
-        <v>43</v>
-      </c>
-      <c r="B45" s="5"/>
-      <c r="C45" s="21"/>
-      <c r="D45" s="7"/>
-      <c r="E45" s="7"/>
-      <c r="F45" s="5" t="str">
+      <c r="O44" s="11"/>
+      <c r="P44" s="12"/>
+    </row>
+    <row r="45" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="13">
+        <v>42</v>
+      </c>
+      <c r="B45" s="14"/>
+      <c r="C45" s="22"/>
+      <c r="D45" s="16"/>
+      <c r="E45" s="16"/>
+      <c r="F45" s="14" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="G45" s="5"/>
-      <c r="H45" s="8"/>
+      <c r="G45" s="14"/>
+      <c r="H45" s="17"/>
       <c r="I45" s="9" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="J45" s="10" t="str">
+      <c r="J45" s="18" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="K45" s="10" t="str">
+      <c r="K45" s="18" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
@@ -2880,36 +3444,36 @@
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="N45" s="5" t="str">
+      <c r="N45" s="14" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="O45" s="11"/>
-      <c r="P45" s="12"/>
-    </row>
-    <row r="46" spans="1:16" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="13">
-        <v>44</v>
-      </c>
-      <c r="B46" s="14"/>
-      <c r="C46" s="22"/>
-      <c r="D46" s="16"/>
-      <c r="E46" s="16"/>
-      <c r="F46" s="14" t="str">
+      <c r="O45" s="19"/>
+      <c r="P45" s="20"/>
+    </row>
+    <row r="46" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="4">
+        <v>43</v>
+      </c>
+      <c r="B46" s="5"/>
+      <c r="C46" s="21"/>
+      <c r="D46" s="7"/>
+      <c r="E46" s="7"/>
+      <c r="F46" s="5" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="G46" s="14"/>
-      <c r="H46" s="17"/>
+      <c r="G46" s="5"/>
+      <c r="H46" s="8"/>
       <c r="I46" s="9" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="J46" s="18" t="str">
+      <c r="J46" s="10" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="K46" s="18" t="str">
+      <c r="K46" s="10" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
@@ -2921,36 +3485,36 @@
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="N46" s="14" t="str">
+      <c r="N46" s="5" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="O46" s="19"/>
-      <c r="P46" s="20"/>
-    </row>
-    <row r="47" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="4">
-        <v>45</v>
-      </c>
-      <c r="B47" s="5"/>
-      <c r="C47" s="21"/>
-      <c r="D47" s="7"/>
-      <c r="E47" s="7"/>
-      <c r="F47" s="5" t="str">
+      <c r="O46" s="11"/>
+      <c r="P46" s="12"/>
+    </row>
+    <row r="47" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="13">
+        <v>44</v>
+      </c>
+      <c r="B47" s="14"/>
+      <c r="C47" s="22"/>
+      <c r="D47" s="16"/>
+      <c r="E47" s="16"/>
+      <c r="F47" s="14" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="G47" s="5"/>
-      <c r="H47" s="8"/>
+      <c r="G47" s="14"/>
+      <c r="H47" s="17"/>
       <c r="I47" s="9" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="J47" s="10" t="str">
+      <c r="J47" s="18" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="K47" s="10" t="str">
+      <c r="K47" s="18" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
@@ -2962,36 +3526,36 @@
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="N47" s="5" t="str">
+      <c r="N47" s="14" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="O47" s="11"/>
-      <c r="P47" s="12"/>
-    </row>
-    <row r="48" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="13">
-        <v>46</v>
-      </c>
-      <c r="B48" s="14"/>
-      <c r="C48" s="22"/>
-      <c r="D48" s="16"/>
-      <c r="E48" s="16"/>
-      <c r="F48" s="14" t="str">
+      <c r="O47" s="19"/>
+      <c r="P47" s="20"/>
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A48" s="4">
+        <v>45</v>
+      </c>
+      <c r="B48" s="5"/>
+      <c r="C48" s="21"/>
+      <c r="D48" s="7"/>
+      <c r="E48" s="7"/>
+      <c r="F48" s="5" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="G48" s="14"/>
-      <c r="H48" s="17"/>
+      <c r="G48" s="5"/>
+      <c r="H48" s="8"/>
       <c r="I48" s="9" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="J48" s="18" t="str">
+      <c r="J48" s="10" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="K48" s="18" t="str">
+      <c r="K48" s="10" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
@@ -3003,36 +3567,36 @@
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="N48" s="14" t="str">
+      <c r="N48" s="5" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="O48" s="19"/>
-      <c r="P48" s="20"/>
-    </row>
-    <row r="49" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="4">
-        <v>47</v>
-      </c>
-      <c r="B49" s="5"/>
-      <c r="C49" s="21"/>
-      <c r="D49" s="7"/>
-      <c r="E49" s="7"/>
-      <c r="F49" s="5" t="str">
+      <c r="O48" s="11"/>
+      <c r="P48" s="12"/>
+    </row>
+    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A49" s="13">
+        <v>46</v>
+      </c>
+      <c r="B49" s="14"/>
+      <c r="C49" s="22"/>
+      <c r="D49" s="16"/>
+      <c r="E49" s="16"/>
+      <c r="F49" s="14" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="G49" s="5"/>
-      <c r="H49" s="8"/>
+      <c r="G49" s="14"/>
+      <c r="H49" s="17"/>
       <c r="I49" s="9" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="J49" s="10" t="str">
+      <c r="J49" s="18" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="K49" s="10" t="str">
+      <c r="K49" s="18" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
@@ -3044,190 +3608,126 @@
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="N49" s="5" t="str">
+      <c r="N49" s="14" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="O49" s="11"/>
-      <c r="P49" s="12"/>
+      <c r="O49" s="19"/>
+      <c r="P49" s="20"/>
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A50" s="13">
-        <v>9</v>
-      </c>
-      <c r="B50" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="C50" s="22" t="s">
-        <v>56</v>
-      </c>
-      <c r="D50" s="16">
-        <v>46175</v>
-      </c>
-      <c r="E50" s="16">
-        <v>46178</v>
-      </c>
-      <c r="F50" s="14">
+      <c r="A50" s="4">
+        <v>47</v>
+      </c>
+      <c r="B50" s="5"/>
+      <c r="C50" s="21"/>
+      <c r="D50" s="7"/>
+      <c r="E50" s="7"/>
+      <c r="F50" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>3</v>
-      </c>
-      <c r="G50" s="14">
-        <v>5</v>
-      </c>
-      <c r="H50" s="17">
-        <v>364.5</v>
-      </c>
-      <c r="I50" s="9"/>
-      <c r="J50" s="18">
-        <v>328.67</v>
-      </c>
-      <c r="K50" s="18">
+        <v/>
+      </c>
+      <c r="G50" s="5"/>
+      <c r="H50" s="8"/>
+      <c r="I50" s="9" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="J50" s="10" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="K50" s="10" t="str">
         <f t="shared" si="10"/>
-        <v>82.167500000000004</v>
-      </c>
-      <c r="L50" s="9"/>
-      <c r="M50" s="9"/>
-      <c r="N50" s="14" t="str">
+        <v/>
+      </c>
+      <c r="L50" s="9" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="M50" s="9" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="N50" s="5" t="str">
         <f t="shared" ca="1" si="13"/>
-        <v>🔵 À venir</v>
-      </c>
-      <c r="O50" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="P50" s="20" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A51" s="13">
-        <v>10</v>
-      </c>
-      <c r="B51" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="C51" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="D51" s="16">
-        <v>46143</v>
-      </c>
-      <c r="E51" s="16">
-        <v>46144</v>
-      </c>
-      <c r="F51" s="14">
-        <f t="shared" ref="F51" si="14">IF(AND(D51&lt;&gt;"",E51&lt;&gt;""),E51-D51,"")</f>
-        <v>1</v>
-      </c>
-      <c r="G51" s="14">
-        <v>3</v>
-      </c>
-      <c r="H51" s="17">
-        <v>130</v>
-      </c>
-      <c r="I51" s="9" t="str">
-        <f t="shared" ref="I51" si="15">IF(B51="Direto","",IF(B51="Airbnb",IF(H51&lt;&gt;"",H51*0.03+H51*0.03*0.2,""),IF(B51="Booking.com",IF(H51&lt;&gt;"",H51*0.15+H51*0.014,""),"")))</f>
-        <v/>
-      </c>
-      <c r="J51" s="18">
-        <f t="shared" ref="J51" si="16">IF(B51="Direto",IF(H51&lt;&gt;"",H51,""),IF(H51&lt;&gt;"",H51-IF(I51&lt;&gt;"",I51,0),""))</f>
-        <v>130</v>
-      </c>
-      <c r="K51" s="18">
-        <f t="shared" ref="K51" si="17">IF(J51&lt;&gt;"",J51*0.25,"")</f>
-        <v>32.5</v>
-      </c>
-      <c r="L51" s="9" t="str">
-        <f t="shared" ref="L51" si="18">IF(B51="Airbnb",IF(H51&lt;&gt;"",H51*0.03,""),IF(B51="Booking.com",IF(H51&lt;&gt;"",H51*0.15,""),""))</f>
-        <v/>
-      </c>
-      <c r="M51" s="9" t="str">
-        <f t="shared" ref="M51" si="19">IF(B51="Airbnb",IF(L51&lt;&gt;"",L51*0.2,""),IF(B51="Booking.com",IF(H51&lt;&gt;"",H51*0.014,""),""))</f>
-        <v/>
-      </c>
-      <c r="N51" s="14" t="str">
-        <f t="shared" ref="N51" ca="1" si="20">IF(D51="","",IF(E51&lt;TODAY(),"✅ Terminée",IF(D51&lt;=TODAY(),"🟡 En cours","🔵 À venir")))</f>
-        <v>🔵 À venir</v>
-      </c>
-      <c r="O51" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="P51" s="20" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="52" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="39" t="s">
+        <v/>
+      </c>
+      <c r="O50" s="11"/>
+      <c r="P50" s="12"/>
+    </row>
+    <row r="51" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="B52" s="39"/>
-      <c r="C52" s="39"/>
-      <c r="D52" s="39"/>
-      <c r="E52" s="39"/>
-      <c r="F52" s="39"/>
-      <c r="G52" s="39"/>
-      <c r="H52" s="23">
-        <f t="shared" ref="H52:M52" si="21">SUMIF(H3:H51,"&gt;0")</f>
-        <v>3598.54</v>
-      </c>
-      <c r="I52" s="24">
-        <f t="shared" si="21"/>
-        <v>401.54255999999998</v>
-      </c>
-      <c r="J52" s="23">
-        <f t="shared" si="21"/>
-        <v>3103.3274399999996</v>
-      </c>
-      <c r="K52" s="23">
-        <f t="shared" si="21"/>
-        <v>775.83185999999989</v>
-      </c>
-      <c r="L52" s="24">
-        <f t="shared" si="21"/>
-        <v>364.80599999999998</v>
-      </c>
-      <c r="M52" s="24">
-        <f t="shared" si="21"/>
-        <v>36.736560000000004</v>
-      </c>
-      <c r="N52" s="25" t="str">
+      <c r="B51" s="38"/>
+      <c r="C51" s="38"/>
+      <c r="D51" s="38"/>
+      <c r="E51" s="38"/>
+      <c r="F51" s="38"/>
+      <c r="G51" s="38"/>
+      <c r="H51" s="23">
+        <f>SUMIF(H3:H50,"&gt;0")</f>
+        <v>5088.54</v>
+      </c>
+      <c r="I51" s="24">
+        <f>SUMIF(I3:I50,"&gt;0")</f>
+        <v>645.90255999999999</v>
+      </c>
+      <c r="J51" s="23">
+        <f>SUMIF(J3:J50,"&gt;0")</f>
+        <v>4348.9674399999994</v>
+      </c>
+      <c r="K51" s="23">
+        <f>SUMIF(K3:K50,"&gt;0")</f>
+        <v>1087.2418599999999</v>
+      </c>
+      <c r="L51" s="24">
+        <f>SUMIF(L3:L50,"&gt;0")</f>
+        <v>588.30600000000004</v>
+      </c>
+      <c r="M51" s="24">
+        <f>SUMIF(M3:M50,"&gt;0")</f>
+        <v>57.596560000000011</v>
+      </c>
+      <c r="N51" s="25" t="str">
         <f ca="1">COUNTIF(N3:N10,"✅ Terminée")&amp;" terminée(s)"</f>
-        <v>3 terminée(s)</v>
-      </c>
-      <c r="O52" s="26"/>
-      <c r="P52" s="26"/>
-    </row>
-    <row r="53" spans="1:16" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J53" s="27">
-        <f>J52-K52</f>
-        <v>2327.4955799999998</v>
-      </c>
-    </row>
-    <row r="54" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="40" t="s">
+        <v>5 terminée(s)</v>
+      </c>
+      <c r="O51" s="26"/>
+      <c r="P51" s="26"/>
+    </row>
+    <row r="52" spans="1:16" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J52" s="27">
+        <f>J51-K51</f>
+        <v>3261.7255799999994</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="40" t="s">
         <v>27</v>
       </c>
-      <c r="B54" s="40"/>
-      <c r="C54" s="40"/>
-      <c r="D54" s="40"/>
-      <c r="E54" s="40"/>
-      <c r="F54" s="40"/>
-      <c r="G54" s="40"/>
-      <c r="H54" s="40"/>
-      <c r="I54" s="40"/>
-      <c r="J54" s="40"/>
-      <c r="K54" s="40"/>
-      <c r="L54" s="40"/>
-      <c r="M54" s="40"/>
-      <c r="N54" s="40"/>
-      <c r="O54" s="40"/>
-      <c r="P54" s="40"/>
-    </row>
-    <row r="55" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="B53" s="40"/>
+      <c r="C53" s="40"/>
+      <c r="D53" s="40"/>
+      <c r="E53" s="40"/>
+      <c r="F53" s="40"/>
+      <c r="G53" s="40"/>
+      <c r="H53" s="40"/>
+      <c r="I53" s="40"/>
+      <c r="J53" s="40"/>
+      <c r="K53" s="40"/>
+      <c r="L53" s="40"/>
+      <c r="M53" s="40"/>
+      <c r="N53" s="40"/>
+      <c r="O53" s="40"/>
+      <c r="P53" s="40"/>
+    </row>
+    <row r="54" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="2">
     <mergeCell ref="A1:P1"/>
-    <mergeCell ref="A52:G52"/>
-    <mergeCell ref="A54:P54"/>
+    <mergeCell ref="A53:P53"/>
   </mergeCells>
   <conditionalFormatting sqref="B1:B1048576">
     <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="booking">
@@ -3238,17 +3738,20 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" sqref="B3:B51" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="B3:B50" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Airbnb,Booking.com,Direto"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="O3:O51" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="O3:O50" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"A definir,Manhã,Tarde,Noite,08h00,09h00,10h00,11h00,12h00,13h00,14h00,15h00,16h00,17h00,18h00,19h00,20h00,21h00,22h00"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 

--- a/Casa_do_Mosteiro_v6.xlsx
+++ b/Casa_do_Mosteiro_v6.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Patrick SALVADOR\Documents\Immobilier\Locations - Airbnb - Booking\Casa do mosteiro - Aluguer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AE64396-3160-4EB3-A9E2-682788976357}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D5D89BF-3FA6-49C4-8840-6AF6474188D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="67">
   <si>
     <t>🏠  CASA DO MOSTEIRO — Réservations</t>
   </si>
@@ -103,12 +103,6 @@
     <t>María Isabel Moreno Montoro</t>
   </si>
   <si>
-    <t>Rubén Rivas lópez</t>
-  </si>
-  <si>
-    <t>TOTAUX</t>
-  </si>
-  <si>
     <t>🔵 Azul = introdução manual   ⚫ Preto = cálculo automático   🔒 Cinzento = calculado automaticamente   Direto: preço bruto = líquido, sem comissão   Airbnb: comissão 3% + TVA 20%   Booking: comissão 15% + fr.banc. 1.4%</t>
   </si>
   <si>
@@ -218,6 +212,21 @@
   </si>
   <si>
     <t>00351936282687</t>
+  </si>
+  <si>
+    <t>Eva Fernandez Losada</t>
+  </si>
+  <si>
+    <t>Alex Sandro Moreira</t>
+  </si>
+  <si>
+    <t>Pedro Joao Rodrigues</t>
+  </si>
+  <si>
+    <t>+393463256052</t>
+  </si>
+  <si>
+    <t>+351960070755</t>
   </si>
 </sst>
 </file>
@@ -523,7 +532,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -644,6 +653,7 @@
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1544,10 +1554,10 @@
         <v>✅ Terminée</v>
       </c>
       <c r="O3" s="11" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="P3" s="12" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1600,10 +1610,10 @@
         <v>🔵 À venir</v>
       </c>
       <c r="O4" s="19" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="P4" s="20" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1657,10 +1667,10 @@
         <v>✅ Terminée</v>
       </c>
       <c r="O5" s="11" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="P5" s="12" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1714,10 +1724,10 @@
         <v>✅ Terminée</v>
       </c>
       <c r="O6" s="19" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="P6" s="20" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1771,10 +1781,10 @@
         <v>✅ Terminée</v>
       </c>
       <c r="O7" s="11" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="P7" s="12" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1828,10 +1838,10 @@
         <v>✅ Terminée</v>
       </c>
       <c r="O8" s="19" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="P8" s="20" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1842,7 +1852,7 @@
         <v>20</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="D9" s="7">
         <v>46150</v>
@@ -1882,13 +1892,13 @@
       </c>
       <c r="N9" s="5" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>🔵 À venir</v>
+        <v>✅ Terminée</v>
       </c>
       <c r="O9" s="11" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="P9" s="12" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
@@ -1899,7 +1909,7 @@
         <v>20</v>
       </c>
       <c r="C10" s="22" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D10" s="16">
         <v>46185</v>
@@ -1942,10 +1952,10 @@
         <v>🔵 À venir</v>
       </c>
       <c r="O10" s="19" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="P10" s="20" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1956,7 +1966,7 @@
         <v>20</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D11" s="7">
         <v>46297</v>
@@ -1999,10 +2009,10 @@
         <v>🔵 À venir</v>
       </c>
       <c r="O11" s="19" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="P11" s="20" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2013,7 +2023,7 @@
         <v>20</v>
       </c>
       <c r="C12" s="21" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D12" s="7">
         <v>46236</v>
@@ -2056,19 +2066,21 @@
         <v>🔵 À venir</v>
       </c>
       <c r="O12" s="19" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="P12" s="20" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="13"/>
+      <c r="A13" s="4">
+        <v>11</v>
+      </c>
       <c r="B13" s="5" t="s">
         <v>20</v>
       </c>
       <c r="C13" s="21" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D13" s="7">
         <v>46291</v>
@@ -2111,21 +2123,21 @@
         <v>🔵 À venir</v>
       </c>
       <c r="O13" s="19" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="P13" s="20" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C14" s="22" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D14" s="16">
         <v>46175</v>
@@ -2158,21 +2170,21 @@
         <v>🔵 À venir</v>
       </c>
       <c r="O14" s="19" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="P14" s="20" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="13">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C15" s="22" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D15" s="16">
         <v>46143</v>
@@ -2212,105 +2224,137 @@
       </c>
       <c r="N15" s="14" t="str">
         <f ca="1">IF(D15="","",IF(E15&lt;TODAY(),"✅ Terminée",IF(D15&lt;=TODAY(),"🟡 En cours","🔵 À venir")))</f>
-        <v>🔵 À venir</v>
+        <v>✅ Terminée</v>
       </c>
       <c r="O15" s="19" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="P15" s="20" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
-        <v>13</v>
-      </c>
-      <c r="B16" s="5"/>
-      <c r="C16" s="21"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="5" t="str">
+        <v>14</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="D16" s="7">
+        <v>46275</v>
+      </c>
+      <c r="E16" s="7">
+        <v>46279</v>
+      </c>
+      <c r="F16" s="5">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G16" s="5"/>
-      <c r="H16" s="8"/>
-      <c r="I16" s="9" t="str">
+        <v>4</v>
+      </c>
+      <c r="G16" s="5">
+        <v>3</v>
+      </c>
+      <c r="H16" s="8">
+        <v>600</v>
+      </c>
+      <c r="I16" s="9">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J16" s="10" t="str">
+        <v>98.4</v>
+      </c>
+      <c r="J16" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K16" s="10" t="str">
+        <v>501.6</v>
+      </c>
+      <c r="K16" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="L16" s="9" t="str">
+        <v>125.4</v>
+      </c>
+      <c r="L16" s="9">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="M16" s="9" t="str">
+        <v>90</v>
+      </c>
+      <c r="M16" s="9">
         <f t="shared" si="5"/>
-        <v/>
+        <v>8.4</v>
       </c>
       <c r="N16" s="5" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="O16" s="11"/>
-      <c r="P16" s="12"/>
+        <v>🔵 À venir</v>
+      </c>
+      <c r="O16" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="P16" s="12" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="17" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="13">
-        <v>14</v>
-      </c>
-      <c r="B17" s="14"/>
-      <c r="C17" s="22"/>
-      <c r="D17" s="16"/>
-      <c r="E17" s="16"/>
-      <c r="F17" s="14" t="str">
+      <c r="A17" s="4">
+        <v>15</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="D17" s="16">
+        <v>46521</v>
+      </c>
+      <c r="E17" s="16">
+        <v>46523</v>
+      </c>
+      <c r="F17" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G17" s="14"/>
-      <c r="H17" s="17"/>
-      <c r="I17" s="9" t="str">
+        <v>2</v>
+      </c>
+      <c r="G17" s="14">
+        <v>4</v>
+      </c>
+      <c r="H17" s="17">
+        <v>270</v>
+      </c>
+      <c r="I17" s="9">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J17" s="18" t="str">
+        <v>44.28</v>
+      </c>
+      <c r="J17" s="37">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K17" s="18" t="str">
+        <v>225.72</v>
+      </c>
+      <c r="K17" s="18">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="L17" s="9" t="str">
+        <v>56.43</v>
+      </c>
+      <c r="L17" s="9">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="M17" s="9" t="str">
+        <v>40.5</v>
+      </c>
+      <c r="M17" s="9">
         <f t="shared" si="5"/>
-        <v/>
+        <v>3.7800000000000002</v>
       </c>
       <c r="N17" s="14" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="O17" s="19"/>
-      <c r="P17" s="20"/>
+        <v>🔵 À venir</v>
+      </c>
+      <c r="O17" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="P17" s="20" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="18" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="4">
-        <v>15</v>
+      <c r="A18" s="13">
+        <v>16</v>
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="21"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="16"/>
       <c r="F18" s="5" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2345,8 +2389,8 @@
       <c r="P18" s="12"/>
     </row>
     <row r="19" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="13">
-        <v>16</v>
+      <c r="A19" s="4">
+        <v>17</v>
       </c>
       <c r="B19" s="14"/>
       <c r="C19" s="22"/>
@@ -2386,13 +2430,13 @@
       <c r="P19" s="20"/>
     </row>
     <row r="20" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="4">
-        <v>17</v>
+      <c r="A20" s="13">
+        <v>18</v>
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="21"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="16"/>
       <c r="F20" s="5" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2427,8 +2471,8 @@
       <c r="P20" s="12"/>
     </row>
     <row r="21" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="13">
-        <v>18</v>
+      <c r="A21" s="4">
+        <v>19</v>
       </c>
       <c r="B21" s="14"/>
       <c r="C21" s="22"/>
@@ -2469,7 +2513,7 @@
     </row>
     <row r="22" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="21"/>
@@ -2510,7 +2554,7 @@
     </row>
     <row r="23" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="13">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B23" s="14"/>
       <c r="C23" s="22"/>
@@ -2551,27 +2595,27 @@
     </row>
     <row r="24" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="21"/>
       <c r="D24" s="7"/>
       <c r="E24" s="7"/>
-      <c r="F24" s="5" t="str">
+      <c r="F24" s="14" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="G24" s="5"/>
-      <c r="H24" s="8"/>
+      <c r="H24" s="17"/>
       <c r="I24" s="9" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J24" s="10" t="str">
+      <c r="J24" s="18" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K24" s="10" t="str">
+      <c r="K24" s="18" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -2583,26 +2627,26 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N24" s="5" t="str">
+      <c r="N24" s="14" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="O24" s="11"/>
-      <c r="P24" s="12"/>
+      <c r="O24" s="19"/>
+      <c r="P24" s="20"/>
     </row>
     <row r="25" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="13">
-        <v>22</v>
+      <c r="A25" s="4">
+        <v>23</v>
       </c>
       <c r="B25" s="14"/>
       <c r="C25" s="22"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="16"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
       <c r="F25" s="14" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G25" s="14"/>
+      <c r="G25" s="5"/>
       <c r="H25" s="17"/>
       <c r="I25" s="9" t="str">
         <f t="shared" si="1"/>
@@ -2632,28 +2676,28 @@
       <c r="P25" s="20"/>
     </row>
     <row r="26" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="4">
-        <v>23</v>
+      <c r="A26" s="13">
+        <v>24</v>
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="21"/>
       <c r="D26" s="7"/>
       <c r="E26" s="7"/>
-      <c r="F26" s="5" t="str">
+      <c r="F26" s="14" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="G26" s="5"/>
-      <c r="H26" s="8"/>
+      <c r="H26" s="17"/>
       <c r="I26" s="9" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J26" s="10" t="str">
+      <c r="J26" s="18" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K26" s="10" t="str">
+      <c r="K26" s="18" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -2665,16 +2709,16 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N26" s="5" t="str">
+      <c r="N26" s="14" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="O26" s="11"/>
-      <c r="P26" s="12"/>
+      <c r="O26" s="19"/>
+      <c r="P26" s="20"/>
     </row>
     <row r="27" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="13">
-        <v>24</v>
+      <c r="A27" s="4">
+        <v>25</v>
       </c>
       <c r="B27" s="14"/>
       <c r="C27" s="22"/>
@@ -2714,28 +2758,28 @@
       <c r="P27" s="20"/>
     </row>
     <row r="28" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="4">
-        <v>25</v>
+      <c r="A28" s="13">
+        <v>26</v>
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="21"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="5" t="str">
+      <c r="D28" s="16"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="14" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G28" s="5"/>
-      <c r="H28" s="8"/>
+      <c r="G28" s="14"/>
+      <c r="H28" s="17"/>
       <c r="I28" s="9" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J28" s="10" t="str">
+      <c r="J28" s="18" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K28" s="10" t="str">
+      <c r="K28" s="18" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -2747,36 +2791,36 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N28" s="5" t="str">
+      <c r="N28" s="14" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="O28" s="11"/>
-      <c r="P28" s="12"/>
+      <c r="O28" s="19"/>
+      <c r="P28" s="20"/>
     </row>
     <row r="29" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="13">
-        <v>26</v>
+      <c r="A29" s="4">
+        <v>27</v>
       </c>
       <c r="B29" s="14"/>
       <c r="C29" s="22"/>
-      <c r="D29" s="16"/>
-      <c r="E29" s="16"/>
-      <c r="F29" s="14" t="str">
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="5" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G29" s="14"/>
-      <c r="H29" s="17"/>
+      <c r="G29" s="5"/>
+      <c r="H29" s="8"/>
       <c r="I29" s="9" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J29" s="18" t="str">
+      <c r="J29" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K29" s="18" t="str">
+      <c r="K29" s="10" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -2788,36 +2832,36 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N29" s="14" t="str">
+      <c r="N29" s="5" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="O29" s="19"/>
-      <c r="P29" s="20"/>
+      <c r="O29" s="11"/>
+      <c r="P29" s="12"/>
     </row>
     <row r="30" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="4">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="21"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="7"/>
-      <c r="F30" s="5" t="str">
+      <c r="D30" s="16"/>
+      <c r="E30" s="16"/>
+      <c r="F30" s="14" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G30" s="5"/>
-      <c r="H30" s="8"/>
+      <c r="G30" s="14"/>
+      <c r="H30" s="17"/>
       <c r="I30" s="9" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J30" s="10" t="str">
+      <c r="J30" s="37" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K30" s="10" t="str">
+      <c r="K30" s="18" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -2829,36 +2873,36 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N30" s="5" t="str">
+      <c r="N30" s="14" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="O30" s="11"/>
-      <c r="P30" s="12"/>
+      <c r="O30" s="19"/>
+      <c r="P30" s="20"/>
     </row>
     <row r="31" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="13">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B31" s="14"/>
       <c r="C31" s="22"/>
       <c r="D31" s="16"/>
       <c r="E31" s="16"/>
-      <c r="F31" s="14" t="str">
+      <c r="F31" s="5" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G31" s="14"/>
-      <c r="H31" s="17"/>
+      <c r="G31" s="5"/>
+      <c r="H31" s="8"/>
       <c r="I31" s="9" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J31" s="18" t="str">
+      <c r="J31" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K31" s="18" t="str">
+      <c r="K31" s="10" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -2870,36 +2914,36 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N31" s="14" t="str">
+      <c r="N31" s="5" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="O31" s="19"/>
-      <c r="P31" s="20"/>
+      <c r="O31" s="11"/>
+      <c r="P31" s="12"/>
     </row>
     <row r="32" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="4">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="21"/>
-      <c r="D32" s="7"/>
-      <c r="E32" s="7"/>
-      <c r="F32" s="5" t="str">
+      <c r="D32" s="16"/>
+      <c r="E32" s="16"/>
+      <c r="F32" s="14" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G32" s="5"/>
-      <c r="H32" s="8"/>
+      <c r="G32" s="14"/>
+      <c r="H32" s="17"/>
       <c r="I32" s="9" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J32" s="10" t="str">
+      <c r="J32" s="18" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K32" s="10" t="str">
+      <c r="K32" s="18" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -2911,36 +2955,36 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N32" s="5" t="str">
+      <c r="N32" s="14" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="O32" s="11"/>
-      <c r="P32" s="12"/>
+      <c r="O32" s="19"/>
+      <c r="P32" s="20"/>
     </row>
     <row r="33" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="13">
-        <v>30</v>
+      <c r="A33" s="4">
+        <v>31</v>
       </c>
       <c r="B33" s="14"/>
       <c r="C33" s="22"/>
       <c r="D33" s="16"/>
       <c r="E33" s="16"/>
-      <c r="F33" s="14" t="str">
+      <c r="F33" s="5" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G33" s="14"/>
-      <c r="H33" s="17"/>
+      <c r="G33" s="5"/>
+      <c r="H33" s="8"/>
       <c r="I33" s="9" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J33" s="18" t="str">
+      <c r="J33" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K33" s="18" t="str">
+      <c r="K33" s="10" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -2952,36 +2996,36 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N33" s="14" t="str">
+      <c r="N33" s="5" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="O33" s="19"/>
-      <c r="P33" s="20"/>
+      <c r="O33" s="11"/>
+      <c r="P33" s="12"/>
     </row>
     <row r="34" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="4">
-        <v>31</v>
+      <c r="A34" s="13">
+        <v>32</v>
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="21"/>
-      <c r="D34" s="7"/>
-      <c r="E34" s="7"/>
-      <c r="F34" s="5" t="str">
+      <c r="D34" s="16"/>
+      <c r="E34" s="16"/>
+      <c r="F34" s="14" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G34" s="5"/>
-      <c r="H34" s="8"/>
+      <c r="G34" s="14"/>
+      <c r="H34" s="17"/>
       <c r="I34" s="9" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J34" s="10" t="str">
+      <c r="J34" s="18" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K34" s="10" t="str">
+      <c r="K34" s="18" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -2993,36 +3037,36 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N34" s="5" t="str">
+      <c r="N34" s="14" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="O34" s="11"/>
-      <c r="P34" s="12"/>
+      <c r="O34" s="19"/>
+      <c r="P34" s="20"/>
     </row>
     <row r="35" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="13">
-        <v>32</v>
+      <c r="A35" s="4">
+        <v>33</v>
       </c>
       <c r="B35" s="14"/>
       <c r="C35" s="22"/>
-      <c r="D35" s="16"/>
-      <c r="E35" s="16"/>
-      <c r="F35" s="14" t="str">
+      <c r="D35" s="7"/>
+      <c r="E35" s="7"/>
+      <c r="F35" s="5" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G35" s="14"/>
-      <c r="H35" s="17"/>
+      <c r="G35" s="5"/>
+      <c r="H35" s="8"/>
       <c r="I35" s="9" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J35" s="18" t="str">
+      <c r="J35" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K35" s="18" t="str">
+      <c r="K35" s="10" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -3034,36 +3078,36 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N35" s="14" t="str">
+      <c r="N35" s="5" t="str">
         <f t="shared" ca="1" si="6"/>
         <v/>
       </c>
-      <c r="O35" s="19"/>
-      <c r="P35" s="20"/>
+      <c r="O35" s="11"/>
+      <c r="P35" s="12"/>
     </row>
     <row r="36" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="4">
-        <v>33</v>
+      <c r="A36" s="13">
+        <v>34</v>
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="21"/>
-      <c r="D36" s="7"/>
-      <c r="E36" s="7"/>
-      <c r="F36" s="5" t="str">
+      <c r="D36" s="16"/>
+      <c r="E36" s="16"/>
+      <c r="F36" s="14" t="str">
         <f t="shared" ref="F36:F50" si="7">IF(AND(D36&lt;&gt;"",E36&lt;&gt;""),E36-D36,"")</f>
         <v/>
       </c>
-      <c r="G36" s="5"/>
-      <c r="H36" s="8"/>
+      <c r="G36" s="14"/>
+      <c r="H36" s="17"/>
       <c r="I36" s="9" t="str">
         <f t="shared" ref="I36:I50" si="8">IF(B36="Direto","",IF(B36="Airbnb",IF(H36&lt;&gt;"",H36*0.03+H36*0.03*0.2,""),IF(B36="Booking.com",IF(H36&lt;&gt;"",H36*0.15+H36*0.014,""),"")))</f>
         <v/>
       </c>
-      <c r="J36" s="10" t="str">
+      <c r="J36" s="18" t="str">
         <f t="shared" ref="J36:J50" si="9">IF(B36="Direto",IF(H36&lt;&gt;"",H36,""),IF(H36&lt;&gt;"",H36-IF(I36&lt;&gt;"",I36,0),""))</f>
         <v/>
       </c>
-      <c r="K36" s="10" t="str">
+      <c r="K36" s="18" t="str">
         <f t="shared" ref="K36:K50" si="10">IF(J36&lt;&gt;"",J36*0.25,"")</f>
         <v/>
       </c>
@@ -3075,26 +3119,26 @@
         <f t="shared" ref="M36:M50" si="12">IF(B36="Airbnb",IF(L36&lt;&gt;"",L36*0.2,""),IF(B36="Booking.com",IF(H36&lt;&gt;"",H36*0.014,""),""))</f>
         <v/>
       </c>
-      <c r="N36" s="5" t="str">
+      <c r="N36" s="14" t="str">
         <f t="shared" ref="N36:N50" ca="1" si="13">IF(D36="","",IF(E36&lt;TODAY(),"✅ Terminée",IF(D36&lt;=TODAY(),"🟡 En cours","🔵 À venir")))</f>
         <v/>
       </c>
-      <c r="O36" s="11"/>
-      <c r="P36" s="12"/>
+      <c r="O36" s="19"/>
+      <c r="P36" s="20"/>
     </row>
     <row r="37" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="13">
-        <v>34</v>
+      <c r="A37" s="4">
+        <v>35</v>
       </c>
       <c r="B37" s="14"/>
       <c r="C37" s="22"/>
-      <c r="D37" s="16"/>
-      <c r="E37" s="16"/>
+      <c r="D37" s="7"/>
+      <c r="E37" s="7"/>
       <c r="F37" s="14" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="G37" s="14"/>
+      <c r="G37" s="5"/>
       <c r="H37" s="17"/>
       <c r="I37" s="9" t="str">
         <f t="shared" si="8"/>
@@ -3125,27 +3169,27 @@
     </row>
     <row r="38" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="4">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="21"/>
       <c r="D38" s="7"/>
       <c r="E38" s="7"/>
-      <c r="F38" s="5" t="str">
+      <c r="F38" s="14" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="G38" s="5"/>
-      <c r="H38" s="8"/>
+      <c r="H38" s="17"/>
       <c r="I38" s="9" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="J38" s="10" t="str">
+      <c r="J38" s="18" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="K38" s="10" t="str">
+      <c r="K38" s="18" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
@@ -3157,26 +3201,26 @@
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="N38" s="5" t="str">
+      <c r="N38" s="14" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="O38" s="11"/>
-      <c r="P38" s="12"/>
+      <c r="O38" s="19"/>
+      <c r="P38" s="20"/>
     </row>
     <row r="39" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="13">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B39" s="14"/>
       <c r="C39" s="22"/>
-      <c r="D39" s="16"/>
-      <c r="E39" s="16"/>
+      <c r="D39" s="7"/>
+      <c r="E39" s="7"/>
       <c r="F39" s="14" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="G39" s="14"/>
+      <c r="G39" s="5"/>
       <c r="H39" s="17"/>
       <c r="I39" s="9" t="str">
         <f t="shared" si="8"/>
@@ -3207,27 +3251,27 @@
     </row>
     <row r="40" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="4">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="21"/>
-      <c r="D40" s="7"/>
-      <c r="E40" s="7"/>
-      <c r="F40" s="5" t="str">
+      <c r="D40" s="16"/>
+      <c r="E40" s="16"/>
+      <c r="F40" s="14" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="G40" s="5"/>
-      <c r="H40" s="8"/>
+      <c r="G40" s="14"/>
+      <c r="H40" s="17"/>
       <c r="I40" s="9" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="J40" s="10" t="str">
+      <c r="J40" s="18" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="K40" s="10" t="str">
+      <c r="K40" s="18" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
@@ -3239,16 +3283,16 @@
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="N40" s="5" t="str">
+      <c r="N40" s="14" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="O40" s="11"/>
-      <c r="P40" s="12"/>
+      <c r="O40" s="19"/>
+      <c r="P40" s="20"/>
     </row>
     <row r="41" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="13">
-        <v>38</v>
+      <c r="A41" s="4">
+        <v>39</v>
       </c>
       <c r="B41" s="14"/>
       <c r="C41" s="22"/>
@@ -3288,8 +3332,8 @@
       <c r="P41" s="20"/>
     </row>
     <row r="42" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="4">
-        <v>39</v>
+      <c r="A42" s="13">
+        <v>40</v>
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="21"/>
@@ -3329,8 +3373,8 @@
       <c r="P42" s="12"/>
     </row>
     <row r="43" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="13">
-        <v>40</v>
+      <c r="A43" s="4">
+        <v>41</v>
       </c>
       <c r="B43" s="14"/>
       <c r="C43" s="22"/>
@@ -3346,7 +3390,7 @@
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="J43" s="18" t="str">
+      <c r="J43" s="37" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -3370,13 +3414,13 @@
       <c r="P43" s="20"/>
     </row>
     <row r="44" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="4">
-        <v>41</v>
+      <c r="A44" s="13">
+        <v>42</v>
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="21"/>
-      <c r="D44" s="7"/>
-      <c r="E44" s="7"/>
+      <c r="D44" s="16"/>
+      <c r="E44" s="16"/>
       <c r="F44" s="5" t="str">
         <f t="shared" si="7"/>
         <v/>
@@ -3411,8 +3455,8 @@
       <c r="P44" s="12"/>
     </row>
     <row r="45" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="13">
-        <v>42</v>
+      <c r="A45" s="4">
+        <v>43</v>
       </c>
       <c r="B45" s="14"/>
       <c r="C45" s="22"/>
@@ -3453,12 +3497,12 @@
     </row>
     <row r="46" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="4">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="21"/>
-      <c r="D46" s="7"/>
-      <c r="E46" s="7"/>
+      <c r="D46" s="16"/>
+      <c r="E46" s="16"/>
       <c r="F46" s="5" t="str">
         <f t="shared" si="7"/>
         <v/>
@@ -3494,7 +3538,7 @@
     </row>
     <row r="47" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="13">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B47" s="14"/>
       <c r="C47" s="22"/>
@@ -3535,7 +3579,7 @@
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A48" s="4">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="21"/>
@@ -3575,8 +3619,8 @@
       <c r="P48" s="12"/>
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A49" s="13">
-        <v>46</v>
+      <c r="A49" s="4">
+        <v>47</v>
       </c>
       <c r="B49" s="14"/>
       <c r="C49" s="22"/>
@@ -3616,28 +3660,28 @@
       <c r="P49" s="20"/>
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A50" s="4">
-        <v>47</v>
+      <c r="A50" s="13">
+        <v>48</v>
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="21"/>
       <c r="D50" s="7"/>
       <c r="E50" s="7"/>
-      <c r="F50" s="5" t="str">
+      <c r="F50" s="14" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="G50" s="5"/>
-      <c r="H50" s="8"/>
+      <c r="H50" s="17"/>
       <c r="I50" s="9" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="J50" s="10" t="str">
+      <c r="J50" s="18" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="K50" s="10" t="str">
+      <c r="K50" s="18" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
@@ -3649,16 +3693,16 @@
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="N50" s="5" t="str">
+      <c r="N50" s="14" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="O50" s="11"/>
-      <c r="P50" s="12"/>
+      <c r="O50" s="19"/>
+      <c r="P50" s="20"/>
     </row>
     <row r="51" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="38" t="s">
-        <v>26</v>
+      <c r="A51" s="4">
+        <v>49</v>
       </c>
       <c r="B51" s="38"/>
       <c r="C51" s="38"/>
@@ -3667,32 +3711,32 @@
       <c r="F51" s="38"/>
       <c r="G51" s="38"/>
       <c r="H51" s="23">
-        <f>SUMIF(H3:H50,"&gt;0")</f>
-        <v>5088.54</v>
+        <f t="shared" ref="H51:M51" si="14">SUMIF(H3:H50,"&gt;0")</f>
+        <v>5958.54</v>
       </c>
       <c r="I51" s="24">
-        <f>SUMIF(I3:I50,"&gt;0")</f>
-        <v>645.90255999999999</v>
+        <f t="shared" si="14"/>
+        <v>788.58255999999994</v>
       </c>
       <c r="J51" s="23">
-        <f>SUMIF(J3:J50,"&gt;0")</f>
-        <v>4348.9674399999994</v>
+        <f t="shared" si="14"/>
+        <v>5076.2874400000001</v>
       </c>
       <c r="K51" s="23">
-        <f>SUMIF(K3:K50,"&gt;0")</f>
-        <v>1087.2418599999999</v>
+        <f t="shared" si="14"/>
+        <v>1269.07186</v>
       </c>
       <c r="L51" s="24">
-        <f>SUMIF(L3:L50,"&gt;0")</f>
-        <v>588.30600000000004</v>
+        <f t="shared" si="14"/>
+        <v>718.80600000000004</v>
       </c>
       <c r="M51" s="24">
-        <f>SUMIF(M3:M50,"&gt;0")</f>
-        <v>57.596560000000011</v>
+        <f t="shared" si="14"/>
+        <v>69.776560000000018</v>
       </c>
       <c r="N51" s="25" t="str">
         <f ca="1">COUNTIF(N3:N10,"✅ Terminée")&amp;" terminée(s)"</f>
-        <v>5 terminée(s)</v>
+        <v>6 terminée(s)</v>
       </c>
       <c r="O51" s="26"/>
       <c r="P51" s="26"/>
@@ -3700,12 +3744,12 @@
     <row r="52" spans="1:16" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J52" s="27">
         <f>J51-K51</f>
-        <v>3261.7255799999994</v>
+        <v>3807.21558</v>
       </c>
     </row>
     <row r="53" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="40" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B53" s="40"/>
       <c r="C53" s="40"/>
@@ -3723,7 +3767,12 @@
       <c r="O53" s="40"/>
       <c r="P53" s="40"/>
     </row>
-    <row r="54" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J54" s="42">
+        <f>J52*0.94</f>
+        <v>3578.7826451999999</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:P1"/>
@@ -3771,7 +3820,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="41" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B1" s="41"/>
       <c r="C1" s="41"/>
@@ -3779,42 +3828,42 @@
     </row>
     <row r="2" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" s="28" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="28" t="s">
+      <c r="D2" s="28" t="s">
         <v>30</v>
-      </c>
-      <c r="C2" s="28" t="s">
-        <v>31</v>
-      </c>
-      <c r="D2" s="28" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" s="30" t="s">
         <v>33</v>
       </c>
-      <c r="B3" s="30" t="s">
+      <c r="D3" s="30" t="s">
         <v>34</v>
-      </c>
-      <c r="C3" s="30" t="s">
-        <v>35</v>
-      </c>
-      <c r="D3" s="30" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="31"/>
       <c r="B4" s="32" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" s="32" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" s="32" t="s">
         <v>37</v>
-      </c>
-      <c r="C4" s="32" t="s">
-        <v>38</v>
-      </c>
-      <c r="D4" s="32" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">

--- a/Casa_do_Mosteiro_v6.xlsx
+++ b/Casa_do_Mosteiro_v6.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Patrick SALVADOR\Documents\Immobilier\Locations - Airbnb - Booking\Casa do mosteiro - Aluguer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D5D89BF-3FA6-49C4-8840-6AF6474188D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BC2C3F7-B026-4466-9770-49937CA4666F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="71">
   <si>
     <t>🏠  CASA DO MOSTEIRO — Réservations</t>
   </si>
@@ -227,6 +227,18 @@
   </si>
   <si>
     <t>+351960070755</t>
+  </si>
+  <si>
+    <t>Adelina Neves</t>
+  </si>
+  <si>
+    <t>+351935023820</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>y</t>
   </si>
 </sst>
 </file>
@@ -646,6 +658,7 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -653,7 +666,6 @@
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1434,24 +1446,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
-      <c r="J1" s="39"/>
-      <c r="K1" s="39"/>
-      <c r="L1" s="39"/>
-      <c r="M1" s="39"/>
-      <c r="N1" s="39"/>
-      <c r="O1" s="39"/>
-      <c r="P1" s="39"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="40"/>
+      <c r="K1" s="40"/>
+      <c r="L1" s="40"/>
+      <c r="M1" s="40"/>
+      <c r="N1" s="40"/>
+      <c r="O1" s="40"/>
+      <c r="P1" s="40"/>
     </row>
     <row r="2" spans="1:16" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -2167,7 +2179,7 @@
       <c r="M14" s="9"/>
       <c r="N14" s="14" t="str">
         <f ca="1">IF(D14="","",IF(E14&lt;TODAY(),"✅ Terminée",IF(D14&lt;=TODAY(),"🟡 En cours","🔵 À venir")))</f>
-        <v>🔵 À venir</v>
+        <v>🟡 En cours</v>
       </c>
       <c r="O14" s="19" t="s">
         <v>39</v>
@@ -2347,72 +2359,100 @@
         <v>66</v>
       </c>
     </row>
-    <row r="18" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="13">
         <v>16</v>
       </c>
-      <c r="B18" s="5"/>
-      <c r="C18" s="21"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="16"/>
-      <c r="F18" s="5" t="str">
+      <c r="B18" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="D18" s="16">
+        <v>46166</v>
+      </c>
+      <c r="E18" s="16">
+        <v>46169</v>
+      </c>
+      <c r="F18" s="5">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G18" s="5"/>
-      <c r="H18" s="8"/>
-      <c r="I18" s="9" t="str">
+        <v>3</v>
+      </c>
+      <c r="G18" s="5">
+        <v>4</v>
+      </c>
+      <c r="H18" s="8">
+        <v>405</v>
+      </c>
+      <c r="I18" s="9">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J18" s="10" t="str">
+        <v>14.58</v>
+      </c>
+      <c r="J18" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K18" s="10" t="str">
+        <v>390.42</v>
+      </c>
+      <c r="K18" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="L18" s="9" t="str">
+        <v>97.605000000000004</v>
+      </c>
+      <c r="L18" s="9">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="M18" s="9" t="str">
+        <v>12.15</v>
+      </c>
+      <c r="M18" s="9">
         <f t="shared" si="5"/>
-        <v/>
+        <v>2.4300000000000002</v>
       </c>
       <c r="N18" s="5" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="O18" s="11"/>
-      <c r="P18" s="12"/>
-    </row>
-    <row r="19" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>✅ Terminée</v>
+      </c>
+      <c r="O18" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="P18" s="12" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <v>17</v>
       </c>
-      <c r="B19" s="14"/>
-      <c r="C19" s="22"/>
-      <c r="D19" s="16"/>
-      <c r="E19" s="16"/>
-      <c r="F19" s="14" t="str">
+      <c r="B19" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="C19" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="D19" s="16">
+        <v>46219</v>
+      </c>
+      <c r="E19" s="16">
+        <v>46223</v>
+      </c>
+      <c r="F19" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G19" s="14"/>
-      <c r="H19" s="17"/>
+        <v>4</v>
+      </c>
+      <c r="G19" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="H19" s="17">
+        <v>120</v>
+      </c>
       <c r="I19" s="9" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J19" s="18" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K19" s="18" t="str">
+      <c r="J19" s="18">
+        <f>Tableau1[[#This Row],[Prix brut (€)]]*Tableau1[[#This Row],[Nuits]]</f>
+        <v>480</v>
+      </c>
+      <c r="K19" s="18">
         <f t="shared" si="3"/>
-        <v/>
+        <v>120</v>
       </c>
       <c r="L19" s="9" t="str">
         <f t="shared" si="4"/>
@@ -2424,12 +2464,16 @@
       </c>
       <c r="N19" s="14" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="O19" s="19"/>
-      <c r="P19" s="20"/>
-    </row>
-    <row r="20" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>🔵 À venir</v>
+      </c>
+      <c r="O19" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="P19" s="20" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="13">
         <v>18</v>
       </c>
@@ -2470,7 +2514,7 @@
       <c r="O20" s="11"/>
       <c r="P20" s="12"/>
     </row>
-    <row r="21" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
         <v>19</v>
       </c>
@@ -2511,7 +2555,7 @@
       <c r="O21" s="19"/>
       <c r="P21" s="20"/>
     </row>
-    <row r="22" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
         <v>20</v>
       </c>
@@ -2552,7 +2596,7 @@
       <c r="O22" s="11"/>
       <c r="P22" s="12"/>
     </row>
-    <row r="23" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="13">
         <v>21</v>
       </c>
@@ -2593,7 +2637,7 @@
       <c r="O23" s="19"/>
       <c r="P23" s="20"/>
     </row>
-    <row r="24" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
         <v>22</v>
       </c>
@@ -2634,7 +2678,7 @@
       <c r="O24" s="19"/>
       <c r="P24" s="20"/>
     </row>
-    <row r="25" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
         <v>23</v>
       </c>
@@ -2675,7 +2719,7 @@
       <c r="O25" s="19"/>
       <c r="P25" s="20"/>
     </row>
-    <row r="26" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="13">
         <v>24</v>
       </c>
@@ -2716,7 +2760,7 @@
       <c r="O26" s="19"/>
       <c r="P26" s="20"/>
     </row>
-    <row r="27" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4">
         <v>25</v>
       </c>
@@ -2757,7 +2801,7 @@
       <c r="O27" s="19"/>
       <c r="P27" s="20"/>
     </row>
-    <row r="28" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="13">
         <v>26</v>
       </c>
@@ -2798,7 +2842,7 @@
       <c r="O28" s="19"/>
       <c r="P28" s="20"/>
     </row>
-    <row r="29" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4">
         <v>27</v>
       </c>
@@ -2839,7 +2883,7 @@
       <c r="O29" s="11"/>
       <c r="P29" s="12"/>
     </row>
-    <row r="30" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="4">
         <v>28</v>
       </c>
@@ -2880,7 +2924,7 @@
       <c r="O30" s="19"/>
       <c r="P30" s="20"/>
     </row>
-    <row r="31" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="13">
         <v>29</v>
       </c>
@@ -2921,7 +2965,7 @@
       <c r="O31" s="11"/>
       <c r="P31" s="12"/>
     </row>
-    <row r="32" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="4">
         <v>30</v>
       </c>
@@ -2962,7 +3006,7 @@
       <c r="O32" s="19"/>
       <c r="P32" s="20"/>
     </row>
-    <row r="33" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4">
         <v>31</v>
       </c>
@@ -3003,7 +3047,7 @@
       <c r="O33" s="11"/>
       <c r="P33" s="12"/>
     </row>
-    <row r="34" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="13">
         <v>32</v>
       </c>
@@ -3044,7 +3088,7 @@
       <c r="O34" s="19"/>
       <c r="P34" s="20"/>
     </row>
-    <row r="35" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="4">
         <v>33</v>
       </c>
@@ -3085,7 +3129,7 @@
       <c r="O35" s="11"/>
       <c r="P35" s="12"/>
     </row>
-    <row r="36" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="13">
         <v>34</v>
       </c>
@@ -3126,7 +3170,7 @@
       <c r="O36" s="19"/>
       <c r="P36" s="20"/>
     </row>
-    <row r="37" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="4">
         <v>35</v>
       </c>
@@ -3167,7 +3211,7 @@
       <c r="O37" s="19"/>
       <c r="P37" s="20"/>
     </row>
-    <row r="38" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="4">
         <v>36</v>
       </c>
@@ -3208,7 +3252,7 @@
       <c r="O38" s="19"/>
       <c r="P38" s="20"/>
     </row>
-    <row r="39" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="13">
         <v>37</v>
       </c>
@@ -3249,7 +3293,7 @@
       <c r="O39" s="19"/>
       <c r="P39" s="20"/>
     </row>
-    <row r="40" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="4">
         <v>38</v>
       </c>
@@ -3290,7 +3334,7 @@
       <c r="O40" s="19"/>
       <c r="P40" s="20"/>
     </row>
-    <row r="41" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="4">
         <v>39</v>
       </c>
@@ -3331,7 +3375,7 @@
       <c r="O41" s="19"/>
       <c r="P41" s="20"/>
     </row>
-    <row r="42" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="13">
         <v>40</v>
       </c>
@@ -3372,7 +3416,7 @@
       <c r="O42" s="11"/>
       <c r="P42" s="12"/>
     </row>
-    <row r="43" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="4">
         <v>41</v>
       </c>
@@ -3413,7 +3457,7 @@
       <c r="O43" s="19"/>
       <c r="P43" s="20"/>
     </row>
-    <row r="44" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="13">
         <v>42</v>
       </c>
@@ -3454,7 +3498,7 @@
       <c r="O44" s="11"/>
       <c r="P44" s="12"/>
     </row>
-    <row r="45" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="4">
         <v>43</v>
       </c>
@@ -3495,7 +3539,7 @@
       <c r="O45" s="19"/>
       <c r="P45" s="20"/>
     </row>
-    <row r="46" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="4">
         <v>44</v>
       </c>
@@ -3536,7 +3580,7 @@
       <c r="O46" s="11"/>
       <c r="P46" s="12"/>
     </row>
-    <row r="47" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="13">
         <v>45</v>
       </c>
@@ -3577,7 +3621,7 @@
       <c r="O47" s="19"/>
       <c r="P47" s="20"/>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="4">
         <v>46</v>
       </c>
@@ -3618,7 +3662,7 @@
       <c r="O48" s="11"/>
       <c r="P48" s="12"/>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="4">
         <v>47</v>
       </c>
@@ -3659,7 +3703,7 @@
       <c r="O49" s="19"/>
       <c r="P49" s="20"/>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="13">
         <v>48</v>
       </c>
@@ -3712,27 +3756,27 @@
       <c r="G51" s="38"/>
       <c r="H51" s="23">
         <f t="shared" ref="H51:M51" si="14">SUMIF(H3:H50,"&gt;0")</f>
-        <v>5958.54</v>
+        <v>6483.54</v>
       </c>
       <c r="I51" s="24">
         <f t="shared" si="14"/>
-        <v>788.58255999999994</v>
+        <v>803.16255999999998</v>
       </c>
       <c r="J51" s="23">
         <f t="shared" si="14"/>
-        <v>5076.2874400000001</v>
+        <v>5946.7074400000001</v>
       </c>
       <c r="K51" s="23">
         <f t="shared" si="14"/>
-        <v>1269.07186</v>
+        <v>1486.67686</v>
       </c>
       <c r="L51" s="24">
         <f t="shared" si="14"/>
-        <v>718.80600000000004</v>
+        <v>730.95600000000002</v>
       </c>
       <c r="M51" s="24">
         <f t="shared" si="14"/>
-        <v>69.776560000000018</v>
+        <v>72.206560000000025</v>
       </c>
       <c r="N51" s="25" t="str">
         <f ca="1">COUNTIF(N3:N10,"✅ Terminée")&amp;" terminée(s)"</f>
@@ -3744,33 +3788,33 @@
     <row r="52" spans="1:16" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J52" s="27">
         <f>J51-K51</f>
-        <v>3807.21558</v>
+        <v>4460.0305800000006</v>
       </c>
     </row>
     <row r="53" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="40" t="s">
+      <c r="A53" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="B53" s="40"/>
-      <c r="C53" s="40"/>
-      <c r="D53" s="40"/>
-      <c r="E53" s="40"/>
-      <c r="F53" s="40"/>
-      <c r="G53" s="40"/>
-      <c r="H53" s="40"/>
-      <c r="I53" s="40"/>
-      <c r="J53" s="40"/>
-      <c r="K53" s="40"/>
-      <c r="L53" s="40"/>
-      <c r="M53" s="40"/>
-      <c r="N53" s="40"/>
-      <c r="O53" s="40"/>
-      <c r="P53" s="40"/>
+      <c r="B53" s="41"/>
+      <c r="C53" s="41"/>
+      <c r="D53" s="41"/>
+      <c r="E53" s="41"/>
+      <c r="F53" s="41"/>
+      <c r="G53" s="41"/>
+      <c r="H53" s="41"/>
+      <c r="I53" s="41"/>
+      <c r="J53" s="41"/>
+      <c r="K53" s="41"/>
+      <c r="L53" s="41"/>
+      <c r="M53" s="41"/>
+      <c r="N53" s="41"/>
+      <c r="O53" s="41"/>
+      <c r="P53" s="41"/>
     </row>
     <row r="54" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J54" s="42">
-        <f>J52*0.94</f>
-        <v>3578.7826451999999</v>
+      <c r="J54" s="39">
+        <f>J52*0.75</f>
+        <v>3345.0229350000004</v>
       </c>
     </row>
   </sheetData>
@@ -3819,12 +3863,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="42" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
     </row>
     <row r="2" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="28" t="s">

--- a/Casa_do_Mosteiro_v6.xlsx
+++ b/Casa_do_Mosteiro_v6.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Patrick SALVADOR\Documents\Immobilier\Locations - Airbnb - Booking\Casa do mosteiro - Aluguer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BC2C3F7-B026-4466-9770-49937CA4666F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E21ED32D-EC58-4548-8EAD-3F03B04EA021}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="📋 Réservations" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="73">
   <si>
     <t>🏠  CASA DO MOSTEIRO — Réservations</t>
   </si>
@@ -239,6 +239,12 @@
   </si>
   <si>
     <t>y</t>
+  </si>
+  <si>
+    <t>Sandrine Brahiti</t>
+  </si>
+  <si>
+    <t>0650464553</t>
   </si>
 </sst>
 </file>
@@ -2179,7 +2185,7 @@
       <c r="M14" s="9"/>
       <c r="N14" s="14" t="str">
         <f ca="1">IF(D14="","",IF(E14&lt;TODAY(),"✅ Terminée",IF(D14&lt;=TODAY(),"🟡 En cours","🔵 À venir")))</f>
-        <v>🟡 En cours</v>
+        <v>✅ Terminée</v>
       </c>
       <c r="O14" s="19" t="s">
         <v>39</v>
@@ -2473,48 +2479,64 @@
         <v>70</v>
       </c>
     </row>
-    <row r="20" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="13">
         <v>18</v>
       </c>
-      <c r="B20" s="5"/>
-      <c r="C20" s="21"/>
-      <c r="D20" s="16"/>
-      <c r="E20" s="16"/>
-      <c r="F20" s="5" t="str">
+      <c r="B20" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="D20" s="16">
+        <v>46251</v>
+      </c>
+      <c r="E20" s="16">
+        <v>46264</v>
+      </c>
+      <c r="F20" s="5">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G20" s="5"/>
-      <c r="H20" s="8"/>
-      <c r="I20" s="9" t="str">
+        <v>13</v>
+      </c>
+      <c r="G20" s="5">
+        <v>4</v>
+      </c>
+      <c r="H20" s="8">
+        <v>1950</v>
+      </c>
+      <c r="I20" s="9">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J20" s="10" t="str">
+        <v>319.8</v>
+      </c>
+      <c r="J20" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K20" s="10" t="str">
+        <v>1630.2</v>
+      </c>
+      <c r="K20" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="L20" s="9" t="str">
+        <v>407.55</v>
+      </c>
+      <c r="L20" s="9">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="M20" s="9" t="str">
+        <v>292.5</v>
+      </c>
+      <c r="M20" s="9">
         <f t="shared" si="5"/>
-        <v/>
+        <v>27.3</v>
       </c>
       <c r="N20" s="5" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="O20" s="11"/>
-      <c r="P20" s="12"/>
-    </row>
-    <row r="21" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+        <v>🔵 À venir</v>
+      </c>
+      <c r="O20" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="P20" s="12" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
         <v>19</v>
       </c>
@@ -3756,27 +3778,27 @@
       <c r="G51" s="38"/>
       <c r="H51" s="23">
         <f t="shared" ref="H51:M51" si="14">SUMIF(H3:H50,"&gt;0")</f>
-        <v>6483.54</v>
+        <v>8433.5400000000009</v>
       </c>
       <c r="I51" s="24">
         <f t="shared" si="14"/>
-        <v>803.16255999999998</v>
+        <v>1122.9625599999999</v>
       </c>
       <c r="J51" s="23">
         <f t="shared" si="14"/>
-        <v>5946.7074400000001</v>
+        <v>7576.90744</v>
       </c>
       <c r="K51" s="23">
         <f t="shared" si="14"/>
-        <v>1486.67686</v>
+        <v>1894.22686</v>
       </c>
       <c r="L51" s="24">
         <f t="shared" si="14"/>
-        <v>730.95600000000002</v>
+        <v>1023.456</v>
       </c>
       <c r="M51" s="24">
         <f t="shared" si="14"/>
-        <v>72.206560000000025</v>
+        <v>99.506560000000022</v>
       </c>
       <c r="N51" s="25" t="str">
         <f ca="1">COUNTIF(N3:N10,"✅ Terminée")&amp;" terminée(s)"</f>
@@ -3788,7 +3810,7 @@
     <row r="52" spans="1:16" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J52" s="27">
         <f>J51-K51</f>
-        <v>4460.0305800000006</v>
+        <v>5682.6805800000002</v>
       </c>
     </row>
     <row r="53" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3814,7 +3836,7 @@
     <row r="54" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J54" s="39">
         <f>J52*0.75</f>
-        <v>3345.0229350000004</v>
+        <v>4262.0104350000001</v>
       </c>
     </row>
   </sheetData>

--- a/Casa_do_Mosteiro_v6.xlsx
+++ b/Casa_do_Mosteiro_v6.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Patrick SALVADOR\Documents\Immobilier\Locations - Airbnb - Booking\Casa do mosteiro - Aluguer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E21ED32D-EC58-4548-8EAD-3F03B04EA021}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12FD5AAC-CA85-4B2D-8B01-2999022C54E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="📋 Réservations" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="75">
   <si>
     <t>🏠  CASA DO MOSTEIRO — Réservations</t>
   </si>
@@ -241,10 +241,16 @@
     <t>y</t>
   </si>
   <si>
-    <t>Sandrine Brahiti</t>
-  </si>
-  <si>
-    <t>0650464553</t>
+    <t>Antonio Pinho</t>
+  </si>
+  <si>
+    <t>Ana Moura</t>
+  </si>
+  <si>
+    <t>00351919451210</t>
+  </si>
+  <si>
+    <t>00351912080179</t>
   </si>
 </sst>
 </file>
@@ -255,7 +261,7 @@
     <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
     <numFmt numFmtId="165" formatCode="#,##0.00&quot; €&quot;"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -348,6 +354,18 @@
       <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -550,7 +568,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -671,12 +689,55 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="13">
+  <dxfs count="17">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59987182226020086"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79989013336588644"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1225,7 +1286,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F2313CAB-7AD2-4EDB-930F-5D65625B6D2B}" name="Tableau1" displayName="Tableau1" ref="A2:P51" totalsRowShown="0" headerRowDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F2313CAB-7AD2-4EDB-930F-5D65625B6D2B}" name="Tableau1" displayName="Tableau1" ref="A2:P51" totalsRowShown="0" headerRowDxfId="16">
   <autoFilter ref="A2:P51" xr:uid="{F2313CAB-7AD2-4EDB-930F-5D65625B6D2B}"/>
   <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{AC60970B-A2FC-4DDF-A9CC-349A2480743F}" name="N°"/>
@@ -1233,17 +1294,17 @@
     <tableColumn id="3" xr3:uid="{B122446C-E3FE-40E2-87A7-AB4899728B1C}" name="Voyageur"/>
     <tableColumn id="4" xr3:uid="{97208B29-BAB5-42E9-B831-9D4590177054}" name="Arrivée"/>
     <tableColumn id="5" xr3:uid="{D3FE3381-C4B8-498F-A625-9962CB8A6588}" name="Départ"/>
-    <tableColumn id="6" xr3:uid="{597E1DA1-8BEB-4388-9DEE-46070032A16C}" name="Nuits" dataDxfId="11"/>
+    <tableColumn id="6" xr3:uid="{597E1DA1-8BEB-4388-9DEE-46070032A16C}" name="Nuits" dataDxfId="15"/>
     <tableColumn id="7" xr3:uid="{FB4B88CE-AF8F-4750-B8B0-B7F7393E68C9}" name="Personnes"/>
-    <tableColumn id="8" xr3:uid="{5D9F9F94-AD5D-4170-9B0D-1889D7F3F70D}" name="Prix brut (€)" dataDxfId="10"/>
-    <tableColumn id="9" xr3:uid="{E2297A44-4273-4BA7-878E-97F599090065}" name="Frais plate. (€) 🔒" dataDxfId="9"/>
-    <tableColumn id="10" xr3:uid="{CFAAEAA3-2982-40AF-B875-EE881355E43E}" name="Net reçu (€)" dataDxfId="8"/>
-    <tableColumn id="11" xr3:uid="{B8A370C8-5D57-48C1-8BE6-3A2B5ACFB5DD}" name="Gloria 25% (€)" dataDxfId="7"/>
-    <tableColumn id="12" xr3:uid="{596F80C5-7E4A-4CD8-9C07-871967C53D6A}" name="Commission (€) 🔒" dataDxfId="6"/>
-    <tableColumn id="13" xr3:uid="{EB1AD7D4-C5F7-417D-9953-52A1CF811051}" name="TVA / Fr.banc. (€) 🔒" dataDxfId="5"/>
-    <tableColumn id="14" xr3:uid="{DE0D1F8C-57FF-492D-BFE6-FE4E7A8BEABC}" name="Statut" dataDxfId="4"/>
-    <tableColumn id="15" xr3:uid="{8C802233-1B0A-46BB-A281-14B1BE490844}" name="Hora de chegada" dataDxfId="3"/>
-    <tableColumn id="16" xr3:uid="{0737B9E8-1278-4EF0-9A9B-3B9B8DE56851}" name="Telefone" dataDxfId="2"/>
+    <tableColumn id="8" xr3:uid="{5D9F9F94-AD5D-4170-9B0D-1889D7F3F70D}" name="Prix brut (€)" dataDxfId="14"/>
+    <tableColumn id="9" xr3:uid="{E2297A44-4273-4BA7-878E-97F599090065}" name="Frais plate. (€) 🔒" dataDxfId="13"/>
+    <tableColumn id="10" xr3:uid="{CFAAEAA3-2982-40AF-B875-EE881355E43E}" name="Net reçu (€)" dataDxfId="12"/>
+    <tableColumn id="11" xr3:uid="{B8A370C8-5D57-48C1-8BE6-3A2B5ACFB5DD}" name="Gloria 25% (€)" dataDxfId="11"/>
+    <tableColumn id="12" xr3:uid="{596F80C5-7E4A-4CD8-9C07-871967C53D6A}" name="Commission (€) 🔒" dataDxfId="10"/>
+    <tableColumn id="13" xr3:uid="{EB1AD7D4-C5F7-417D-9953-52A1CF811051}" name="TVA / Fr.banc. (€) 🔒" dataDxfId="9"/>
+    <tableColumn id="14" xr3:uid="{DE0D1F8C-57FF-492D-BFE6-FE4E7A8BEABC}" name="Statut" dataDxfId="8"/>
+    <tableColumn id="15" xr3:uid="{8C802233-1B0A-46BB-A281-14B1BE490844}" name="Hora de chegada" dataDxfId="7"/>
+    <tableColumn id="16" xr3:uid="{0737B9E8-1278-4EF0-9A9B-3B9B8DE56851}" name="Telefone" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1625,7 +1686,7 @@
       </c>
       <c r="N4" s="14" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>🔵 À venir</v>
+        <v>✅ Terminée</v>
       </c>
       <c r="O4" s="19" t="s">
         <v>39</v>
@@ -1967,7 +2028,7 @@
       </c>
       <c r="N10" s="14" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>🔵 À venir</v>
+        <v>✅ Terminée</v>
       </c>
       <c r="O10" s="19" t="s">
         <v>39</v>
@@ -2081,7 +2142,7 @@
       </c>
       <c r="N12" s="14" t="str">
         <f ca="1">IF(D12="","",IF(E12&lt;TODAY(),"✅ Terminée",IF(D12&lt;=TODAY(),"🟡 En cours","🔵 À venir")))</f>
-        <v>🔵 À venir</v>
+        <v>✅ Terminée</v>
       </c>
       <c r="O12" s="19" t="s">
         <v>39</v>
@@ -2470,7 +2531,7 @@
       </c>
       <c r="N19" s="14" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>🔵 À venir</v>
+        <v>✅ Terminée</v>
       </c>
       <c r="O19" s="19" t="s">
         <v>70</v>
@@ -2486,44 +2547,44 @@
       <c r="B20" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C20" s="21" t="s">
+      <c r="C20" s="43" t="s">
         <v>71</v>
       </c>
       <c r="D20" s="16">
-        <v>46251</v>
+        <v>46250</v>
       </c>
       <c r="E20" s="16">
-        <v>46264</v>
+        <v>46255</v>
       </c>
       <c r="F20" s="5">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="G20" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H20" s="8">
-        <v>1950</v>
+        <v>607.5</v>
       </c>
       <c r="I20" s="9">
-        <f t="shared" si="1"/>
-        <v>319.8</v>
+        <f>104.5</f>
+        <v>104.5</v>
       </c>
       <c r="J20" s="10">
         <f t="shared" si="2"/>
-        <v>1630.2</v>
+        <v>503</v>
       </c>
       <c r="K20" s="10">
         <f t="shared" si="3"/>
-        <v>407.55</v>
+        <v>125.75</v>
       </c>
       <c r="L20" s="9">
         <f t="shared" si="4"/>
-        <v>292.5</v>
+        <v>91.125</v>
       </c>
       <c r="M20" s="9">
         <f t="shared" si="5"/>
-        <v>27.3</v>
+        <v>8.5050000000000008</v>
       </c>
       <c r="N20" s="5" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -2532,50 +2593,65 @@
       <c r="O20" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="P20" s="12" t="s">
-        <v>72</v>
+      <c r="P20" s="46" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
         <v>19</v>
       </c>
-      <c r="B21" s="14"/>
-      <c r="C21" s="22"/>
-      <c r="D21" s="16"/>
-      <c r="E21" s="16"/>
-      <c r="F21" s="14" t="str">
+      <c r="B21" s="44" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" s="45" t="s">
+        <v>72</v>
+      </c>
+      <c r="D21" s="16">
+        <v>46257</v>
+      </c>
+      <c r="E21" s="16">
+        <v>46261</v>
+      </c>
+      <c r="F21" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G21" s="14"/>
-      <c r="H21" s="17"/>
-      <c r="I21" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J21" s="18" t="str">
+        <v>4</v>
+      </c>
+      <c r="G21" s="14">
+        <v>4</v>
+      </c>
+      <c r="H21" s="17">
+        <v>486</v>
+      </c>
+      <c r="I21" s="9">
+        <v>84.6</v>
+      </c>
+      <c r="J21" s="18">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K21" s="18" t="str">
+        <v>401.4</v>
+      </c>
+      <c r="K21" s="18">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="L21" s="9" t="str">
+        <v>100.35</v>
+      </c>
+      <c r="L21" s="9">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="M21" s="9" t="str">
+        <v>72.899999999999991</v>
+      </c>
+      <c r="M21" s="9">
         <f t="shared" si="5"/>
-        <v/>
+        <v>6.8040000000000003</v>
       </c>
       <c r="N21" s="14" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="O21" s="19"/>
-      <c r="P21" s="20"/>
+        <v>🔵 À venir</v>
+      </c>
+      <c r="O21" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="P21" s="47" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="22" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
@@ -3778,31 +3854,31 @@
       <c r="G51" s="38"/>
       <c r="H51" s="23">
         <f t="shared" ref="H51:M51" si="14">SUMIF(H3:H50,"&gt;0")</f>
-        <v>8433.5400000000009</v>
+        <v>7577.04</v>
       </c>
       <c r="I51" s="24">
         <f t="shared" si="14"/>
-        <v>1122.9625599999999</v>
+        <v>992.26256000000001</v>
       </c>
       <c r="J51" s="23">
         <f t="shared" si="14"/>
-        <v>7576.90744</v>
+        <v>6851.1074399999998</v>
       </c>
       <c r="K51" s="23">
         <f t="shared" si="14"/>
-        <v>1894.22686</v>
+        <v>1712.7768599999999</v>
       </c>
       <c r="L51" s="24">
         <f t="shared" si="14"/>
-        <v>1023.456</v>
+        <v>894.98099999999999</v>
       </c>
       <c r="M51" s="24">
         <f t="shared" si="14"/>
-        <v>99.506560000000022</v>
+        <v>87.515560000000022</v>
       </c>
       <c r="N51" s="25" t="str">
         <f ca="1">COUNTIF(N3:N10,"✅ Terminée")&amp;" terminée(s)"</f>
-        <v>6 terminée(s)</v>
+        <v>8 terminée(s)</v>
       </c>
       <c r="O51" s="26"/>
       <c r="P51" s="26"/>
@@ -3810,7 +3886,7 @@
     <row r="52" spans="1:16" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J52" s="27">
         <f>J51-K51</f>
-        <v>5682.6805800000002</v>
+        <v>5138.3305799999998</v>
       </c>
     </row>
     <row r="53" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3836,7 +3912,7 @@
     <row r="54" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J54" s="39">
         <f>J52*0.75</f>
-        <v>4262.0104350000001</v>
+        <v>3853.7479349999999</v>
       </c>
     </row>
   </sheetData>
@@ -3845,10 +3921,10 @@
     <mergeCell ref="A53:P53"/>
   </mergeCells>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="booking">
+    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="booking">
       <formula>NOT(ISERROR(SEARCH("booking",B1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="3" operator="containsText" text="airbnb">
+    <cfRule type="containsText" dxfId="1" priority="4" operator="containsText" text="airbnb">
       <formula>NOT(ISERROR(SEARCH("airbnb",B1)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3867,6 +3943,26 @@
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="1" operator="containsText" id="{FF531569-1D25-48B2-83FD-EC26D35B94A9}">
+            <xm:f>NOT(ISERROR(SEARCH($N$3,N1)))</xm:f>
+            <xm:f>$N$3</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFC00000"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>N1:N1048576</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 

--- a/Casa_do_Mosteiro_v6.xlsx
+++ b/Casa_do_Mosteiro_v6.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Patrick SALVADOR\Documents\Immobilier\Locations - Airbnb - Booking\Casa do mosteiro - Aluguer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12FD5AAC-CA85-4B2D-8B01-2999022C54E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E003BCD-6D4A-41D2-8522-EB5C749E1F5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="76">
   <si>
     <t>🏠  CASA DO MOSTEIRO — Réservations</t>
   </si>
@@ -241,9 +241,6 @@
     <t>y</t>
   </si>
   <si>
-    <t>Antonio Pinho</t>
-  </si>
-  <si>
     <t>Ana Moura</t>
   </si>
   <si>
@@ -251,6 +248,12 @@
   </si>
   <si>
     <t>00351912080179</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>Antonio Pinho empresa</t>
   </si>
 </sst>
 </file>
@@ -370,7 +373,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -435,6 +438,12 @@
       <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor rgb="FFFDFAF6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFBF0"/>
       </patternFill>
     </fill>
   </fills>
@@ -568,7 +577,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -683,6 +692,21 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -690,47 +714,14 @@
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="17">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59987182226020086"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79989013336588644"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="14">
     <dxf>
       <fill>
         <patternFill>
@@ -1286,7 +1277,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F2313CAB-7AD2-4EDB-930F-5D65625B6D2B}" name="Tableau1" displayName="Tableau1" ref="A2:P51" totalsRowShown="0" headerRowDxfId="16">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F2313CAB-7AD2-4EDB-930F-5D65625B6D2B}" name="Tableau1" displayName="Tableau1" ref="A2:P51" totalsRowShown="0" headerRowDxfId="13">
   <autoFilter ref="A2:P51" xr:uid="{F2313CAB-7AD2-4EDB-930F-5D65625B6D2B}"/>
   <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{AC60970B-A2FC-4DDF-A9CC-349A2480743F}" name="N°"/>
@@ -1294,17 +1285,17 @@
     <tableColumn id="3" xr3:uid="{B122446C-E3FE-40E2-87A7-AB4899728B1C}" name="Voyageur"/>
     <tableColumn id="4" xr3:uid="{97208B29-BAB5-42E9-B831-9D4590177054}" name="Arrivée"/>
     <tableColumn id="5" xr3:uid="{D3FE3381-C4B8-498F-A625-9962CB8A6588}" name="Départ"/>
-    <tableColumn id="6" xr3:uid="{597E1DA1-8BEB-4388-9DEE-46070032A16C}" name="Nuits" dataDxfId="15"/>
+    <tableColumn id="6" xr3:uid="{597E1DA1-8BEB-4388-9DEE-46070032A16C}" name="Nuits" dataDxfId="12"/>
     <tableColumn id="7" xr3:uid="{FB4B88CE-AF8F-4750-B8B0-B7F7393E68C9}" name="Personnes"/>
-    <tableColumn id="8" xr3:uid="{5D9F9F94-AD5D-4170-9B0D-1889D7F3F70D}" name="Prix brut (€)" dataDxfId="14"/>
-    <tableColumn id="9" xr3:uid="{E2297A44-4273-4BA7-878E-97F599090065}" name="Frais plate. (€) 🔒" dataDxfId="13"/>
-    <tableColumn id="10" xr3:uid="{CFAAEAA3-2982-40AF-B875-EE881355E43E}" name="Net reçu (€)" dataDxfId="12"/>
-    <tableColumn id="11" xr3:uid="{B8A370C8-5D57-48C1-8BE6-3A2B5ACFB5DD}" name="Gloria 25% (€)" dataDxfId="11"/>
-    <tableColumn id="12" xr3:uid="{596F80C5-7E4A-4CD8-9C07-871967C53D6A}" name="Commission (€) 🔒" dataDxfId="10"/>
-    <tableColumn id="13" xr3:uid="{EB1AD7D4-C5F7-417D-9953-52A1CF811051}" name="TVA / Fr.banc. (€) 🔒" dataDxfId="9"/>
-    <tableColumn id="14" xr3:uid="{DE0D1F8C-57FF-492D-BFE6-FE4E7A8BEABC}" name="Statut" dataDxfId="8"/>
-    <tableColumn id="15" xr3:uid="{8C802233-1B0A-46BB-A281-14B1BE490844}" name="Hora de chegada" dataDxfId="7"/>
-    <tableColumn id="16" xr3:uid="{0737B9E8-1278-4EF0-9A9B-3B9B8DE56851}" name="Telefone" dataDxfId="6"/>
+    <tableColumn id="8" xr3:uid="{5D9F9F94-AD5D-4170-9B0D-1889D7F3F70D}" name="Prix brut (€)" dataDxfId="11"/>
+    <tableColumn id="9" xr3:uid="{E2297A44-4273-4BA7-878E-97F599090065}" name="Frais plate. (€) 🔒" dataDxfId="10"/>
+    <tableColumn id="10" xr3:uid="{CFAAEAA3-2982-40AF-B875-EE881355E43E}" name="Net reçu (€)" dataDxfId="9"/>
+    <tableColumn id="11" xr3:uid="{B8A370C8-5D57-48C1-8BE6-3A2B5ACFB5DD}" name="Gloria 25% (€)" dataDxfId="8"/>
+    <tableColumn id="12" xr3:uid="{596F80C5-7E4A-4CD8-9C07-871967C53D6A}" name="Commission (€) 🔒" dataDxfId="7"/>
+    <tableColumn id="13" xr3:uid="{EB1AD7D4-C5F7-417D-9953-52A1CF811051}" name="TVA / Fr.banc. (€) 🔒" dataDxfId="6"/>
+    <tableColumn id="14" xr3:uid="{DE0D1F8C-57FF-492D-BFE6-FE4E7A8BEABC}" name="Statut" dataDxfId="5"/>
+    <tableColumn id="15" xr3:uid="{8C802233-1B0A-46BB-A281-14B1BE490844}" name="Hora de chegada" dataDxfId="4"/>
+    <tableColumn id="16" xr3:uid="{0737B9E8-1278-4EF0-9A9B-3B9B8DE56851}" name="Telefone" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1492,7 +1483,7 @@
   <sheetPr>
     <tabColor rgb="FFC2714F"/>
   </sheetPr>
-  <dimension ref="A1:P54"/>
+  <dimension ref="A1:P62"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1513,24 +1504,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
-      <c r="J1" s="40"/>
-      <c r="K1" s="40"/>
-      <c r="L1" s="40"/>
-      <c r="M1" s="40"/>
-      <c r="N1" s="40"/>
-      <c r="O1" s="40"/>
-      <c r="P1" s="40"/>
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
+      <c r="I1" s="45"/>
+      <c r="J1" s="45"/>
+      <c r="K1" s="45"/>
+      <c r="L1" s="45"/>
+      <c r="M1" s="45"/>
+      <c r="N1" s="45"/>
+      <c r="O1" s="45"/>
+      <c r="P1" s="45"/>
     </row>
     <row r="2" spans="1:16" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -2500,8 +2491,7 @@
         <v>46223</v>
       </c>
       <c r="F19" s="14">
-        <f t="shared" si="0"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G19" s="14" t="s">
         <v>70</v>
@@ -2515,11 +2505,11 @@
       </c>
       <c r="J19" s="18">
         <f>Tableau1[[#This Row],[Prix brut (€)]]*Tableau1[[#This Row],[Nuits]]</f>
-        <v>480</v>
+        <v>360</v>
       </c>
       <c r="K19" s="18">
         <f t="shared" si="3"/>
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="L19" s="9" t="str">
         <f t="shared" si="4"/>
@@ -2547,8 +2537,8 @@
       <c r="B20" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C20" s="43" t="s">
-        <v>71</v>
+      <c r="C20" s="40" t="s">
+        <v>75</v>
       </c>
       <c r="D20" s="16">
         <v>46250</v>
@@ -2588,24 +2578,24 @@
       </c>
       <c r="N20" s="5" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>🔵 À venir</v>
+        <v>🟡 En cours</v>
       </c>
       <c r="O20" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="P20" s="46" t="s">
-        <v>73</v>
+      <c r="P20" s="43" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
         <v>19</v>
       </c>
-      <c r="B21" s="44" t="s">
+      <c r="B21" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="45" t="s">
-        <v>72</v>
+      <c r="C21" s="42" t="s">
+        <v>71</v>
       </c>
       <c r="D21" s="16">
         <v>46257</v>
@@ -2647,37 +2637,49 @@
         <v>🔵 À venir</v>
       </c>
       <c r="O21" s="19" t="s">
-        <v>39</v>
-      </c>
-      <c r="P21" s="47" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="4">
+        <v>41</v>
+      </c>
+      <c r="P21" s="44" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A22" s="48">
         <v>20</v>
       </c>
-      <c r="B22" s="5"/>
-      <c r="C22" s="21"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="5" t="str">
+      <c r="B22" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C22" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="D22" s="7">
+        <v>46261</v>
+      </c>
+      <c r="E22" s="7">
+        <v>46275</v>
+      </c>
+      <c r="F22" s="5">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G22" s="5"/>
-      <c r="H22" s="8"/>
+        <v>14</v>
+      </c>
+      <c r="G22" s="5">
+        <v>4</v>
+      </c>
+      <c r="H22" s="8">
+        <v>1400</v>
+      </c>
       <c r="I22" s="9" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J22" s="10" t="str">
+      <c r="J22" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K22" s="10" t="str">
+        <v>1400</v>
+      </c>
+      <c r="K22" s="10">
         <f t="shared" si="3"/>
-        <v/>
+        <v>350</v>
       </c>
       <c r="L22" s="9" t="str">
         <f t="shared" si="4"/>
@@ -2689,12 +2691,16 @@
       </c>
       <c r="N22" s="5" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="O22" s="11"/>
-      <c r="P22" s="12"/>
-    </row>
-    <row r="23" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+        <v>🔵 À venir</v>
+      </c>
+      <c r="O22" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="P22" s="43" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" s="13">
         <v>21</v>
       </c>
@@ -2735,7 +2741,7 @@
       <c r="O23" s="19"/>
       <c r="P23" s="20"/>
     </row>
-    <row r="24" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
         <v>22</v>
       </c>
@@ -2776,7 +2782,7 @@
       <c r="O24" s="19"/>
       <c r="P24" s="20"/>
     </row>
-    <row r="25" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
         <v>23</v>
       </c>
@@ -2817,7 +2823,7 @@
       <c r="O25" s="19"/>
       <c r="P25" s="20"/>
     </row>
-    <row r="26" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" s="13">
         <v>24</v>
       </c>
@@ -2858,7 +2864,7 @@
       <c r="O26" s="19"/>
       <c r="P26" s="20"/>
     </row>
-    <row r="27" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" s="4">
         <v>25</v>
       </c>
@@ -2899,7 +2905,7 @@
       <c r="O27" s="19"/>
       <c r="P27" s="20"/>
     </row>
-    <row r="28" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" s="13">
         <v>26</v>
       </c>
@@ -2940,7 +2946,7 @@
       <c r="O28" s="19"/>
       <c r="P28" s="20"/>
     </row>
-    <row r="29" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" s="4">
         <v>27</v>
       </c>
@@ -2981,7 +2987,7 @@
       <c r="O29" s="11"/>
       <c r="P29" s="12"/>
     </row>
-    <row r="30" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" s="4">
         <v>28</v>
       </c>
@@ -3022,7 +3028,7 @@
       <c r="O30" s="19"/>
       <c r="P30" s="20"/>
     </row>
-    <row r="31" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" s="13">
         <v>29</v>
       </c>
@@ -3063,7 +3069,7 @@
       <c r="O31" s="11"/>
       <c r="P31" s="12"/>
     </row>
-    <row r="32" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" s="4">
         <v>30</v>
       </c>
@@ -3104,7 +3110,7 @@
       <c r="O32" s="19"/>
       <c r="P32" s="20"/>
     </row>
-    <row r="33" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" s="4">
         <v>31</v>
       </c>
@@ -3145,7 +3151,7 @@
       <c r="O33" s="11"/>
       <c r="P33" s="12"/>
     </row>
-    <row r="34" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" s="13">
         <v>32</v>
       </c>
@@ -3186,7 +3192,7 @@
       <c r="O34" s="19"/>
       <c r="P34" s="20"/>
     </row>
-    <row r="35" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" s="4">
         <v>33</v>
       </c>
@@ -3227,7 +3233,7 @@
       <c r="O35" s="11"/>
       <c r="P35" s="12"/>
     </row>
-    <row r="36" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36" s="13">
         <v>34</v>
       </c>
@@ -3268,7 +3274,7 @@
       <c r="O36" s="19"/>
       <c r="P36" s="20"/>
     </row>
-    <row r="37" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" s="4">
         <v>35</v>
       </c>
@@ -3309,7 +3315,7 @@
       <c r="O37" s="19"/>
       <c r="P37" s="20"/>
     </row>
-    <row r="38" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A38" s="4">
         <v>36</v>
       </c>
@@ -3350,7 +3356,7 @@
       <c r="O38" s="19"/>
       <c r="P38" s="20"/>
     </row>
-    <row r="39" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A39" s="13">
         <v>37</v>
       </c>
@@ -3391,7 +3397,7 @@
       <c r="O39" s="19"/>
       <c r="P39" s="20"/>
     </row>
-    <row r="40" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A40" s="4">
         <v>38</v>
       </c>
@@ -3432,7 +3438,7 @@
       <c r="O40" s="19"/>
       <c r="P40" s="20"/>
     </row>
-    <row r="41" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A41" s="4">
         <v>39</v>
       </c>
@@ -3473,7 +3479,7 @@
       <c r="O41" s="19"/>
       <c r="P41" s="20"/>
     </row>
-    <row r="42" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A42" s="13">
         <v>40</v>
       </c>
@@ -3514,7 +3520,7 @@
       <c r="O42" s="11"/>
       <c r="P42" s="12"/>
     </row>
-    <row r="43" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A43" s="4">
         <v>41</v>
       </c>
@@ -3555,7 +3561,7 @@
       <c r="O43" s="19"/>
       <c r="P43" s="20"/>
     </row>
-    <row r="44" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A44" s="13">
         <v>42</v>
       </c>
@@ -3596,7 +3602,7 @@
       <c r="O44" s="11"/>
       <c r="P44" s="12"/>
     </row>
-    <row r="45" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A45" s="4">
         <v>43</v>
       </c>
@@ -3637,7 +3643,7 @@
       <c r="O45" s="19"/>
       <c r="P45" s="20"/>
     </row>
-    <row r="46" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A46" s="4">
         <v>44</v>
       </c>
@@ -3678,7 +3684,7 @@
       <c r="O46" s="11"/>
       <c r="P46" s="12"/>
     </row>
-    <row r="47" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A47" s="13">
         <v>45</v>
       </c>
@@ -3719,7 +3725,7 @@
       <c r="O47" s="19"/>
       <c r="P47" s="20"/>
     </row>
-    <row r="48" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A48" s="4">
         <v>46</v>
       </c>
@@ -3760,7 +3766,7 @@
       <c r="O48" s="11"/>
       <c r="P48" s="12"/>
     </row>
-    <row r="49" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A49" s="4">
         <v>47</v>
       </c>
@@ -3801,7 +3807,7 @@
       <c r="O49" s="19"/>
       <c r="P49" s="20"/>
     </row>
-    <row r="50" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A50" s="13">
         <v>48</v>
       </c>
@@ -3854,7 +3860,7 @@
       <c r="G51" s="38"/>
       <c r="H51" s="23">
         <f t="shared" ref="H51:M51" si="14">SUMIF(H3:H50,"&gt;0")</f>
-        <v>7577.04</v>
+        <v>8977.0400000000009</v>
       </c>
       <c r="I51" s="24">
         <f t="shared" si="14"/>
@@ -3862,11 +3868,11 @@
       </c>
       <c r="J51" s="23">
         <f t="shared" si="14"/>
-        <v>6851.1074399999998</v>
+        <v>8131.1074399999998</v>
       </c>
       <c r="K51" s="23">
         <f t="shared" si="14"/>
-        <v>1712.7768599999999</v>
+        <v>2032.7768599999999</v>
       </c>
       <c r="L51" s="24">
         <f t="shared" si="14"/>
@@ -3886,33 +3892,65 @@
     <row r="52" spans="1:16" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J52" s="27">
         <f>J51-K51</f>
-        <v>5138.3305799999998</v>
+        <v>6098.3305799999998</v>
       </c>
     </row>
     <row r="53" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="41" t="s">
+      <c r="A53" s="46" t="s">
         <v>25</v>
       </c>
-      <c r="B53" s="41"/>
-      <c r="C53" s="41"/>
-      <c r="D53" s="41"/>
-      <c r="E53" s="41"/>
-      <c r="F53" s="41"/>
-      <c r="G53" s="41"/>
-      <c r="H53" s="41"/>
-      <c r="I53" s="41"/>
-      <c r="J53" s="41"/>
-      <c r="K53" s="41"/>
-      <c r="L53" s="41"/>
-      <c r="M53" s="41"/>
-      <c r="N53" s="41"/>
-      <c r="O53" s="41"/>
-      <c r="P53" s="41"/>
+      <c r="B53" s="46"/>
+      <c r="C53" s="46"/>
+      <c r="D53" s="46"/>
+      <c r="E53" s="46"/>
+      <c r="F53" s="46"/>
+      <c r="G53" s="46"/>
+      <c r="H53" s="46"/>
+      <c r="I53" s="46"/>
+      <c r="J53" s="46"/>
+      <c r="K53" s="46"/>
+      <c r="L53" s="46"/>
+      <c r="M53" s="46"/>
+      <c r="N53" s="46"/>
+      <c r="O53" s="46"/>
+      <c r="P53" s="46"/>
     </row>
     <row r="54" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J54" s="39">
-        <f>J52*0.75</f>
-        <v>3853.7479349999999</v>
+        <f>J52-720-130-180</f>
+        <v>5068.3305799999998</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="E56">
+        <v>1713</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="E59">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="D60" t="s">
+        <v>74</v>
+      </c>
+      <c r="E60">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="D61" t="s">
+        <v>70</v>
+      </c>
+      <c r="E61">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="E62">
+        <f>E56-E59-E60-E61</f>
+        <v>1213</v>
       </c>
     </row>
   </sheetData>
@@ -3981,12 +4019,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
     </row>
     <row r="2" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="28" t="s">
